--- a/ecy4.xlsx
+++ b/ecy4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://perissosprivatewealth-my.sharepoint.com/personal/brandon_perissosprivatewealth_com/Documents/1 Perissos Private Wealth Management/5 Python/Wealth Utility API/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://perissosprivatewealth-my.sharepoint.com/personal/brandon_perissosprivatewealth_com/Documents/1 Perissos Private Wealth Management/5 Python/01_Active_Strategies/Wealth Utility API/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="220" documentId="13_ncr:1_{A317B0E7-1C5D-450E-A529-DF31A54AA737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75A33BBF-8E5A-42EB-9F4B-2EE4DC6596E7}"/>
+  <xr:revisionPtr revIDLastSave="418" documentId="13_ncr:1_{A317B0E7-1C5D-450E-A529-DF31A54AA737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E0B27F3-1BEB-4DCC-822C-B34D4988B4E8}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="15840" windowWidth="28800" windowHeight="15840" activeTab="1" xr2:uid="{7D23DFD4-FCD3-40E1-B8A0-B864FE11F7D6}"/>
   </bookViews>
@@ -945,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173E5D82-F300-41D6-89B7-1A964CE4FD56}">
-  <dimension ref="A1:F554"/>
+  <dimension ref="A1:F557"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -977,15 +977,15 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="array" ref="A2:A554">_xll.YCDS("I:SP500ECY",,"1980-01-01")</f>
+        <f t="array" ref="A2:A557">_xll.YCDS("I:SP500ECY",,"1980-01-01")</f>
         <v>1980-01-31</v>
       </c>
       <c r="B2">
-        <f t="array" aca="1" ref="B2:B554" ca="1">_xll.YCS("I:SP500ECY",,"1980-01-01")</f>
+        <f t="array" aca="1" ref="B2:B557" ca="1">_xll.YCS("I:SP500ECY",,"1980-01-01")</f>
         <v>7.9799999999999996E-2</v>
       </c>
       <c r="C2">
-        <f t="array" aca="1" ref="C2:C554" ca="1">_xll.YCS("I:usltir",,"1980-01-01")</f>
+        <f t="array" aca="1" ref="C2:C557" ca="1">_xll.YCS("I:usltir",,"1980-01-01")</f>
         <v>0.108</v>
       </c>
       <c r="D2">
@@ -993,7 +993,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="E2" s="1">
-        <f t="array" aca="1" ref="E2:E553" ca="1">_xll.YCS("I:us1mccpi",,"1980-01-01")</f>
+        <f t="array" aca="1" ref="E2:E556" ca="1">_xll.YCS("I:us1mccpi",,"1980-01-01")</f>
         <v>1.4E-2</v>
       </c>
       <c r="F2" s="1">
@@ -13319,11 +13319,11 @@
       </c>
       <c r="E495" s="1">
         <f ca="1"/>
-        <v>4.0000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="F495" s="1">
         <f t="shared" ca="1" si="15"/>
-        <v>-2.9500000000000004E-3</v>
+        <v>-1.9500000000000001E-3</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -13369,11 +13369,11 @@
       </c>
       <c r="E497" s="1">
         <f ca="1"/>
-        <v>7.0000000000000001E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="F497" s="1">
         <f t="shared" ca="1" si="15"/>
-        <v>-5.6333333333333331E-3</v>
+        <v>-4.6333333333333331E-3</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -13419,11 +13419,11 @@
       </c>
       <c r="E499" s="1">
         <f ca="1"/>
-        <v>8.9999999999999993E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="F499" s="1">
         <f t="shared" ca="1" si="15"/>
-        <v>-7.7333333333333325E-3</v>
+        <v>-6.7333333333333334E-3</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -13494,11 +13494,11 @@
       </c>
       <c r="E502" s="1">
         <f ca="1"/>
-        <v>4.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F502" s="1">
         <f t="shared" ca="1" si="15"/>
-        <v>-2.8583333333333334E-3</v>
+        <v>-3.8583333333333334E-3</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -13519,11 +13519,11 @@
       </c>
       <c r="E503" s="1">
         <f ca="1"/>
-        <v>8.9999999999999993E-3</v>
+        <v>0.01</v>
       </c>
       <c r="F503" s="1">
         <f t="shared" ca="1" si="15"/>
-        <v>-7.6833333333333328E-3</v>
+        <v>-8.6833333333333328E-3</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -13544,11 +13544,11 @@
       </c>
       <c r="E504" s="1">
         <f ca="1"/>
-        <v>8.0000000000000002E-3</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="F504" s="1">
         <f t="shared" ca="1" si="15"/>
-        <v>-6.7000000000000002E-3</v>
+        <v>-7.6999999999999994E-3</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -13644,11 +13644,11 @@
       </c>
       <c r="E508" s="1">
         <f ca="1"/>
-        <v>0.01</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="F508" s="1">
         <f t="shared" ca="1" si="15"/>
-        <v>-8.2249999999999997E-3</v>
+        <v>-9.2249999999999988E-3</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
@@ -13669,11 +13669,11 @@
       </c>
       <c r="E509" s="1">
         <f ca="1"/>
-        <v>4.0000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="F509" s="1">
         <f t="shared" ca="1" si="15"/>
-        <v>-1.7083333333333334E-3</v>
+        <v>-7.0833333333333338E-4</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -13819,11 +13819,11 @@
       </c>
       <c r="E515" s="1">
         <f ca="1"/>
-        <v>5.0000000000000001E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="F515" s="1">
         <f t="shared" ref="F515:F549" ca="1" si="17">D515-E515</f>
-        <v>-1.6833333333333331E-3</v>
+        <v>-2.6833333333333331E-3</v>
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
@@ -13844,11 +13844,11 @@
       </c>
       <c r="E516" s="1">
         <f ca="1"/>
-        <v>2E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="F516" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>1.2416666666666665E-3</v>
+        <v>2.4166666666666651E-4</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
@@ -13894,11 +13894,11 @@
       </c>
       <c r="E518" s="1">
         <f ca="1"/>
-        <v>6.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F518" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>-3.0583333333333335E-3</v>
+        <v>-2.0583333333333335E-3</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
@@ -13969,11 +13969,11 @@
       </c>
       <c r="E521" s="1">
         <f ca="1"/>
-        <v>4.0000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="F521" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>-1.1166666666666668E-3</v>
+        <v>-1.1666666666666683E-4</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
@@ -14019,11 +14019,11 @@
       </c>
       <c r="E523" s="1">
         <f ca="1"/>
-        <v>3.0000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="F523" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>1.2499999999999968E-4</v>
+        <v>1.1249999999999997E-3</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
@@ -14244,11 +14244,11 @@
       </c>
       <c r="E532" s="1">
         <f ca="1"/>
-        <v>3.0000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="F532" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>5.0833333333333329E-4</v>
+        <v>-4.9166666666666673E-4</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
@@ -14269,11 +14269,11 @@
       </c>
       <c r="E533" s="1">
         <f ca="1"/>
-        <v>3.0000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="F533" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>7.8333333333333336E-4</v>
+        <v>1.7833333333333334E-3</v>
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
@@ -14344,11 +14344,11 @@
       </c>
       <c r="E536" s="1">
         <f ca="1"/>
-        <v>1E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="F536" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>2.5416666666666669E-3</v>
+        <v>1.5416666666666669E-3</v>
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
@@ -14419,11 +14419,11 @@
       </c>
       <c r="E539" s="1">
         <f ca="1"/>
-        <v>2E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="F539" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>1.4166666666666668E-3</v>
+        <v>4.1666666666666675E-4</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
@@ -14469,11 +14469,11 @@
       </c>
       <c r="E541" s="1">
         <f ca="1"/>
-        <v>4.0000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="F541" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>-3.4166666666666677E-4</v>
+        <v>6.5833333333333325E-4</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
@@ -14494,11 +14494,11 @@
       </c>
       <c r="E542" s="1">
         <f ca="1"/>
-        <v>5.0000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="F542" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>-1.1416666666666667E-3</v>
+        <v>-1.4166666666666668E-4</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
@@ -14544,11 +14544,11 @@
       </c>
       <c r="E544" s="1">
         <f ca="1"/>
-        <v>-1E-3</v>
+        <v>0</v>
       </c>
       <c r="F544" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>4.5666666666666668E-3</v>
+        <v>3.5666666666666663E-3</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
@@ -14669,11 +14669,11 @@
       </c>
       <c r="E549" s="1">
         <f ca="1"/>
-        <v>4.0000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="F549" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>-4.5000000000000031E-4</v>
+        <v>5.4999999999999971E-4</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="B552">
         <f ca="1"/>
-        <v>1.6199999999999999E-2</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="C552">
         <f ca="1"/>
@@ -14737,7 +14737,7 @@
       </c>
       <c r="B553">
         <f ca="1"/>
-        <v>1.55E-2</v>
+        <v>1.5900000000000001E-2</v>
       </c>
       <c r="C553">
         <f ca="1"/>
@@ -14754,11 +14754,62 @@
       </c>
       <c r="B554">
         <f ca="1"/>
-        <v>1.49E-2</v>
+        <v>1.54E-2</v>
       </c>
       <c r="C554">
         <f ca="1"/>
-        <v>4.1799999999999997E-2</v>
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="E554" s="1">
+        <f ca="1"/>
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A555" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="B555">
+        <f ca="1"/>
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="C555">
+        <f ca="1"/>
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="E555" s="1">
+        <f ca="1"/>
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A556" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="B556">
+        <f ca="1"/>
+        <v>1.67E-2</v>
+      </c>
+      <c r="C556">
+        <f ca="1"/>
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="E556" s="1">
+        <f ca="1"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A557" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="B557">
+        <f ca="1"/>
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="C557">
+        <f ca="1"/>
+        <v>4.2999999999999997E-2</v>
       </c>
     </row>
   </sheetData>
@@ -14768,7 +14819,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA56A079-CA0B-477E-8FC4-5F43798C1EE5}">
-  <dimension ref="A1:J674"/>
+  <dimension ref="A1:J677"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -14813,19 +14864,19 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="array" ref="A2:A674">_xll.YCDS("I:USLTIR",,"1970-01-31")</f>
+        <f t="array" ref="A2:A677">_xll.YCDS("I:USLTIR",,"1970-01-31")</f>
         <v>1970-01-31</v>
       </c>
       <c r="B2">
         <f t="shared" ref="B2:B65" ca="1" si="0">F2*$C$669/C2</f>
-        <v>48.888541424802114</v>
+        <v>48.877504749340375</v>
       </c>
       <c r="C2">
-        <f t="array" aca="1" ref="C2:C673" ca="1">_xll.YCS("I:USCPI",,"1970-01-31")</f>
+        <f t="array" aca="1" ref="C2:C676" ca="1">_xll.YCS("I:USCPI",,"1970-01-31")</f>
         <v>37.9</v>
       </c>
       <c r="D2">
-        <f t="array" aca="1" ref="D2:D674" ca="1">_xll.YCS("I:USLTIR",,"1970-01-31")</f>
+        <f t="array" aca="1" ref="D2:D677" ca="1">_xll.YCS("I:USLTIR",,"1970-01-31")</f>
         <v>7.7899999999999997E-2</v>
       </c>
       <c r="E2">
@@ -14833,7 +14884,7 @@
         <v>6.4916666666666664E-3</v>
       </c>
       <c r="F2">
-        <f t="array" aca="1" ref="F2:F670" ca="1">_xll.YCS("I:SP500E",,"1970-01-31")</f>
+        <f t="array" aca="1" ref="F2:F676" ca="1">_xll.YCS("I:SP500E",,"1970-01-31")</f>
         <v>5.73</v>
       </c>
       <c r="G2">
@@ -14844,11 +14895,11 @@
         <v>1.0916666666666661E-3</v>
       </c>
       <c r="I2" s="2">
-        <f t="array" aca="1" ref="I2:I674" ca="1">_xll.YCS("I:SP500ECY",,"1970-01-31")</f>
+        <f t="array" aca="1" ref="I2:I677" ca="1">_xll.YCS("I:SP500ECY",,"1970-01-31")</f>
         <v>6.4000000000000003E-3</v>
       </c>
       <c r="J2" s="2">
-        <f t="array" aca="1" ref="J2:J673" ca="1">_xll.YCS("I:SP500RD", ,"1970-01-31")</f>
+        <f t="array" aca="1" ref="J2:J676" ca="1">_xll.YCS("I:SP500RD", ,"1970-01-31")</f>
         <v>21.813400000000001</v>
       </c>
     </row>
@@ -14858,7 +14909,7 @@
       </c>
       <c r="B3">
         <f t="shared" ca="1" si="0"/>
-        <v>48.207546456692903</v>
+        <v>48.196663517060365</v>
       </c>
       <c r="C3">
         <f ca="1"/>
@@ -14899,7 +14950,7 @@
       </c>
       <c r="B4">
         <f t="shared" ca="1" si="0"/>
-        <v>47.533663707571804</v>
+        <v>47.522932898172328</v>
       </c>
       <c r="C4">
         <f ca="1"/>
@@ -14940,7 +14991,7 @@
       </c>
       <c r="B5">
         <f t="shared" ca="1" si="0"/>
-        <v>46.978741873246747</v>
+        <v>46.96813633844156</v>
       </c>
       <c r="C5">
         <f ca="1"/>
@@ -14981,7 +15032,7 @@
       </c>
       <c r="B6">
         <f t="shared" ca="1" si="0"/>
-        <v>46.549923261139895</v>
+        <v>46.53941453290156</v>
       </c>
       <c r="C6">
         <f ca="1"/>
@@ -15022,7 +15073,7 @@
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="0"/>
-        <v>46.004362886597939</v>
+        <v>45.993977319587628</v>
       </c>
       <c r="C7">
         <f ca="1"/>
@@ -15063,7 +15114,7 @@
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="0"/>
-        <v>45.442783493059125</v>
+        <v>45.432524703598972</v>
       </c>
       <c r="C8">
         <f ca="1"/>
@@ -15104,7 +15155,7 @@
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="0"/>
-        <v>44.884001079999997</v>
+        <v>44.873868436666669</v>
       </c>
       <c r="C9">
         <f ca="1"/>
@@ -15145,7 +15196,7 @@
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="0"/>
-        <v>44.2150775510204</v>
+        <v>44.205095918367348</v>
       </c>
       <c r="C10">
         <f ca="1"/>
@@ -15186,7 +15237,7 @@
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="0"/>
-        <v>43.361388886294414</v>
+        <v>43.351599975380715</v>
       </c>
       <c r="C11">
         <f ca="1"/>
@@ -15227,7 +15278,7 @@
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="0"/>
-        <v>42.51640499696969</v>
+        <v>42.506806842676767</v>
       </c>
       <c r="C12">
         <f ca="1"/>
@@ -15268,7 +15319,7 @@
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="0"/>
-        <v>41.679832160804018</v>
+        <v>41.670422864321608</v>
       </c>
       <c r="C13">
         <f ca="1"/>
@@ -15309,7 +15360,7 @@
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="0"/>
-        <v>41.818502255639096</v>
+        <v>41.809061654135341</v>
       </c>
       <c r="C14">
         <f ca="1"/>
@@ -15350,7 +15401,7 @@
       </c>
       <c r="B15">
         <f t="shared" ca="1" si="0"/>
-        <v>42.06163308270677</v>
+        <v>42.052137593984966</v>
       </c>
       <c r="C15">
         <f ca="1"/>
@@ -15391,7 +15442,7 @@
       </c>
       <c r="B16">
         <f t="shared" ca="1" si="0"/>
-        <v>42.199001999999993</v>
+        <v>42.1894755</v>
       </c>
       <c r="C16">
         <f ca="1"/>
@@ -15432,7 +15483,7 @@
       </c>
       <c r="B17">
         <f t="shared" ca="1" si="0"/>
-        <v>42.36253870623441</v>
+        <v>42.352975287531173</v>
       </c>
       <c r="C17">
         <f ca="1"/>
@@ -15473,7 +15524,7 @@
       </c>
       <c r="B18">
         <f t="shared" ca="1" si="0"/>
-        <v>42.419820294789083</v>
+        <v>42.410243944665012</v>
       </c>
       <c r="C18">
         <f ca="1"/>
@@ -15514,7 +15565,7 @@
       </c>
       <c r="B19">
         <f t="shared" ca="1" si="0"/>
-        <v>42.476456296296298</v>
+        <v>42.466867160493827</v>
       </c>
       <c r="C19">
         <f ca="1"/>
@@ -15555,7 +15606,7 @@
       </c>
       <c r="B20">
         <f t="shared" ca="1" si="0"/>
-        <v>42.663897484729063</v>
+        <v>42.654266033743845</v>
       </c>
       <c r="C20">
         <f ca="1"/>
@@ -15596,7 +15647,7 @@
       </c>
       <c r="B21">
         <f t="shared" ca="1" si="0"/>
-        <v>42.850338135626529</v>
+        <v>42.840664595331688</v>
       </c>
       <c r="C21">
         <f ca="1"/>
@@ -15637,7 +15688,7 @@
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="0"/>
-        <v>43.035944117647055</v>
+        <v>43.026228676470588</v>
       </c>
       <c r="C22">
         <f ca="1"/>
@@ -15678,7 +15729,7 @@
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="0"/>
-        <v>43.642280684596571</v>
+        <v>43.632428361858189</v>
       </c>
       <c r="C23">
         <f ca="1"/>
@@ -15719,7 +15770,7 @@
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="0"/>
-        <v>44.245659512195125</v>
+        <v>44.235670975609757</v>
       </c>
       <c r="C24">
         <f ca="1"/>
@@ -15760,7 +15811,7 @@
       </c>
       <c r="B25">
         <f t="shared" ca="1" si="0"/>
-        <v>44.846102189781021</v>
+        <v>44.835978102189785</v>
       </c>
       <c r="C25">
         <f ca="1"/>
@@ -15801,7 +15852,7 @@
       </c>
       <c r="B26">
         <f t="shared" ca="1" si="0"/>
-        <v>45.025062084466015</v>
+        <v>45.014897596359219</v>
       </c>
       <c r="C26">
         <f ca="1"/>
@@ -15842,7 +15893,7 @@
       </c>
       <c r="B27">
         <f t="shared" ca="1" si="0"/>
-        <v>45.093890872463767</v>
+        <v>45.083710846135268</v>
       </c>
       <c r="C27">
         <f ca="1"/>
@@ -15883,7 +15934,7 @@
       </c>
       <c r="B28">
         <f t="shared" ca="1" si="0"/>
-        <v>45.380310144927535</v>
+        <v>45.370065458937198</v>
       </c>
       <c r="C28">
         <f ca="1"/>
@@ -15924,7 +15975,7 @@
       </c>
       <c r="B29">
         <f t="shared" ca="1" si="0"/>
-        <v>45.686502219759035</v>
+        <v>45.676188410361448</v>
       </c>
       <c r="C29">
         <f ca="1"/>
@@ -15965,7 +16016,7 @@
       </c>
       <c r="B30">
         <f t="shared" ca="1" si="0"/>
-        <v>45.991299949038456</v>
+        <v>45.980917331009607</v>
       </c>
       <c r="C30">
         <f ca="1"/>
@@ -16006,7 +16057,7 @@
       </c>
       <c r="B31">
         <f t="shared" ca="1" si="0"/>
-        <v>46.294558273381284</v>
+        <v>46.284107194244598</v>
       </c>
       <c r="C31">
         <f ca="1"/>
@@ -16047,7 +16098,7 @@
       </c>
       <c r="B32">
         <f t="shared" ca="1" si="0"/>
-        <v>46.622203777033491</v>
+        <v>46.611678731339715</v>
       </c>
       <c r="C32">
         <f ca="1"/>
@@ -16088,7 +16139,7 @@
       </c>
       <c r="B33">
         <f t="shared" ca="1" si="0"/>
-        <v>46.94820816515513</v>
+        <v>46.937609523389028</v>
       </c>
       <c r="C33">
         <f ca="1"/>
@@ -16129,7 +16180,7 @@
       </c>
       <c r="B34">
         <f t="shared" ca="1" si="0"/>
-        <v>47.160450356294533</v>
+        <v>47.149803800475055</v>
       </c>
       <c r="C34">
         <f ca="1"/>
@@ -16170,7 +16221,7 @@
       </c>
       <c r="B35">
         <f t="shared" ca="1" si="0"/>
-        <v>47.76385123507108</v>
+        <v>47.753068460426533</v>
       </c>
       <c r="C35">
         <f ca="1"/>
@@ -16211,7 +16262,7 @@
       </c>
       <c r="B36">
         <f t="shared" ca="1" si="0"/>
-        <v>48.250408440566034</v>
+        <v>48.239515824764155</v>
       </c>
       <c r="C36">
         <f ca="1"/>
@@ -16252,7 +16303,7 @@
       </c>
       <c r="B37">
         <f t="shared" ca="1" si="0"/>
-        <v>48.846985411764699</v>
+        <v>48.83595811764706</v>
       </c>
       <c r="C37">
         <f ca="1"/>
@@ -16293,7 +16344,7 @@
       </c>
       <c r="B38">
         <f t="shared" ca="1" si="0"/>
-        <v>49.57745662482435</v>
+        <v>49.566264425526924</v>
       </c>
       <c r="C38">
         <f ca="1"/>
@@ -16334,7 +16385,7 @@
       </c>
       <c r="B39">
         <f t="shared" ca="1" si="0"/>
-        <v>50.184062374883716</v>
+        <v>50.172733233255819</v>
       </c>
       <c r="C39">
         <f ca="1"/>
@@ -16375,7 +16426,7 @@
       </c>
       <c r="B40">
         <f t="shared" ca="1" si="0"/>
-        <v>50.66532718894009</v>
+        <v>50.653889400921656</v>
       </c>
       <c r="C40">
         <f ca="1"/>
@@ -16416,7 +16467,7 @@
       </c>
       <c r="B41">
         <f t="shared" ca="1" si="0"/>
-        <v>51.378099819679619</v>
+        <v>51.366501121967957</v>
       </c>
       <c r="C41">
         <f ca="1"/>
@@ -16457,7 +16508,7 @@
       </c>
       <c r="B42">
         <f t="shared" ca="1" si="0"/>
-        <v>52.199862366287014</v>
+        <v>52.188078154214118</v>
       </c>
       <c r="C42">
         <f ca="1"/>
@@ -16498,7 +16549,7 @@
       </c>
       <c r="B43">
         <f t="shared" ca="1" si="0"/>
-        <v>52.894156561085964</v>
+        <v>52.882215610859731</v>
       </c>
       <c r="C43">
         <f ca="1"/>
@@ -16539,7 +16590,7 @@
       </c>
       <c r="B44">
         <f t="shared" ca="1" si="0"/>
-        <v>54.01590774027148</v>
+        <v>54.003713552714927</v>
       </c>
       <c r="C44">
         <f ca="1"/>
@@ -16580,7 +16631,7 @@
       </c>
       <c r="B45">
         <f t="shared" ca="1" si="0"/>
-        <v>54.157505730666671</v>
+        <v>54.145279577111111</v>
       </c>
       <c r="C45">
         <f ca="1"/>
@@ -16621,7 +16672,7 @@
       </c>
       <c r="B46">
         <f t="shared" ca="1" si="0"/>
-        <v>55.014804424778752</v>
+        <v>55.002384734513271</v>
       </c>
       <c r="C46">
         <f ca="1"/>
@@ -16662,7 +16713,7 @@
       </c>
       <c r="B47">
         <f t="shared" ca="1" si="0"/>
-        <v>55.64321486578946</v>
+        <v>55.630653310745608</v>
       </c>
       <c r="C47">
         <f ca="1"/>
@@ -16703,7 +16754,7 @@
       </c>
       <c r="B48">
         <f t="shared" ca="1" si="0"/>
-        <v>56.383198303267974</v>
+        <v>56.370469695642704</v>
       </c>
       <c r="C48">
         <f ca="1"/>
@@ -16744,7 +16795,7 @@
       </c>
       <c r="B49">
         <f t="shared" ca="1" si="0"/>
-        <v>56.990285961123114</v>
+        <v>56.977420302375812</v>
       </c>
       <c r="C49">
         <f ca="1"/>
@@ -16785,7 +16836,7 @@
       </c>
       <c r="B50">
         <f t="shared" ca="1" si="0"/>
-        <v>56.842070894871789</v>
+        <v>56.829238695940177</v>
       </c>
       <c r="C50">
         <f ca="1"/>
@@ -16826,7 +16877,7 @@
       </c>
       <c r="B51">
         <f t="shared" ca="1" si="0"/>
-        <v>56.696920975052848</v>
+        <v>56.684121543974626</v>
       </c>
       <c r="C51">
         <f ca="1"/>
@@ -16867,7 +16918,7 @@
       </c>
       <c r="B52">
         <f t="shared" ca="1" si="0"/>
-        <v>56.554875313807528</v>
+        <v>56.542107949790797</v>
       </c>
       <c r="C52">
         <f ca="1"/>
@@ -16908,7 +16959,7 @@
       </c>
       <c r="B53">
         <f t="shared" ca="1" si="0"/>
-        <v>57.053712222037419</v>
+        <v>57.040832244698542</v>
       </c>
       <c r="C53">
         <f ca="1"/>
@@ -16949,7 +17000,7 @@
       </c>
       <c r="B54">
         <f t="shared" ca="1" si="0"/>
-        <v>57.309482348148144</v>
+        <v>57.296544630246913</v>
       </c>
       <c r="C54">
         <f ca="1"/>
@@ -16990,7 +17041,7 @@
       </c>
       <c r="B55">
         <f t="shared" ca="1" si="0"/>
-        <v>57.677578775510206</v>
+        <v>57.664557959183675</v>
       </c>
       <c r="C55">
         <f ca="1"/>
@@ -17031,7 +17082,7 @@
       </c>
       <c r="B56">
         <f t="shared" ca="1" si="0"/>
-        <v>58.13553432292089</v>
+        <v>58.122410122312374</v>
       </c>
       <c r="C56">
         <f ca="1"/>
@@ -17072,7 +17123,7 @@
       </c>
       <c r="B57">
         <f t="shared" ca="1" si="0"/>
-        <v>58.235782723046093</v>
+        <v>58.222635891182371</v>
       </c>
       <c r="C57">
         <f ca="1"/>
@@ -17113,7 +17164,7 @@
       </c>
       <c r="B58">
         <f t="shared" ca="1" si="0"/>
-        <v>58.218301185770741</v>
+        <v>58.205158300395254</v>
       </c>
       <c r="C58">
         <f ca="1"/>
@@ -17154,7 +17205,7 @@
       </c>
       <c r="B59">
         <f t="shared" ca="1" si="0"/>
-        <v>57.29674035058823</v>
+        <v>57.283805509215689</v>
       </c>
       <c r="C59">
         <f ca="1"/>
@@ -17195,7 +17246,7 @@
       </c>
       <c r="B60">
         <f t="shared" ca="1" si="0"/>
-        <v>56.279965866407757</v>
+        <v>56.267260563689312</v>
       </c>
       <c r="C60">
         <f ca="1"/>
@@ -17236,7 +17287,7 @@
       </c>
       <c r="B61">
         <f t="shared" ca="1" si="0"/>
-        <v>55.389324855491324</v>
+        <v>55.376820616570328</v>
       </c>
       <c r="C61">
         <f ca="1"/>
@@ -17277,7 +17328,7 @@
       </c>
       <c r="B62">
         <f t="shared" ca="1" si="0"/>
-        <v>54.058855872275331</v>
+        <v>54.046651989101342</v>
       </c>
       <c r="C62">
         <f ca="1"/>
@@ -17318,7 +17369,7 @@
       </c>
       <c r="B63">
         <f t="shared" ca="1" si="0"/>
-        <v>52.848927716349799</v>
+        <v>52.836996976615964</v>
       </c>
       <c r="C63">
         <f ca="1"/>
@@ -17359,7 +17410,7 @@
       </c>
       <c r="B64">
         <f t="shared" ca="1" si="0"/>
-        <v>51.750488636363627</v>
+        <v>51.738805871212115</v>
       </c>
       <c r="C64">
         <f ca="1"/>
@@ -17400,7 +17451,7 @@
       </c>
       <c r="B65">
         <f t="shared" ca="1" si="0"/>
-        <v>50.558693544905665</v>
+        <v>50.547279829622646</v>
       </c>
       <c r="C65">
         <f ca="1"/>
@@ -17441,7 +17492,7 @@
       </c>
       <c r="B66">
         <f t="shared" ref="B66:B129" ca="1" si="4">F66*$C$669/C66</f>
-        <v>49.468784974011285</v>
+        <v>49.457617307532949</v>
       </c>
       <c r="C66">
         <f ca="1"/>
@@ -17482,7 +17533,7 @@
       </c>
       <c r="B67">
         <f t="shared" ca="1" si="4"/>
-        <v>48.111727850467283</v>
+        <v>48.100866542056082</v>
       </c>
       <c r="C67">
         <f ca="1"/>
@@ -17523,7 +17574,7 @@
       </c>
       <c r="B68">
         <f t="shared" ca="1" si="4"/>
-        <v>47.267014113333332</v>
+        <v>47.256343500555559</v>
       </c>
       <c r="C68">
         <f ca="1"/>
@@ -17564,7 +17615,7 @@
       </c>
       <c r="B69">
         <f t="shared" ca="1" si="4"/>
-        <v>46.694895163837629</v>
+        <v>46.684353707933575</v>
       </c>
       <c r="C69">
         <f ca="1"/>
@@ -17605,7 +17656,7 @@
       </c>
       <c r="B70">
         <f t="shared" ca="1" si="4"/>
-        <v>45.957960439560438</v>
+        <v>45.947585347985346</v>
       </c>
       <c r="C70">
         <f ca="1"/>
@@ -17646,7 +17697,7 @@
       </c>
       <c r="B71">
         <f t="shared" ca="1" si="4"/>
-        <v>46.099513986885242</v>
+        <v>46.089106939344262</v>
       </c>
       <c r="C71">
         <f ca="1"/>
@@ -17687,7 +17738,7 @@
       </c>
       <c r="B72">
         <f t="shared" ca="1" si="4"/>
-        <v>46.155854649547919</v>
+        <v>46.145434883001812</v>
       </c>
       <c r="C72">
         <f ca="1"/>
@@ -17728,7 +17779,7 @@
       </c>
       <c r="B73">
         <f t="shared" ca="1" si="4"/>
-        <v>46.294558273381284</v>
+        <v>46.284107194244605</v>
       </c>
       <c r="C73">
         <f ca="1"/>
@@ -17769,7 +17820,7 @@
       </c>
       <c r="B74">
         <f t="shared" ca="1" si="4"/>
-        <v>47.480787851612902</v>
+        <v>47.470068979032256</v>
       </c>
       <c r="C74">
         <f ca="1"/>
@@ -17810,7 +17861,7 @@
       </c>
       <c r="B75">
         <f t="shared" ca="1" si="4"/>
-        <v>48.745647904830044</v>
+        <v>48.73464348783542</v>
       </c>
       <c r="C75">
         <f ca="1"/>
@@ -17851,7 +17902,7 @@
       </c>
       <c r="B76">
         <f t="shared" ca="1" si="4"/>
-        <v>50.005932857142852</v>
+        <v>49.994643928571428</v>
       </c>
       <c r="C76">
         <f ca="1"/>
@@ -17892,7 +17943,7 @@
       </c>
       <c r="B77">
         <f t="shared" ca="1" si="4"/>
-        <v>51.050414222459878</v>
+        <v>51.038889500356504</v>
       </c>
       <c r="C77">
         <f ca="1"/>
@@ -17933,7 +17984,7 @@
       </c>
       <c r="B78">
         <f t="shared" ca="1" si="4"/>
-        <v>51.906400746808515</v>
+        <v>51.894682784219867</v>
       </c>
       <c r="C78">
         <f ca="1"/>
@@ -17974,7 +18025,7 @@
       </c>
       <c r="B79">
         <f t="shared" ca="1" si="4"/>
-        <v>52.753386243386238</v>
+        <v>52.741477072310403</v>
       </c>
       <c r="C79">
         <f ca="1"/>
@@ -18015,7 +18066,7 @@
       </c>
       <c r="B80">
         <f t="shared" ca="1" si="4"/>
-        <v>53.043042105263154</v>
+        <v>53.031067543859649</v>
       </c>
       <c r="C80">
         <f ca="1"/>
@@ -18056,7 +18107,7 @@
       </c>
       <c r="B81">
         <f t="shared" ca="1" si="4"/>
-        <v>53.329664921465962</v>
+        <v>53.317625654450261</v>
       </c>
       <c r="C81">
         <f ca="1"/>
@@ -18097,7 +18148,7 @@
       </c>
       <c r="B82">
         <f t="shared" ca="1" si="4"/>
-        <v>53.613302083333338</v>
+        <v>53.601198784722222</v>
       </c>
       <c r="C82">
         <f ca="1"/>
@@ -18138,7 +18189,7 @@
       </c>
       <c r="B83">
         <f t="shared" ca="1" si="4"/>
-        <v>54.005697409326423</v>
+        <v>53.993505526770292</v>
       </c>
       <c r="C83">
         <f ca="1"/>
@@ -18179,7 +18230,7 @@
       </c>
       <c r="B84">
         <f t="shared" ca="1" si="4"/>
-        <v>54.487668846815829</v>
+        <v>54.475368158347671</v>
       </c>
       <c r="C84">
         <f ca="1"/>
@@ -18220,7 +18271,7 @@
       </c>
       <c r="B85">
         <f t="shared" ca="1" si="4"/>
-        <v>54.872213013698627</v>
+        <v>54.859825513698631</v>
       </c>
       <c r="C85">
         <f ca="1"/>
@@ -18261,7 +18312,7 @@
       </c>
       <c r="B86">
         <f t="shared" ca="1" si="4"/>
-        <v>54.903957033730833</v>
+        <v>54.891562367461667</v>
       </c>
       <c r="C86">
         <f ca="1"/>
@@ -18302,7 +18353,7 @@
       </c>
       <c r="B87">
         <f t="shared" ca="1" si="4"/>
-        <v>54.657240829679594</v>
+        <v>54.644901860033734</v>
       </c>
       <c r="C87">
         <f ca="1"/>
@@ -18343,7 +18394,7 @@
       </c>
       <c r="B88">
         <f t="shared" ca="1" si="4"/>
-        <v>54.689750335570466</v>
+        <v>54.677404026845636</v>
       </c>
       <c r="C88">
         <f ca="1"/>
@@ -18384,7 +18435,7 @@
       </c>
       <c r="B89">
         <f t="shared" ca="1" si="4"/>
-        <v>54.935771019999997</v>
+        <v>54.923369171666671</v>
       </c>
       <c r="C89">
         <f ca="1"/>
@@ -18425,7 +18476,7 @@
       </c>
       <c r="B90">
         <f t="shared" ca="1" si="4"/>
-        <v>55.362387687707631</v>
+        <v>55.349889529900331</v>
       </c>
       <c r="C90">
         <f ca="1"/>
@@ -18466,7 +18517,7 @@
       </c>
       <c r="B91">
         <f t="shared" ca="1" si="4"/>
-        <v>55.69343603305785</v>
+        <v>55.680863140495866</v>
       </c>
       <c r="C91">
         <f ca="1"/>
@@ -18507,7 +18558,7 @@
       </c>
       <c r="B92">
         <f t="shared" ca="1" si="4"/>
-        <v>55.93293057236842</v>
+        <v>55.920303613486844</v>
       </c>
       <c r="C92">
         <f ca="1"/>
@@ -18548,7 +18599,7 @@
       </c>
       <c r="B93">
         <f t="shared" ca="1" si="4"/>
-        <v>56.169544045826513</v>
+        <v>56.156863671031097</v>
       </c>
       <c r="C93">
         <f ca="1"/>
@@ -18589,7 +18640,7 @@
       </c>
       <c r="B94">
         <f t="shared" ca="1" si="4"/>
-        <v>56.496385644371941</v>
+        <v>56.483631484502453</v>
       </c>
       <c r="C94">
         <f ca="1"/>
@@ -18630,7 +18681,7 @@
       </c>
       <c r="B95">
         <f t="shared" ca="1" si="4"/>
-        <v>56.53620584415583</v>
+        <v>56.52344269480519</v>
       </c>
       <c r="C95">
         <f ca="1"/>
@@ -18671,7 +18722,7 @@
       </c>
       <c r="B96">
         <f t="shared" ca="1" si="4"/>
-        <v>56.484389032258065</v>
+        <v>56.471637580645158</v>
       </c>
       <c r="C96">
         <f ca="1"/>
@@ -18712,7 +18763,7 @@
       </c>
       <c r="B97">
         <f t="shared" ca="1" si="4"/>
-        <v>56.52381958266453</v>
+        <v>56.511059229534517</v>
       </c>
       <c r="C97">
         <f ca="1"/>
@@ -18753,7 +18804,7 @@
       </c>
       <c r="B98">
         <f t="shared" ca="1" si="4"/>
-        <v>56.214794258373196</v>
+        <v>56.202103668261564</v>
       </c>
       <c r="C98">
         <f ca="1"/>
@@ -18794,7 +18845,7 @@
       </c>
       <c r="B99">
         <f t="shared" ca="1" si="4"/>
-        <v>55.998432380952373</v>
+        <v>55.985790634920633</v>
       </c>
       <c r="C99">
         <f ca="1"/>
@@ -18835,7 +18886,7 @@
       </c>
       <c r="B100">
         <f t="shared" ca="1" si="4"/>
-        <v>55.696133753943215</v>
+        <v>55.683560252365929</v>
       </c>
       <c r="C100">
         <f ca="1"/>
@@ -18876,7 +18927,7 @@
       </c>
       <c r="B101">
         <f t="shared" ca="1" si="4"/>
-        <v>55.783073258215964</v>
+        <v>55.770480129890458</v>
       </c>
       <c r="C101">
         <f ca="1"/>
@@ -18917,7 +18968,7 @@
       </c>
       <c r="B102">
         <f t="shared" ca="1" si="4"/>
-        <v>55.782546027906967</v>
+        <v>55.769953018604646</v>
       </c>
       <c r="C102">
         <f ca="1"/>
@@ -18958,7 +19009,7 @@
       </c>
       <c r="B103">
         <f t="shared" ca="1" si="4"/>
-        <v>55.867349538461539</v>
+        <v>55.854737384615383</v>
       </c>
       <c r="C103">
         <f ca="1"/>
@@ -18999,7 +19050,7 @@
       </c>
       <c r="B104">
         <f t="shared" ca="1" si="4"/>
-        <v>56.000226888549605</v>
+        <v>55.987584737404575</v>
       </c>
       <c r="C104">
         <f ca="1"/>
@@ -19040,7 +19091,7 @@
       </c>
       <c r="B105">
         <f t="shared" ca="1" si="4"/>
-        <v>56.216757796661597</v>
+        <v>56.204066763277687</v>
       </c>
       <c r="C105">
         <f ca="1"/>
@@ -19081,7 +19132,7 @@
       </c>
       <c r="B106">
         <f t="shared" ca="1" si="4"/>
-        <v>56.260473383458638</v>
+        <v>56.247772481203008</v>
       </c>
       <c r="C106">
         <f ca="1"/>
@@ -19122,7 +19173,7 @@
       </c>
       <c r="B107">
         <f t="shared" ca="1" si="4"/>
-        <v>56.978086157973173</v>
+        <v>56.965223253353201</v>
       </c>
       <c r="C107">
         <f ca="1"/>
@@ -19163,7 +19214,7 @@
       </c>
       <c r="B108">
         <f t="shared" ca="1" si="4"/>
-        <v>57.854370648888889</v>
+        <v>57.841309921481489</v>
       </c>
       <c r="C108">
         <f ca="1"/>
@@ -19204,7 +19255,7 @@
       </c>
       <c r="B109">
         <f t="shared" ca="1" si="4"/>
-        <v>58.719854491899845</v>
+        <v>58.706598379970544</v>
       </c>
       <c r="C109">
         <f ca="1"/>
@@ -19245,7 +19296,7 @@
       </c>
       <c r="B110">
         <f t="shared" ca="1" si="4"/>
-        <v>59.731703667153283</v>
+        <v>59.718219128467155</v>
       </c>
       <c r="C110">
         <f ca="1"/>
@@ -19286,7 +19337,7 @@
       </c>
       <c r="B111">
         <f t="shared" ca="1" si="4"/>
-        <v>60.638693913294794</v>
+        <v>60.625004619942189</v>
       </c>
       <c r="C111">
         <f ca="1"/>
@@ -19327,7 +19378,7 @@
       </c>
       <c r="B112">
         <f t="shared" ca="1" si="4"/>
-        <v>61.527055793991401</v>
+        <v>61.513165951359085</v>
       </c>
       <c r="C112">
         <f ca="1"/>
@@ -19368,7 +19419,7 @@
       </c>
       <c r="B113">
         <f t="shared" ca="1" si="4"/>
-        <v>61.955351541076489</v>
+        <v>61.941365009915017</v>
       </c>
       <c r="C113">
         <f ca="1"/>
@@ -19409,7 +19460,7 @@
       </c>
       <c r="B114">
         <f t="shared" ca="1" si="4"/>
-        <v>62.287424386554612</v>
+        <v>62.273362889355731</v>
       </c>
       <c r="C114">
         <f ca="1"/>
@@ -19450,7 +19501,7 @@
       </c>
       <c r="B115">
         <f t="shared" ca="1" si="4"/>
-        <v>62.61258614958448</v>
+        <v>62.598451246537394</v>
       </c>
       <c r="C115">
         <f ca="1"/>
@@ -19491,7 +19542,7 @@
       </c>
       <c r="B116">
         <f t="shared" ca="1" si="4"/>
-        <v>62.886324641095882</v>
+        <v>62.87212794109589</v>
       </c>
       <c r="C116">
         <f ca="1"/>
@@ -19532,7 +19583,7 @@
       </c>
       <c r="B117">
         <f t="shared" ca="1" si="4"/>
-        <v>63.239380477611938</v>
+        <v>63.225104074626856</v>
       </c>
       <c r="C117">
         <f ca="1"/>
@@ -19573,7 +19624,7 @@
       </c>
       <c r="B118">
         <f t="shared" ca="1" si="4"/>
-        <v>63.586227419354827</v>
+        <v>63.571872715053757</v>
       </c>
       <c r="C118">
         <f ca="1"/>
@@ -19614,7 +19665,7 @@
       </c>
       <c r="B119">
         <f t="shared" ca="1" si="4"/>
-        <v>63.239592271276592</v>
+        <v>63.225315820478727</v>
       </c>
       <c r="C119">
         <f ca="1"/>
@@ -19655,7 +19706,7 @@
       </c>
       <c r="B120">
         <f t="shared" ca="1" si="4"/>
-        <v>62.899829226315795</v>
+        <v>62.885629477631575</v>
       </c>
       <c r="C120">
         <f ca="1"/>
@@ -19696,7 +19747,7 @@
       </c>
       <c r="B121">
         <f t="shared" ca="1" si="4"/>
-        <v>62.486203381014292</v>
+        <v>62.472097009102725</v>
       </c>
       <c r="C121">
         <f ca="1"/>
@@ -19737,7 +19788,7 @@
       </c>
       <c r="B122">
         <f t="shared" ca="1" si="4"/>
-        <v>62.199065399999995</v>
+        <v>62.18502385</v>
       </c>
       <c r="C122">
         <f ca="1"/>
@@ -19778,7 +19829,7 @@
       </c>
       <c r="B123">
         <f t="shared" ca="1" si="4"/>
-        <v>61.998702516455687</v>
+        <v>61.984706198734173</v>
       </c>
       <c r="C123">
         <f ca="1"/>
@@ -19819,7 +19870,7 @@
       </c>
       <c r="B124">
         <f t="shared" ca="1" si="4"/>
-        <v>61.725787265917596</v>
+        <v>61.71185255930088</v>
       </c>
       <c r="C124">
         <f ca="1"/>
@@ -19860,7 +19911,7 @@
       </c>
       <c r="B125">
         <f t="shared" ca="1" si="4"/>
-        <v>60.64893672682323</v>
+        <v>60.635245121137203</v>
       </c>
       <c r="C125">
         <f ca="1"/>
@@ -19901,7 +19952,7 @@
       </c>
       <c r="B126">
         <f t="shared" ca="1" si="4"/>
-        <v>59.593570854345153</v>
+        <v>59.580117499387995</v>
       </c>
       <c r="C126">
         <f ca="1"/>
@@ -19942,7 +19993,7 @@
       </c>
       <c r="B127">
         <f t="shared" ca="1" si="4"/>
-        <v>58.558280727272724</v>
+        <v>58.545061090909087</v>
       </c>
       <c r="C127">
         <f ca="1"/>
@@ -19983,7 +20034,7 @@
       </c>
       <c r="B128">
         <f t="shared" ca="1" si="4"/>
-        <v>58.095905084745759</v>
+        <v>58.082789830508474</v>
       </c>
       <c r="C128">
         <f ca="1"/>
@@ -20024,7 +20075,7 @@
       </c>
       <c r="B129">
         <f t="shared" ca="1" si="4"/>
-        <v>57.288285576923066</v>
+        <v>57.275352644230765</v>
       </c>
       <c r="C129">
         <f ca="1"/>
@@ -20065,7 +20116,7 @@
       </c>
       <c r="B130">
         <f t="shared" ref="B130:B193" ca="1" si="8">F130*$C$669/C130</f>
-        <v>56.424898212157331</v>
+        <v>56.412160190703212</v>
       </c>
       <c r="C130">
         <f ca="1"/>
@@ -20106,7 +20157,7 @@
       </c>
       <c r="B131">
         <f t="shared" ca="1" si="8"/>
-        <v>56.121024793388422</v>
+        <v>56.108355371900828</v>
       </c>
       <c r="C131">
         <f ca="1"/>
@@ -20147,7 +20198,7 @@
       </c>
       <c r="B132">
         <f t="shared" ca="1" si="8"/>
-        <v>55.757624299065412</v>
+        <v>55.745036915887859</v>
       </c>
       <c r="C132">
         <f ca="1"/>
@@ -20188,7 +20239,7 @@
       </c>
       <c r="B133">
         <f t="shared" ca="1" si="8"/>
-        <v>55.465908333333324</v>
+        <v>55.453386805555553</v>
       </c>
       <c r="C133">
         <f ca="1"/>
@@ -20229,7 +20280,7 @@
       </c>
       <c r="B134">
         <f t="shared" ca="1" si="8"/>
-        <v>54.660382568807329</v>
+        <v>54.648042889908254</v>
       </c>
       <c r="C134">
         <f ca="1"/>
@@ -20270,7 +20321,7 @@
       </c>
       <c r="B135">
         <f t="shared" ca="1" si="8"/>
-        <v>53.869502727272724</v>
+        <v>53.857341590909094</v>
       </c>
       <c r="C135">
         <f ca="1"/>
@@ -20311,7 +20362,7 @@
       </c>
       <c r="B136">
         <f t="shared" ca="1" si="8"/>
-        <v>53.212721444695262</v>
+        <v>53.200708577878103</v>
       </c>
       <c r="C136">
         <f ca="1"/>
@@ -20352,7 +20403,7 @@
       </c>
       <c r="B137">
         <f t="shared" ca="1" si="8"/>
-        <v>53.434177117845117</v>
+        <v>53.422114257014591</v>
       </c>
       <c r="C137">
         <f ca="1"/>
@@ -20393,7 +20444,7 @@
       </c>
       <c r="B138">
         <f t="shared" ca="1" si="8"/>
-        <v>53.593707678929761</v>
+        <v>53.581608803790417</v>
       </c>
       <c r="C138">
         <f ca="1"/>
@@ -20434,7 +20485,7 @@
       </c>
       <c r="B139">
         <f t="shared" ca="1" si="8"/>
-        <v>53.63197392265193</v>
+        <v>53.619866408839776</v>
       </c>
       <c r="C139">
         <f ca="1"/>
@@ -20475,7 +20526,7 @@
       </c>
       <c r="B140">
         <f t="shared" ca="1" si="8"/>
-        <v>53.352232773770488</v>
+        <v>53.34018841202186</v>
       </c>
       <c r="C140">
         <f ca="1"/>
@@ -20516,7 +20567,7 @@
       </c>
       <c r="B141">
         <f t="shared" ca="1" si="8"/>
-        <v>53.250896108459855</v>
+        <v>53.238874623644243</v>
       </c>
       <c r="C141">
         <f ca="1"/>
@@ -20557,7 +20608,7 @@
       </c>
       <c r="B142">
         <f t="shared" ca="1" si="8"/>
-        <v>53.037253276047259</v>
+        <v>53.025280021482274</v>
       </c>
       <c r="C142">
         <f ca="1"/>
@@ -20598,7 +20649,7 @@
       </c>
       <c r="B143">
         <f t="shared" ca="1" si="8"/>
-        <v>52.970762312633823</v>
+        <v>52.958804068522483</v>
       </c>
       <c r="C143">
         <f ca="1"/>
@@ -20639,7 +20690,7 @@
       </c>
       <c r="B144">
         <f t="shared" ca="1" si="8"/>
-        <v>52.848295522388057</v>
+        <v>52.836364925373132</v>
       </c>
       <c r="C144">
         <f ca="1"/>
@@ -20680,7 +20731,7 @@
       </c>
       <c r="B145">
         <f t="shared" ca="1" si="8"/>
-        <v>52.78290159404888</v>
+        <v>52.770985759829969</v>
       </c>
       <c r="C145">
         <f ca="1"/>
@@ -20721,7 +20772,7 @@
       </c>
       <c r="B146">
         <f t="shared" ca="1" si="8"/>
-        <v>51.98727138559321</v>
+        <v>51.975535166313556</v>
       </c>
       <c r="C146">
         <f ca="1"/>
@@ -20762,7 +20813,7 @@
       </c>
       <c r="B147">
         <f t="shared" ca="1" si="8"/>
-        <v>51.196340667370642</v>
+        <v>51.184783002111928</v>
       </c>
       <c r="C147">
         <f ca="1"/>
@@ -20803,7 +20854,7 @@
       </c>
       <c r="B148">
         <f t="shared" ca="1" si="8"/>
-        <v>50.570441816261877</v>
+        <v>50.55902544878564</v>
       </c>
       <c r="C148">
         <f ca="1"/>
@@ -20844,7 +20895,7 @@
       </c>
       <c r="B149">
         <f t="shared" ca="1" si="8"/>
-        <v>49.684708408421052</v>
+        <v>49.673491996842102</v>
       </c>
       <c r="C149">
         <f ca="1"/>
@@ -20885,7 +20936,7 @@
       </c>
       <c r="B150">
         <f t="shared" ca="1" si="8"/>
-        <v>48.49886779144942</v>
+        <v>48.487919085505737</v>
       </c>
       <c r="C150">
         <f ca="1"/>
@@ -20926,7 +20977,7 @@
       </c>
       <c r="B151">
         <f t="shared" ca="1" si="8"/>
-        <v>47.237813195876285</v>
+        <v>47.227149175257736</v>
       </c>
       <c r="C151">
         <f ca="1"/>
@@ -20967,7 +21018,7 @@
       </c>
       <c r="B152">
         <f t="shared" ca="1" si="8"/>
-        <v>46.321312603076912</v>
+        <v>46.310855484102568</v>
       </c>
       <c r="C152">
         <f ca="1"/>
@@ -21008,7 +21059,7 @@
       </c>
       <c r="B153">
         <f t="shared" ca="1" si="8"/>
-        <v>45.553282919140223</v>
+        <v>45.542999184237452</v>
       </c>
       <c r="C153">
         <f ca="1"/>
@@ -21049,7 +21100,7 @@
       </c>
       <c r="B154">
         <f t="shared" ca="1" si="8"/>
-        <v>44.88040777891505</v>
+        <v>44.870275946775841</v>
       </c>
       <c r="C154">
         <f ca="1"/>
@@ -21090,7 +21141,7 @@
       </c>
       <c r="B155">
         <f t="shared" ca="1" si="8"/>
-        <v>43.686443437308867</v>
+        <v>43.676581144750259</v>
       </c>
       <c r="C155">
         <f ca="1"/>
@@ -21131,7 +21182,7 @@
       </c>
       <c r="B156">
         <f t="shared" ca="1" si="8"/>
-        <v>42.719354069387748</v>
+        <v>42.709710098979585</v>
       </c>
       <c r="C156">
         <f ca="1"/>
@@ -21172,7 +21223,7 @@
       </c>
       <c r="B157">
         <f t="shared" ca="1" si="8"/>
-        <v>41.835424360286588</v>
+        <v>41.825979938587508</v>
       </c>
       <c r="C157">
         <f ca="1"/>
@@ -21213,7 +21264,7 @@
       </c>
       <c r="B158">
         <f t="shared" ca="1" si="8"/>
-        <v>41.507848608784471</v>
+        <v>41.498478137895809</v>
       </c>
       <c r="C158">
         <f ca="1"/>
@@ -21254,7 +21305,7 @@
       </c>
       <c r="B159">
         <f t="shared" ca="1" si="8"/>
-        <v>41.223300624489795</v>
+        <v>41.213994390816325</v>
       </c>
       <c r="C159">
         <f ca="1"/>
@@ -21295,7 +21346,7 @@
       </c>
       <c r="B160">
         <f t="shared" ca="1" si="8"/>
-        <v>40.9396623853211</v>
+        <v>40.930420183486241</v>
       </c>
       <c r="C160">
         <f ca="1"/>
@@ -21336,7 +21387,7 @@
       </c>
       <c r="B161">
         <f t="shared" ca="1" si="8"/>
-        <v>40.835178327935218</v>
+        <v>40.825959713562753</v>
       </c>
       <c r="C161">
         <f ca="1"/>
@@ -21377,7 +21428,7 @@
       </c>
       <c r="B162">
         <f t="shared" ca="1" si="8"/>
-        <v>40.855020374999995</v>
+        <v>40.84579728125</v>
       </c>
       <c r="C162">
         <f ca="1"/>
@@ -21418,7 +21469,7 @@
       </c>
       <c r="B163">
         <f t="shared" ca="1" si="8"/>
-        <v>40.957271227364174</v>
+        <v>40.948025050301808</v>
       </c>
       <c r="C163">
         <f ca="1"/>
@@ -21459,7 +21510,7 @@
       </c>
       <c r="B164">
         <f t="shared" ca="1" si="8"/>
-        <v>41.560050288577152</v>
+        <v>41.550668033066138</v>
       </c>
       <c r="C164">
         <f ca="1"/>
@@ -21500,7 +21551,7 @@
       </c>
       <c r="B165">
         <f t="shared" ca="1" si="8"/>
-        <v>42.1998096023976</v>
+        <v>42.190282920079923</v>
       </c>
       <c r="C165">
         <f ca="1"/>
@@ -21541,7 +21592,7 @@
       </c>
       <c r="B166">
         <f t="shared" ca="1" si="8"/>
-        <v>42.836067729083659</v>
+        <v>42.826397410358567</v>
       </c>
       <c r="C166">
         <f ca="1"/>
@@ -21582,7 +21633,7 @@
       </c>
       <c r="B167">
         <f t="shared" ca="1" si="8"/>
-        <v>43.446583940476188</v>
+        <v>43.436775796626989</v>
       </c>
       <c r="C167">
         <f ca="1"/>
@@ -21623,7 +21674,7 @@
       </c>
       <c r="B168">
         <f t="shared" ca="1" si="8"/>
-        <v>44.096166753709198</v>
+        <v>44.086211965380812</v>
       </c>
       <c r="C168">
         <f ca="1"/>
@@ -21664,7 +21715,7 @@
       </c>
       <c r="B169">
         <f t="shared" ca="1" si="8"/>
-        <v>44.741586982248513</v>
+        <v>44.73148648915187</v>
       </c>
       <c r="C169">
         <f ca="1"/>
@@ -21705,7 +21756,7 @@
       </c>
       <c r="B170">
         <f t="shared" ca="1" si="8"/>
-        <v>45.733361018609209</v>
+        <v>45.723036630754166</v>
       </c>
       <c r="C170">
         <f ca="1"/>
@@ -21746,7 +21797,7 @@
       </c>
       <c r="B171">
         <f t="shared" ca="1" si="8"/>
-        <v>46.802684210526316</v>
+        <v>46.792118421052628</v>
       </c>
       <c r="C171">
         <f ca="1"/>
@@ -21787,7 +21838,7 @@
       </c>
       <c r="B172">
         <f t="shared" ca="1" si="8"/>
-        <v>47.95466122448979</v>
+        <v>47.943835374149657</v>
       </c>
       <c r="C172">
         <f ca="1"/>
@@ -21828,7 +21879,7 @@
       </c>
       <c r="B173">
         <f t="shared" ca="1" si="8"/>
-        <v>48.749705529525649</v>
+        <v>48.738700196515005</v>
       </c>
       <c r="C173">
         <f ca="1"/>
@@ -21869,7 +21920,7 @@
       </c>
       <c r="B174">
         <f t="shared" ca="1" si="8"/>
-        <v>49.634655640579709</v>
+        <v>49.623450528502417</v>
       </c>
       <c r="C174">
         <f ca="1"/>
@@ -21910,7 +21961,7 @@
       </c>
       <c r="B175">
         <f t="shared" ca="1" si="8"/>
-        <v>50.515880424300853</v>
+        <v>50.504476374156219</v>
       </c>
       <c r="C175">
         <f ca="1"/>
@@ -21951,7 +22002,7 @@
       </c>
       <c r="B176">
         <f t="shared" ca="1" si="8"/>
-        <v>50.694529106628245</v>
+        <v>50.683084726224784</v>
       </c>
       <c r="C176">
         <f ca="1"/>
@@ -21992,7 +22043,7 @@
       </c>
       <c r="B177">
         <f t="shared" ca="1" si="8"/>
-        <v>50.920537931034481</v>
+        <v>50.909042528735633</v>
       </c>
       <c r="C177">
         <f ca="1"/>
@@ -22033,7 +22084,7 @@
       </c>
       <c r="B178">
         <f t="shared" ca="1" si="8"/>
-        <v>51.145251575931219</v>
+        <v>51.133705444126072</v>
       </c>
       <c r="C178">
         <f ca="1"/>
@@ -22074,7 +22125,7 @@
       </c>
       <c r="B179">
         <f t="shared" ca="1" si="8"/>
-        <v>51.032746515699337</v>
+        <v>51.021225782112282</v>
       </c>
       <c r="C179">
         <f ca="1"/>
@@ -22115,7 +22166,7 @@
       </c>
       <c r="B180">
         <f t="shared" ca="1" si="8"/>
-        <v>51.017503715099707</v>
+        <v>51.005986422602085</v>
       </c>
       <c r="C180">
         <f ca="1"/>
@@ -22156,7 +22207,7 @@
       </c>
       <c r="B181">
         <f t="shared" ca="1" si="8"/>
-        <v>51.002625213270143</v>
+        <v>50.991111279620853</v>
       </c>
       <c r="C181">
         <f ca="1"/>
@@ -22197,7 +22248,7 @@
       </c>
       <c r="B182">
         <f t="shared" ca="1" si="8"/>
-        <v>50.651284189214756</v>
+        <v>50.639849571428563</v>
       </c>
       <c r="C182">
         <f ca="1"/>
@@ -22238,7 +22289,7 @@
       </c>
       <c r="B183">
         <f t="shared" ca="1" si="8"/>
-        <v>50.111685618062083</v>
+        <v>50.100372815616176</v>
       </c>
       <c r="C183">
         <f ca="1"/>
@@ -22279,7 +22330,7 @@
       </c>
       <c r="B184">
         <f t="shared" ca="1" si="8"/>
-        <v>49.624868539325846</v>
+        <v>49.61366563670412</v>
       </c>
       <c r="C184">
         <f ca="1"/>
@@ -22320,7 +22371,7 @@
       </c>
       <c r="B185">
         <f t="shared" ca="1" si="8"/>
-        <v>48.746367476635506</v>
+        <v>48.735362897196261</v>
       </c>
       <c r="C185">
         <f ca="1"/>
@@ -22361,7 +22412,7 @@
       </c>
       <c r="B186">
         <f t="shared" ca="1" si="8"/>
-        <v>47.871144402985067</v>
+        <v>47.860337406716418</v>
       </c>
       <c r="C186">
         <f ca="1"/>
@@ -22402,7 +22453,7 @@
       </c>
       <c r="B187">
         <f t="shared" ca="1" si="8"/>
-        <v>46.955460837209294</v>
+        <v>46.944860558139531</v>
       </c>
       <c r="C187">
         <f ca="1"/>
@@ -22443,7 +22494,7 @@
       </c>
       <c r="B188">
         <f t="shared" ca="1" si="8"/>
-        <v>46.487853493036205</v>
+        <v>46.477358777158777</v>
       </c>
       <c r="C188">
         <f ca="1"/>
@@ -22484,7 +22535,7 @@
       </c>
       <c r="B189">
         <f t="shared" ca="1" si="8"/>
-        <v>46.022279321594063</v>
+        <v>46.011889709916588</v>
       </c>
       <c r="C189">
         <f ca="1"/>
@@ -22525,7 +22576,7 @@
       </c>
       <c r="B190">
         <f t="shared" ca="1" si="8"/>
-        <v>45.558128769657721</v>
+        <v>45.547843940795559</v>
       </c>
       <c r="C190">
         <f ca="1"/>
@@ -22566,7 +22617,7 @@
       </c>
       <c r="B191">
         <f t="shared" ca="1" si="8"/>
-        <v>44.774141762211983</v>
+        <v>44.764033919815674</v>
       </c>
       <c r="C191">
         <f ca="1"/>
@@ -22607,7 +22658,7 @@
       </c>
       <c r="B192">
         <f t="shared" ca="1" si="8"/>
-        <v>43.955847511926606</v>
+        <v>43.945924400917427</v>
       </c>
       <c r="C192">
         <f ca="1"/>
@@ -22648,7 +22699,7 @@
       </c>
       <c r="B193">
         <f t="shared" ca="1" si="8"/>
-        <v>43.144730958904105</v>
+        <v>43.134990958904105</v>
       </c>
       <c r="C193">
         <f ca="1"/>
@@ -22689,7 +22740,7 @@
       </c>
       <c r="B194">
         <f t="shared" ref="B194:B257" ca="1" si="12">F194*$C$669/C194</f>
-        <v>42.899427843494081</v>
+        <v>42.889743221110095</v>
       </c>
       <c r="C194">
         <f ca="1"/>
@@ -22730,7 +22781,7 @@
       </c>
       <c r="B195">
         <f t="shared" ca="1" si="12"/>
-        <v>42.889208751139471</v>
+        <v>42.879526435733823</v>
       </c>
       <c r="C195">
         <f ca="1"/>
@@ -22771,7 +22822,7 @@
       </c>
       <c r="B196">
         <f t="shared" ca="1" si="12"/>
-        <v>43.036162053162229</v>
+        <v>43.026446562786433</v>
       </c>
       <c r="C196">
         <f ca="1"/>
@@ -22812,7 +22863,7 @@
       </c>
       <c r="B197">
         <f t="shared" ca="1" si="12"/>
-        <v>43.382835521619135</v>
+        <v>43.373041769089234</v>
       </c>
       <c r="C197">
         <f ca="1"/>
@@ -22853,7 +22904,7 @@
       </c>
       <c r="B198">
         <f t="shared" ca="1" si="12"/>
-        <v>43.451518337614672</v>
+        <v>43.441709079816512</v>
       </c>
       <c r="C198">
         <f ca="1"/>
@@ -22894,7 +22945,7 @@
       </c>
       <c r="B199">
         <f t="shared" ca="1" si="12"/>
-        <v>43.479748080438753</v>
+        <v>43.469932449725782</v>
       </c>
       <c r="C199">
         <f ca="1"/>
@@ -22935,7 +22986,7 @@
       </c>
       <c r="B200">
         <f t="shared" ca="1" si="12"/>
-        <v>43.577950126027396</v>
+        <v>43.568112326027396</v>
       </c>
       <c r="C200">
         <f ca="1"/>
@@ -22976,7 +23027,7 @@
       </c>
       <c r="B201">
         <f t="shared" ca="1" si="12"/>
-        <v>43.675677930656938</v>
+        <v>43.66581806843066</v>
       </c>
       <c r="C201">
         <f ca="1"/>
@@ -23017,7 +23068,7 @@
       </c>
       <c r="B202">
         <f t="shared" ca="1" si="12"/>
-        <v>43.654139999999998</v>
+        <v>43.644284999999996</v>
       </c>
       <c r="C202">
         <f ca="1"/>
@@ -23058,7 +23109,7 @@
       </c>
       <c r="B203">
         <f t="shared" ca="1" si="12"/>
-        <v>43.213109063520868</v>
+        <v>43.203353627041736</v>
       </c>
       <c r="C203">
         <f ca="1"/>
@@ -23099,7 +23150,7 @@
       </c>
       <c r="B204">
         <f t="shared" ca="1" si="12"/>
-        <v>42.773383163043476</v>
+        <v>42.763726995471018</v>
       </c>
       <c r="C204">
         <f ca="1"/>
@@ -23140,7 +23191,7 @@
       </c>
       <c r="B205">
         <f t="shared" ca="1" si="12"/>
-        <v>42.259122021660644</v>
+        <v>42.249581949458481</v>
       </c>
       <c r="C205">
         <f ca="1"/>
@@ -23181,7 +23232,7 @@
       </c>
       <c r="B206">
         <f t="shared" ca="1" si="12"/>
-        <v>42.631508606822258</v>
+        <v>42.621884467684019</v>
       </c>
       <c r="C206">
         <f ca="1"/>
@@ -23222,7 +23273,7 @@
       </c>
       <c r="B207">
         <f t="shared" ca="1" si="12"/>
-        <v>43.076539008944543</v>
+        <v>43.066814403398922</v>
       </c>
       <c r="C207">
         <f ca="1"/>
@@ -23263,7 +23314,7 @@
       </c>
       <c r="B208">
         <f t="shared" ca="1" si="12"/>
-        <v>43.518684491978604</v>
+        <v>43.508860071301243</v>
       </c>
       <c r="C208">
         <f ca="1"/>
@@ -23304,7 +23355,7 @@
       </c>
       <c r="B209">
         <f t="shared" ca="1" si="12"/>
-        <v>42.675153338065662</v>
+        <v>42.665519346051461</v>
       </c>
       <c r="C209">
         <f ca="1"/>
@@ -23345,7 +23396,7 @@
       </c>
       <c r="B210">
         <f t="shared" ca="1" si="12"/>
-        <v>41.913411493805306</v>
+        <v>41.903949466371685</v>
       </c>
       <c r="C210">
         <f ca="1"/>
@@ -23386,7 +23437,7 @@
       </c>
       <c r="B211">
         <f t="shared" ca="1" si="12"/>
-        <v>41.082897621145371</v>
+        <v>41.07362308370044</v>
       </c>
       <c r="C211">
         <f ca="1"/>
@@ -23427,7 +23478,7 @@
       </c>
       <c r="B212">
         <f t="shared" ca="1" si="12"/>
-        <v>42.338520210896313</v>
+        <v>42.328962214411249</v>
       </c>
       <c r="C212">
         <f ca="1"/>
@@ -23468,7 +23519,7 @@
       </c>
       <c r="B213">
         <f t="shared" ca="1" si="12"/>
-        <v>43.511271391076114</v>
+        <v>43.50144864391951</v>
       </c>
       <c r="C213">
         <f ca="1"/>
@@ -23509,7 +23560,7 @@
       </c>
       <c r="B214">
         <f t="shared" ca="1" si="12"/>
-        <v>44.712755361813421</v>
+        <v>44.70266137750653</v>
       </c>
       <c r="C214">
         <f ca="1"/>
@@ -23550,7 +23601,7 @@
       </c>
       <c r="B215">
         <f t="shared" ca="1" si="12"/>
-        <v>46.13335772869565</v>
+        <v>46.122943040869565</v>
       </c>
       <c r="C215">
         <f ca="1"/>
@@ -23591,7 +23642,7 @@
       </c>
       <c r="B216">
         <f t="shared" ca="1" si="12"/>
-        <v>47.505085798960131</v>
+        <v>47.494361441074517</v>
       </c>
       <c r="C216">
         <f ca="1"/>
@@ -23632,7 +23683,7 @@
       </c>
       <c r="B217">
         <f t="shared" ca="1" si="12"/>
-        <v>48.952162629757787</v>
+        <v>48.941111591695503</v>
       </c>
       <c r="C217">
         <f ca="1"/>
@@ -23673,7 +23724,7 @@
       </c>
       <c r="B218">
         <f t="shared" ca="1" si="12"/>
-        <v>49.796104665517234</v>
+        <v>49.784863106034479</v>
       </c>
       <c r="C218">
         <f ca="1"/>
@@ -23714,7 +23765,7 @@
       </c>
       <c r="B219">
         <f t="shared" ca="1" si="12"/>
-        <v>50.721674860585196</v>
+        <v>50.710224351979342</v>
       </c>
       <c r="C219">
         <f ca="1"/>
@@ -23755,7 +23806,7 @@
       </c>
       <c r="B220">
         <f t="shared" ca="1" si="12"/>
-        <v>51.599457167381971</v>
+        <v>51.587808497854077</v>
       </c>
       <c r="C220">
         <f ca="1"/>
@@ -23796,7 +23847,7 @@
       </c>
       <c r="B221">
         <f t="shared" ca="1" si="12"/>
-        <v>54.124015177474398</v>
+        <v>54.111796584470994</v>
       </c>
       <c r="C221">
         <f ca="1"/>
@@ -23837,7 +23888,7 @@
       </c>
       <c r="B222">
         <f t="shared" ca="1" si="12"/>
-        <v>56.811064350638297</v>
+        <v>56.798239151489362</v>
       </c>
       <c r="C222">
         <f ca="1"/>
@@ -23878,7 +23929,7 @@
       </c>
       <c r="B223">
         <f t="shared" ca="1" si="12"/>
-        <v>59.383880338983055</v>
+        <v>59.3704743220339</v>
       </c>
       <c r="C223">
         <f ca="1"/>
@@ -23919,7 +23970,7 @@
       </c>
       <c r="B224">
         <f t="shared" ca="1" si="12"/>
-        <v>60.097404060759487</v>
+        <v>60.083836964556959</v>
       </c>
       <c r="C224">
         <f ca="1"/>
@@ -23960,7 +24011,7 @@
       </c>
       <c r="B225">
         <f t="shared" ca="1" si="12"/>
-        <v>60.805203519327726</v>
+        <v>60.791476636134455</v>
       </c>
       <c r="C225">
         <f ca="1"/>
@@ -24001,7 +24052,7 @@
       </c>
       <c r="B226">
         <f t="shared" ca="1" si="12"/>
-        <v>61.506809372384929</v>
+        <v>61.492924100418414</v>
       </c>
       <c r="C226">
         <f ca="1"/>
@@ -24042,7 +24093,7 @@
       </c>
       <c r="B227">
         <f t="shared" ca="1" si="12"/>
-        <v>62.227477741451203</v>
+        <v>62.213429777314424</v>
       </c>
       <c r="C227">
         <f ca="1"/>
@@ -24083,7 +24134,7 @@
       </c>
       <c r="B228">
         <f t="shared" ca="1" si="12"/>
-        <v>62.943622433915202</v>
+        <v>62.929412798836246</v>
       </c>
       <c r="C228">
         <f ca="1"/>
@@ -24124,7 +24175,7 @@
       </c>
       <c r="B229">
         <f t="shared" ca="1" si="12"/>
-        <v>63.627961888980941</v>
+        <v>63.61359776304888</v>
       </c>
       <c r="C229">
         <f ca="1"/>
@@ -24165,7 +24216,7 @@
       </c>
       <c r="B230">
         <f t="shared" ca="1" si="12"/>
-        <v>64.459358415841578</v>
+        <v>64.444806600660058</v>
       </c>
       <c r="C230">
         <f ca="1"/>
@@ -24206,7 +24257,7 @@
       </c>
       <c r="B231">
         <f t="shared" ca="1" si="12"/>
-        <v>65.311018421052623</v>
+        <v>65.296274342105264</v>
       </c>
       <c r="C231">
         <f ca="1"/>
@@ -24247,7 +24298,7 @@
       </c>
       <c r="B232">
         <f t="shared" ca="1" si="12"/>
-        <v>66.048817021276591</v>
+        <v>66.033906382978714</v>
       </c>
       <c r="C232">
         <f ca="1"/>
@@ -24288,7 +24339,7 @@
       </c>
       <c r="B233">
         <f t="shared" ca="1" si="12"/>
-        <v>65.793672614134849</v>
+        <v>65.778819575142165</v>
       </c>
       <c r="C233">
         <f ca="1"/>
@@ -24329,7 +24380,7 @@
       </c>
       <c r="B234">
         <f t="shared" ca="1" si="12"/>
-        <v>65.700924989490701</v>
+        <v>65.686092888439759</v>
       </c>
       <c r="C234">
         <f ca="1"/>
@@ -24370,7 +24421,7 @@
       </c>
       <c r="B235">
         <f t="shared" ca="1" si="12"/>
-        <v>65.715069137792099</v>
+        <v>65.700233843674454</v>
       </c>
       <c r="C235">
         <f ca="1"/>
@@ -24411,7 +24462,7 @@
       </c>
       <c r="B236">
         <f t="shared" ca="1" si="12"/>
-        <v>64.179312771084327</v>
+        <v>64.16482417670683</v>
       </c>
       <c r="C236">
         <f ca="1"/>
@@ -24452,7 +24503,7 @@
       </c>
       <c r="B237">
         <f t="shared" ca="1" si="12"/>
-        <v>62.854689156626499</v>
+        <v>62.840499598393571</v>
       </c>
       <c r="C237">
         <f ca="1"/>
@@ -24493,7 +24544,7 @@
       </c>
       <c r="B238">
         <f t="shared" ca="1" si="12"/>
-        <v>61.382156730769232</v>
+        <v>61.368299599358977</v>
       </c>
       <c r="C238">
         <f ca="1"/>
@@ -24534,7 +24585,7 @@
       </c>
       <c r="B239">
         <f t="shared" ca="1" si="12"/>
-        <v>60.409500947368414</v>
+        <v>60.395863394736836</v>
       </c>
       <c r="C239">
         <f ca="1"/>
@@ -24575,7 +24626,7 @@
       </c>
       <c r="B240">
         <f t="shared" ca="1" si="12"/>
-        <v>59.493068635424933</v>
+        <v>59.479637969023031</v>
       </c>
       <c r="C240">
         <f ca="1"/>
@@ -24616,7 +24667,7 @@
       </c>
       <c r="B241">
         <f t="shared" ca="1" si="12"/>
-        <v>58.553718764845605</v>
+        <v>58.540500158353133</v>
       </c>
       <c r="C241">
         <f ca="1"/>
@@ -24657,7 +24708,7 @@
       </c>
       <c r="B242">
         <f t="shared" ca="1" si="12"/>
-        <v>57.038873411764698</v>
+        <v>57.025996784313719</v>
       </c>
       <c r="C242">
         <f ca="1"/>
@@ -24698,7 +24749,7 @@
       </c>
       <c r="B243">
         <f t="shared" ca="1" si="12"/>
-        <v>55.780289999999994</v>
+        <v>55.767697499999997</v>
       </c>
       <c r="C243">
         <f ca="1"/>
@@ -24739,7 +24790,7 @@
       </c>
       <c r="B244">
         <f t="shared" ca="1" si="12"/>
-        <v>54.48909704510109</v>
+        <v>54.476796034214622</v>
       </c>
       <c r="C244">
         <f ca="1"/>
@@ -24780,7 +24831,7 @@
       </c>
       <c r="B245">
         <f t="shared" ca="1" si="12"/>
-        <v>54.019348496508918</v>
+        <v>54.007153532195495</v>
       </c>
       <c r="C245">
         <f ca="1"/>
@@ -24821,7 +24872,7 @@
       </c>
       <c r="B246">
         <f t="shared" ca="1" si="12"/>
-        <v>53.593512771494964</v>
+        <v>53.581413940356306</v>
       </c>
       <c r="C246">
         <f ca="1"/>
@@ -24862,7 +24913,7 @@
       </c>
       <c r="B247">
         <f t="shared" ca="1" si="12"/>
-        <v>52.923161200923786</v>
+        <v>52.91121370284835</v>
       </c>
       <c r="C247">
         <f ca="1"/>
@@ -24903,7 +24954,7 @@
       </c>
       <c r="B248">
         <f t="shared" ca="1" si="12"/>
-        <v>53.076297931034482</v>
+        <v>53.064315862068973</v>
       </c>
       <c r="C248">
         <f ca="1"/>
@@ -24944,7 +24995,7 @@
       </c>
       <c r="B249">
         <f t="shared" ca="1" si="12"/>
-        <v>53.025798784194521</v>
+        <v>53.013828115501518</v>
       </c>
       <c r="C249">
         <f ca="1"/>
@@ -24985,7 +25036,7 @@
       </c>
       <c r="B250">
         <f t="shared" ca="1" si="12"/>
-        <v>53.056100830188676</v>
+        <v>53.044123320754707</v>
       </c>
       <c r="C250">
         <f ca="1"/>
@@ -25026,7 +25077,7 @@
       </c>
       <c r="B251">
         <f t="shared" ca="1" si="12"/>
-        <v>52.375029526236872</v>
+        <v>52.363205769865061</v>
       </c>
       <c r="C251">
         <f ca="1"/>
@@ -25067,7 +25118,7 @@
       </c>
       <c r="B252">
         <f t="shared" ca="1" si="12"/>
-        <v>51.934870465220641</v>
+        <v>51.923146075542263</v>
       </c>
       <c r="C252">
         <f ca="1"/>
@@ -25108,7 +25159,7 @@
       </c>
       <c r="B253">
         <f t="shared" ca="1" si="12"/>
-        <v>51.420177049180325</v>
+        <v>51.40856885245902</v>
       </c>
       <c r="C253">
         <f ca="1"/>
@@ -25149,7 +25200,7 @@
       </c>
       <c r="B254">
         <f t="shared" ca="1" si="12"/>
-        <v>50.853130075723826</v>
+        <v>50.841649890868602</v>
       </c>
       <c r="C254">
         <f ca="1"/>
@@ -25190,7 +25241,7 @@
       </c>
       <c r="B255">
         <f t="shared" ca="1" si="12"/>
-        <v>50.439746430267057</v>
+        <v>50.428359567507421</v>
       </c>
       <c r="C255">
         <f ca="1"/>
@@ -25231,7 +25282,7 @@
       </c>
       <c r="B256">
         <f t="shared" ca="1" si="12"/>
-        <v>50.231766765578627</v>
+        <v>50.22042685459941</v>
       </c>
       <c r="C256">
         <f ca="1"/>
@@ -25272,7 +25323,7 @@
       </c>
       <c r="B257">
         <f t="shared" ca="1" si="12"/>
-        <v>48.739882614359729</v>
+        <v>48.728879498889711</v>
       </c>
       <c r="C257">
         <f ca="1"/>
@@ -25313,7 +25364,7 @@
       </c>
       <c r="B258">
         <f t="shared" ref="B258:B321" ca="1" si="16">F258*$C$669/C258</f>
-        <v>47.352079194690262</v>
+        <v>47.341389378318581</v>
       </c>
       <c r="C258">
         <f ca="1"/>
@@ -25354,7 +25405,7 @@
       </c>
       <c r="B259">
         <f t="shared" ca="1" si="16"/>
-        <v>46.150700294117641</v>
+        <v>46.140281691176469</v>
       </c>
       <c r="C259">
         <f ca="1"/>
@@ -25395,7 +25446,7 @@
       </c>
       <c r="B260">
         <f t="shared" ca="1" si="16"/>
-        <v>44.729645814977971</v>
+        <v>44.719548017621143</v>
       </c>
       <c r="C260">
         <f ca="1"/>
@@ -25436,7 +25487,7 @@
       </c>
       <c r="B261">
         <f t="shared" ca="1" si="16"/>
-        <v>43.391377159590043</v>
+        <v>43.38158147877013</v>
       </c>
       <c r="C261">
         <f ca="1"/>
@@ -25477,7 +25528,7 @@
       </c>
       <c r="B262">
         <f t="shared" ca="1" si="16"/>
-        <v>42.060923211678826</v>
+        <v>42.05142788321168</v>
       </c>
       <c r="C262">
         <f ca="1"/>
@@ -25518,7 +25569,7 @@
       </c>
       <c r="B263">
         <f t="shared" ca="1" si="16"/>
-        <v>40.546121728862971</v>
+        <v>40.536968369533525</v>
       </c>
       <c r="C263">
         <f ca="1"/>
@@ -25559,7 +25610,7 @@
       </c>
       <c r="B264">
         <f t="shared" ca="1" si="16"/>
-        <v>38.922653547169809</v>
+        <v>38.913866688679242</v>
       </c>
       <c r="C264">
         <f ca="1"/>
@@ -25600,7 +25651,7 @@
       </c>
       <c r="B265">
         <f t="shared" ca="1" si="16"/>
-        <v>37.367026628075251</v>
+        <v>37.358590955137487</v>
       </c>
       <c r="C265">
         <f ca="1"/>
@@ -25641,7 +25692,7 @@
       </c>
       <c r="B266">
         <f t="shared" ca="1" si="16"/>
-        <v>37.51934272451193</v>
+        <v>37.510872665943594</v>
       </c>
       <c r="C266">
         <f ca="1"/>
@@ -25682,7 +25733,7 @@
       </c>
       <c r="B267">
         <f t="shared" ca="1" si="16"/>
-        <v>37.616845463203461</v>
+        <v>37.60835339321789</v>
       </c>
       <c r="C267">
         <f ca="1"/>
@@ -25723,7 +25774,7 @@
       </c>
       <c r="B268">
         <f t="shared" ca="1" si="16"/>
-        <v>37.636686987778582</v>
+        <v>37.62819043853343</v>
       </c>
       <c r="C268">
         <f ca="1"/>
@@ -25764,7 +25815,7 @@
       </c>
       <c r="B269">
         <f t="shared" ca="1" si="16"/>
-        <v>38.236053236728836</v>
+        <v>38.227421379483495</v>
       </c>
       <c r="C269">
         <f ca="1"/>
@@ -25805,7 +25856,7 @@
       </c>
       <c r="B270">
         <f t="shared" ca="1" si="16"/>
-        <v>38.809929697924119</v>
+        <v>38.801168287043666</v>
       </c>
       <c r="C270">
         <f ca="1"/>
@@ -25846,7 +25897,7 @@
       </c>
       <c r="B271">
         <f t="shared" ca="1" si="16"/>
-        <v>39.353006423982869</v>
+        <v>39.344122412562463</v>
       </c>
       <c r="C271">
         <f ca="1"/>
@@ -25887,7 +25938,7 @@
       </c>
       <c r="B272">
         <f t="shared" ca="1" si="16"/>
-        <v>40.000472028469744</v>
+        <v>39.991441850533803</v>
       </c>
       <c r="C272">
         <f ca="1"/>
@@ -25928,7 +25979,7 @@
       </c>
       <c r="B273">
         <f t="shared" ca="1" si="16"/>
-        <v>40.673128124999991</v>
+        <v>40.663946093749999</v>
       </c>
       <c r="C273">
         <f ca="1"/>
@@ -25969,7 +26020,7 @@
       </c>
       <c r="B274">
         <f t="shared" ca="1" si="16"/>
-        <v>41.342923883770375</v>
+        <v>41.333590644932677</v>
       </c>
       <c r="C274">
         <f ca="1"/>
@@ -26010,7 +26061,7 @@
       </c>
       <c r="B275">
         <f t="shared" ca="1" si="16"/>
-        <v>41.966576993648559</v>
+        <v>41.957102964008477</v>
       </c>
       <c r="C275">
         <f ca="1"/>
@@ -26051,7 +26102,7 @@
       </c>
       <c r="B276">
         <f t="shared" ca="1" si="16"/>
-        <v>42.644907529908515</v>
+        <v>42.635280365939479</v>
       </c>
       <c r="C276">
         <f ca="1"/>
@@ -26092,7 +26143,7 @@
       </c>
       <c r="B277">
         <f t="shared" ca="1" si="16"/>
-        <v>43.380314546732251</v>
+        <v>43.370521363316932</v>
       </c>
       <c r="C277">
         <f ca="1"/>
@@ -26133,7 +26184,7 @@
       </c>
       <c r="B278">
         <f t="shared" ca="1" si="16"/>
-        <v>43.794536134453772</v>
+        <v>43.784649439775905</v>
       </c>
       <c r="C278">
         <f ca="1"/>
@@ -26174,7 +26225,7 @@
       </c>
       <c r="B279">
         <f t="shared" ca="1" si="16"/>
-        <v>44.267650314465406</v>
+        <v>44.257656813417192</v>
       </c>
       <c r="C279">
         <f ca="1"/>
@@ -26215,7 +26266,7 @@
       </c>
       <c r="B280">
         <f t="shared" ca="1" si="16"/>
-        <v>44.77000530355896</v>
+        <v>44.759898394975572</v>
       </c>
       <c r="C280">
         <f ca="1"/>
@@ -26256,7 +26307,7 @@
       </c>
       <c r="B281">
         <f t="shared" ca="1" si="16"/>
-        <v>44.232057579972178</v>
+        <v>44.222072114047293</v>
       </c>
       <c r="C281">
         <f ca="1"/>
@@ -26297,7 +26348,7 @@
       </c>
       <c r="B282">
         <f t="shared" ca="1" si="16"/>
-        <v>43.728141470180312</v>
+        <v>43.718269764216373</v>
       </c>
       <c r="C282">
         <f ca="1"/>
@@ -26338,7 +26389,7 @@
       </c>
       <c r="B283">
         <f t="shared" ca="1" si="16"/>
-        <v>43.316882328482315</v>
+        <v>43.307103465003458</v>
       </c>
       <c r="C283">
         <f ca="1"/>
@@ -26379,7 +26430,7 @@
       </c>
       <c r="B284">
         <f t="shared" ca="1" si="16"/>
-        <v>44.062540899653982</v>
+        <v>44.052593702422143</v>
       </c>
       <c r="C284">
         <f ca="1"/>
@@ -26420,7 +26471,7 @@
       </c>
       <c r="B285">
         <f t="shared" ca="1" si="16"/>
-        <v>44.775194751381214</v>
+        <v>44.765086671270716</v>
       </c>
       <c r="C285">
         <f ca="1"/>
@@ -26461,7 +26512,7 @@
       </c>
       <c r="B286">
         <f t="shared" ca="1" si="16"/>
-        <v>45.516270620689653</v>
+        <v>45.50599524137931</v>
       </c>
       <c r="C286">
         <f ca="1"/>
@@ -26502,7 +26553,7 @@
       </c>
       <c r="B287">
         <f t="shared" ca="1" si="16"/>
-        <v>46.416947802197797</v>
+        <v>46.406469093406585</v>
       </c>
       <c r="C287">
         <f ca="1"/>
@@ -26543,7 +26594,7 @@
       </c>
       <c r="B288">
         <f t="shared" ca="1" si="16"/>
-        <v>47.375040821917807</v>
+        <v>47.364345821917809</v>
       </c>
       <c r="C288">
         <f ca="1"/>
@@ -26584,7 +26635,7 @@
       </c>
       <c r="B289">
         <f t="shared" ca="1" si="16"/>
-        <v>48.38303458646616</v>
+        <v>48.372112030075186</v>
       </c>
       <c r="C289">
         <f ca="1"/>
@@ -26625,7 +26676,7 @@
       </c>
       <c r="B290">
         <f t="shared" ca="1" si="16"/>
-        <v>48.972516328092958</v>
+        <v>48.961460695146954</v>
       </c>
       <c r="C290">
         <f ca="1"/>
@@ -26666,7 +26717,7 @@
       </c>
       <c r="B291">
         <f t="shared" ca="1" si="16"/>
-        <v>49.44868180777096</v>
+        <v>49.437518679618265</v>
       </c>
       <c r="C291">
         <f ca="1"/>
@@ -26707,7 +26758,7 @@
       </c>
       <c r="B292">
         <f t="shared" ca="1" si="16"/>
-        <v>49.922477498300474</v>
+        <v>49.911207409925225</v>
       </c>
       <c r="C292">
         <f ca="1"/>
@@ -26748,7 +26799,7 @@
       </c>
       <c r="B293">
         <f t="shared" ca="1" si="16"/>
-        <v>51.711878804347819</v>
+        <v>51.700204755434783</v>
       </c>
       <c r="C293">
         <f ca="1"/>
@@ -26789,7 +26840,7 @@
       </c>
       <c r="B294">
         <f t="shared" ca="1" si="16"/>
-        <v>53.426309694915247</v>
+        <v>53.414248610169494</v>
       </c>
       <c r="C294">
         <f ca="1"/>
@@ -26830,7 +26881,7 @@
       </c>
       <c r="B295">
         <f t="shared" ca="1" si="16"/>
-        <v>55.096503042596339</v>
+        <v>55.084064908722105</v>
       </c>
       <c r="C295">
         <f ca="1"/>
@@ -26871,7 +26922,7 @@
       </c>
       <c r="B296">
         <f t="shared" ca="1" si="16"/>
-        <v>56.457959838274931</v>
+        <v>56.445214353099729</v>
       </c>
       <c r="C296">
         <f ca="1"/>
@@ -26912,7 +26963,7 @@
       </c>
       <c r="B297">
         <f t="shared" ca="1" si="16"/>
-        <v>57.771474362416107</v>
+        <v>57.758432348993288</v>
       </c>
       <c r="C297">
         <f ca="1"/>
@@ -26953,7 +27004,7 @@
       </c>
       <c r="B298">
         <f t="shared" ca="1" si="16"/>
-        <v>59.193155525786999</v>
+        <v>59.179792565304744</v>
       </c>
       <c r="C298">
         <f ca="1"/>
@@ -26994,7 +27045,7 @@
       </c>
       <c r="B299">
         <f t="shared" ca="1" si="16"/>
-        <v>61.512750200803211</v>
+        <v>61.49886358768407</v>
       </c>
       <c r="C299">
         <f ca="1"/>
@@ -27035,7 +27086,7 @@
       </c>
       <c r="B300">
         <f t="shared" ca="1" si="16"/>
-        <v>63.701412817089448</v>
+        <v>63.687032109479297</v>
       </c>
       <c r="C300">
         <f ca="1"/>
@@ -27076,7 +27127,7 @@
       </c>
       <c r="B301">
         <f t="shared" ca="1" si="16"/>
-        <v>65.922307794803459</v>
+        <v>65.907425716189209</v>
       </c>
       <c r="C301">
         <f ca="1"/>
@@ -27117,7 +27168,7 @@
       </c>
       <c r="B302">
         <f t="shared" ca="1" si="16"/>
-        <v>67.143687707641192</v>
+        <v>67.128529900332225</v>
       </c>
       <c r="C302">
         <f ca="1"/>
@@ -27158,7 +27209,7 @@
       </c>
       <c r="B303">
         <f t="shared" ca="1" si="16"/>
-        <v>68.358592445328028</v>
+        <v>68.343160371106691</v>
       </c>
       <c r="C303">
         <f ca="1"/>
@@ -27199,7 +27250,7 @@
       </c>
       <c r="B304">
         <f t="shared" ca="1" si="16"/>
-        <v>69.613083333333321</v>
+        <v>69.597368055555549</v>
       </c>
       <c r="C304">
         <f ca="1"/>
@@ -27240,7 +27291,7 @@
       </c>
       <c r="B305">
         <f t="shared" ca="1" si="16"/>
-        <v>70.67292766007904</v>
+        <v>70.656973120553346</v>
       </c>
       <c r="C305">
         <f ca="1"/>
@@ -27281,7 +27332,7 @@
       </c>
       <c r="B306">
         <f t="shared" ca="1" si="16"/>
-        <v>71.865682453648901</v>
+        <v>71.849458647600258</v>
       </c>
       <c r="C306">
         <f ca="1"/>
@@ -27322,7 +27373,7 @@
       </c>
       <c r="B307">
         <f t="shared" ca="1" si="16"/>
-        <v>73.053953543307074</v>
+        <v>73.037461482939634</v>
       </c>
       <c r="C307">
         <f ca="1"/>
@@ -27363,7 +27414,7 @@
       </c>
       <c r="B308">
         <f t="shared" ca="1" si="16"/>
-        <v>73.487965399737874</v>
+        <v>73.471375360419401</v>
       </c>
       <c r="C308">
         <f ca="1"/>
@@ -27404,7 +27455,7 @@
       </c>
       <c r="B309">
         <f t="shared" ca="1" si="16"/>
-        <v>73.872495225637664</v>
+        <v>73.85581837802485</v>
       </c>
       <c r="C309">
         <f ca="1"/>
@@ -27445,7 +27496,7 @@
       </c>
       <c r="B310">
         <f t="shared" ca="1" si="16"/>
-        <v>74.304020378837365</v>
+        <v>74.287246113651207</v>
       </c>
       <c r="C310">
         <f ca="1"/>
@@ -27486,7 +27537,7 @@
       </c>
       <c r="B311">
         <f t="shared" ca="1" si="16"/>
-        <v>73.253637662540712</v>
+        <v>73.237100523127026</v>
       </c>
       <c r="C311">
         <f ca="1"/>
@@ -27527,7 +27578,7 @@
       </c>
       <c r="B312">
         <f t="shared" ca="1" si="16"/>
-        <v>72.302886003903708</v>
+        <v>72.286563498373468</v>
       </c>
       <c r="C312">
         <f ca="1"/>
@@ -27568,7 +27619,7 @@
       </c>
       <c r="B313">
         <f t="shared" ca="1" si="16"/>
-        <v>71.354395321637412</v>
+        <v>71.338286939571148</v>
       </c>
       <c r="C313">
         <f ca="1"/>
@@ -27609,7 +27660,7 @@
       </c>
       <c r="B314">
         <f t="shared" ca="1" si="16"/>
-        <v>71.04121046412412</v>
+        <v>71.02517278409826</v>
       </c>
       <c r="C314">
         <f ca="1"/>
@@ -27650,7 +27701,7 @@
       </c>
       <c r="B315">
         <f t="shared" ca="1" si="16"/>
-        <v>70.959204781935483</v>
+        <v>70.943185614838711</v>
       </c>
       <c r="C315">
         <f ca="1"/>
@@ -27691,7 +27742,7 @@
       </c>
       <c r="B316">
         <f t="shared" ca="1" si="16"/>
-        <v>70.786563086816713</v>
+        <v>70.770582893890676</v>
       </c>
       <c r="C316">
         <f ca="1"/>
@@ -27732,7 +27783,7 @@
       </c>
       <c r="B317">
         <f t="shared" ca="1" si="16"/>
-        <v>71.115221780909664</v>
+        <v>71.099167392696984</v>
       </c>
       <c r="C317">
         <f ca="1"/>
@@ -27773,7 +27824,7 @@
       </c>
       <c r="B318">
         <f t="shared" ca="1" si="16"/>
-        <v>71.57839948849103</v>
+        <v>71.562240537084392</v>
       </c>
       <c r="C318">
         <f ca="1"/>
@@ -27814,7 +27865,7 @@
       </c>
       <c r="B319">
         <f t="shared" ca="1" si="16"/>
-        <v>72.039803701340134</v>
+        <v>72.023540587109125</v>
       </c>
       <c r="C319">
         <f ca="1"/>
@@ -27855,7 +27906,7 @@
       </c>
       <c r="B320">
         <f t="shared" ca="1" si="16"/>
-        <v>72.650416440764332</v>
+        <v>72.63401547961783</v>
       </c>
       <c r="C320">
         <f ca="1"/>
@@ -27896,7 +27947,7 @@
       </c>
       <c r="B321">
         <f t="shared" ca="1" si="16"/>
-        <v>73.305508007633577</v>
+        <v>73.288959158396949</v>
       </c>
       <c r="C321">
         <f ca="1"/>
@@ -27937,7 +27988,7 @@
       </c>
       <c r="B322">
         <f t="shared" ref="B322:B385" ca="1" si="20">F322*$C$669/C322</f>
-        <v>73.818034242232088</v>
+        <v>73.801369689283462</v>
       </c>
       <c r="C322">
         <f ca="1"/>
@@ -27978,7 +28029,7 @@
       </c>
       <c r="B323">
         <f t="shared" ca="1" si="20"/>
-        <v>75.444786599241453</v>
+        <v>75.42775480404552</v>
       </c>
       <c r="C323">
         <f ca="1"/>
@@ -28019,7 +28070,7 @@
       </c>
       <c r="B324">
         <f t="shared" ca="1" si="20"/>
-        <v>77.061288468809067</v>
+        <v>77.043891745431637</v>
       </c>
       <c r="C324">
         <f ca="1"/>
@@ -28060,7 +28111,7 @@
       </c>
       <c r="B325">
         <f t="shared" ca="1" si="20"/>
-        <v>78.717081835323697</v>
+        <v>78.699311313639214</v>
       </c>
       <c r="C325">
         <f ca="1"/>
@@ -28101,7 +28152,7 @@
       </c>
       <c r="B326">
         <f t="shared" ca="1" si="20"/>
-        <v>79.58994241656211</v>
+        <v>79.571974845043911</v>
       </c>
       <c r="C326">
         <f ca="1"/>
@@ -28142,7 +28193,7 @@
       </c>
       <c r="B327">
         <f t="shared" ca="1" si="20"/>
-        <v>80.459726103944888</v>
+        <v>80.441562177207274</v>
       </c>
       <c r="C327">
         <f ca="1"/>
@@ -28183,7 +28234,7 @@
       </c>
       <c r="B328">
         <f t="shared" ca="1" si="20"/>
-        <v>81.427830788485593</v>
+        <v>81.409448310387972</v>
       </c>
       <c r="C328">
         <f ca="1"/>
@@ -28224,7 +28275,7 @@
       </c>
       <c r="B329">
         <f t="shared" ca="1" si="20"/>
-        <v>81.585809013133186</v>
+        <v>81.567390871169479</v>
       </c>
       <c r="C329">
         <f ca="1"/>
@@ -28265,7 +28316,7 @@
       </c>
       <c r="B330">
         <f t="shared" ca="1" si="20"/>
-        <v>81.79491368855534</v>
+        <v>81.776448340838016</v>
       </c>
       <c r="C330">
         <f ca="1"/>
@@ -28306,7 +28357,7 @@
       </c>
       <c r="B331">
         <f t="shared" ca="1" si="20"/>
-        <v>81.850250936329587</v>
+        <v>81.831773096129837</v>
       </c>
       <c r="C331">
         <f ca="1"/>
@@ -28347,7 +28398,7 @@
       </c>
       <c r="B332">
         <f t="shared" ca="1" si="20"/>
-        <v>81.808672817955099</v>
+        <v>81.790204364089774</v>
       </c>
       <c r="C332">
         <f ca="1"/>
@@ -28388,7 +28439,7 @@
       </c>
       <c r="B333">
         <f t="shared" ca="1" si="20"/>
-        <v>81.665497761194018</v>
+        <v>81.647061629353232</v>
       </c>
       <c r="C333">
         <f ca="1"/>
@@ -28429,7 +28480,7 @@
       </c>
       <c r="B334">
         <f t="shared" ca="1" si="20"/>
-        <v>81.523033250620358</v>
+        <v>81.504629280397026</v>
       </c>
       <c r="C334">
         <f ca="1"/>
@@ -28470,7 +28521,7 @@
       </c>
       <c r="B335">
         <f t="shared" ca="1" si="20"/>
-        <v>80.75750601362229</v>
+        <v>80.739274862538693</v>
       </c>
       <c r="C335">
         <f ca="1"/>
@@ -28511,7 +28562,7 @@
       </c>
       <c r="B336">
         <f t="shared" ca="1" si="20"/>
-        <v>80.044488675324672</v>
+        <v>80.026418489177502</v>
       </c>
       <c r="C336">
         <f ca="1"/>
@@ -28552,7 +28603,7 @@
       </c>
       <c r="B337">
         <f t="shared" ca="1" si="20"/>
-        <v>79.382064771322604</v>
+        <v>79.364144128553761</v>
       </c>
       <c r="C337">
         <f ca="1"/>
@@ -28593,7 +28644,7 @@
       </c>
       <c r="B338">
         <f t="shared" ca="1" si="20"/>
-        <v>79.164297777777762</v>
+        <v>79.146426296296283</v>
       </c>
       <c r="C338">
         <f ca="1"/>
@@ -28634,7 +28685,7 @@
       </c>
       <c r="B339">
         <f t="shared" ca="1" si="20"/>
-        <v>79.044533333333334</v>
+        <v>79.026688888888884</v>
       </c>
       <c r="C339">
         <f ca="1"/>
@@ -28675,7 +28726,7 @@
       </c>
       <c r="B340">
         <f t="shared" ca="1" si="20"/>
-        <v>78.924768888888877</v>
+        <v>78.906951481481485</v>
       </c>
       <c r="C340">
         <f ca="1"/>
@@ -28716,7 +28767,7 @@
       </c>
       <c r="B341">
         <f t="shared" ca="1" si="20"/>
-        <v>78.448664611590644</v>
+        <v>78.430954685573369</v>
       </c>
       <c r="C341">
         <f ca="1"/>
@@ -28757,7 +28808,7 @@
       </c>
       <c r="B342">
         <f t="shared" ca="1" si="20"/>
-        <v>77.877824354243543</v>
+        <v>77.860243296432969</v>
       </c>
       <c r="C342">
         <f ca="1"/>
@@ -28798,7 +28849,7 @@
       </c>
       <c r="B343">
         <f t="shared" ca="1" si="20"/>
-        <v>77.404760933660924</v>
+        <v>77.387286670761668</v>
       </c>
       <c r="C343">
         <f ca="1"/>
@@ -28839,7 +28890,7 @@
       </c>
       <c r="B344">
         <f t="shared" ca="1" si="20"/>
-        <v>76.633899624999998</v>
+        <v>76.616599385416663</v>
       </c>
       <c r="C344">
         <f ca="1"/>
@@ -28880,7 +28931,7 @@
       </c>
       <c r="B345">
         <f t="shared" ca="1" si="20"/>
-        <v>75.959470141982848</v>
+        <v>75.942322156058736</v>
       </c>
       <c r="C345">
         <f ca="1"/>
@@ -28921,7 +28972,7 @@
       </c>
       <c r="B346">
         <f t="shared" ca="1" si="20"/>
-        <v>75.332934311926607</v>
+        <v>75.3159277675841</v>
       </c>
       <c r="C346">
         <f ca="1"/>
@@ -28962,7 +29013,7 @@
       </c>
       <c r="B347">
         <f t="shared" ca="1" si="20"/>
-        <v>74.899112514948115</v>
+        <v>74.882203906650389</v>
       </c>
       <c r="C347">
         <f ca="1"/>
@@ -29003,7 +29054,7 @@
       </c>
       <c r="B348">
         <f t="shared" ca="1" si="20"/>
-        <v>74.558358676416816</v>
+        <v>74.54152699390616</v>
       </c>
       <c r="C348">
         <f ca="1"/>
@@ -29044,7 +29095,7 @@
       </c>
       <c r="B349">
         <f t="shared" ca="1" si="20"/>
-        <v>74.17309270072991</v>
+        <v>74.156347992700731</v>
       </c>
       <c r="C349">
         <f ca="1"/>
@@ -29085,7 +29136,7 @@
       </c>
       <c r="B350">
         <f t="shared" ca="1" si="20"/>
-        <v>74.476462186520934</v>
+        <v>74.459648992289019</v>
       </c>
       <c r="C350">
         <f ca="1"/>
@@ -29126,7 +29177,7 @@
       </c>
       <c r="B351">
         <f t="shared" ca="1" si="20"/>
-        <v>74.914957121311474</v>
+        <v>74.898044936065574</v>
       </c>
       <c r="C351">
         <f ca="1"/>
@@ -29167,7 +29218,7 @@
       </c>
       <c r="B352">
         <f t="shared" ca="1" si="20"/>
-        <v>75.307708252427176</v>
+        <v>75.290707402912616</v>
       </c>
       <c r="C352">
         <f ca="1"/>
@@ -29208,7 +29259,7 @@
       </c>
       <c r="B353">
         <f t="shared" ca="1" si="20"/>
-        <v>76.523632549728745</v>
+        <v>76.506357203134399</v>
       </c>
       <c r="C353">
         <f ca="1"/>
@@ -29249,7 +29300,7 @@
       </c>
       <c r="B354">
         <f t="shared" ca="1" si="20"/>
-        <v>78.191752771084339</v>
+        <v>78.174100843373495</v>
       </c>
       <c r="C354">
         <f ca="1"/>
@@ -29290,7 +29341,7 @@
       </c>
       <c r="B355">
         <f t="shared" ca="1" si="20"/>
-        <v>79.905971566265066</v>
+        <v>79.887932650602423</v>
       </c>
       <c r="C355">
         <f ca="1"/>
@@ -29331,7 +29382,7 @@
       </c>
       <c r="B356">
         <f t="shared" ca="1" si="20"/>
-        <v>81.471433713257341</v>
+        <v>81.453041391721655</v>
       </c>
       <c r="C356">
         <f ca="1"/>
@@ -29372,7 +29423,7 @@
       </c>
       <c r="B357">
         <f t="shared" ca="1" si="20"/>
-        <v>83.172858886894062</v>
+        <v>83.154082465589468</v>
       </c>
       <c r="C357">
         <f ca="1"/>
@@ -29413,7 +29464,7 @@
       </c>
       <c r="B358">
         <f t="shared" ca="1" si="20"/>
-        <v>84.714430512514895</v>
+        <v>84.69530607866507</v>
       </c>
       <c r="C358">
         <f ca="1"/>
@@ -29454,7 +29505,7 @@
       </c>
       <c r="B359">
         <f t="shared" ca="1" si="20"/>
-        <v>87.262747424866149</v>
+        <v>87.243047703926237</v>
       </c>
       <c r="C359">
         <f ca="1"/>
@@ -29495,7 +29546,7 @@
       </c>
       <c r="B360">
         <f t="shared" ca="1" si="20"/>
-        <v>89.80200402541567</v>
+        <v>89.781731062767221</v>
       </c>
       <c r="C360">
         <f ca="1"/>
@@ -29536,7 +29587,7 @@
       </c>
       <c r="B361">
         <f t="shared" ca="1" si="20"/>
-        <v>92.27751113744074</v>
+        <v>92.256679324644551</v>
       </c>
       <c r="C361">
         <f ca="1"/>
@@ -29577,7 +29628,7 @@
       </c>
       <c r="B362">
         <f t="shared" ca="1" si="20"/>
-        <v>93.774929698050784</v>
+        <v>93.753759840342582</v>
       </c>
       <c r="C362">
         <f ca="1"/>
@@ -29618,7 +29669,7 @@
       </c>
       <c r="B363">
         <f t="shared" ca="1" si="20"/>
-        <v>95.151435777176474</v>
+        <v>95.129955170764703</v>
       </c>
       <c r="C363">
         <f ca="1"/>
@@ -29659,7 +29710,7 @@
       </c>
       <c r="B364">
         <f t="shared" ca="1" si="20"/>
-        <v>96.347343859649115</v>
+        <v>96.325593274853802</v>
       </c>
       <c r="C364">
         <f ca="1"/>
@@ -29700,7 +29751,7 @@
       </c>
       <c r="B365">
         <f t="shared" ca="1" si="20"/>
-        <v>97.015500773083659</v>
+        <v>96.993599350672909</v>
       </c>
       <c r="C365">
         <f ca="1"/>
@@ -29741,7 +29792,7 @@
       </c>
       <c r="B366">
         <f t="shared" ca="1" si="20"/>
-        <v>97.456224286682257</v>
+        <v>97.434223370151884</v>
       </c>
       <c r="C366">
         <f ca="1"/>
@@ -29782,7 +29833,7 @@
       </c>
       <c r="B367">
         <f t="shared" ca="1" si="20"/>
-        <v>97.49743832752614</v>
+        <v>97.475428106852505</v>
       </c>
       <c r="C367">
         <f ca="1"/>
@@ -29823,7 +29874,7 @@
       </c>
       <c r="B368">
         <f t="shared" ca="1" si="20"/>
-        <v>98.326117209727869</v>
+        <v>98.303919913317912</v>
       </c>
       <c r="C368">
         <f ca="1"/>
@@ -29864,7 +29915,7 @@
       </c>
       <c r="B369">
         <f t="shared" ca="1" si="20"/>
-        <v>99.437088812275618</v>
+        <v>99.414640712044019</v>
       </c>
       <c r="C369">
         <f ca="1"/>
@@ -29905,7 +29956,7 @@
       </c>
       <c r="B370">
         <f t="shared" ca="1" si="20"/>
-        <v>100.02676728110599</v>
+        <v>100.00418605990784</v>
       </c>
       <c r="C370">
         <f ca="1"/>
@@ -29946,7 +29997,7 @@
       </c>
       <c r="B371">
         <f t="shared" ca="1" si="20"/>
-        <v>97.560852661759625</v>
+        <v>97.538828125186882</v>
       </c>
       <c r="C371">
         <f ca="1"/>
@@ -29987,7 +30038,7 @@
       </c>
       <c r="B372">
         <f t="shared" ca="1" si="20"/>
-        <v>95.103412870952937</v>
+        <v>95.081943105797947</v>
       </c>
       <c r="C372">
         <f ca="1"/>
@@ -30028,7 +30079,7 @@
       </c>
       <c r="B373">
         <f t="shared" ca="1" si="20"/>
-        <v>92.601374570446737</v>
+        <v>92.580469644902635</v>
       </c>
       <c r="C373">
         <f ca="1"/>
@@ -30069,7 +30120,7 @@
       </c>
       <c r="B374">
         <f t="shared" ca="1" si="20"/>
-        <v>89.274981321184498</v>
+        <v>89.254827334851925</v>
       </c>
       <c r="C374">
         <f ca="1"/>
@@ -30110,7 +30161,7 @@
       </c>
       <c r="B375">
         <f t="shared" ca="1" si="20"/>
-        <v>86.279394545454537</v>
+        <v>86.259916818181821</v>
       </c>
       <c r="C375">
         <f ca="1"/>
@@ -30151,7 +30202,7 @@
       </c>
       <c r="B376">
         <f t="shared" ca="1" si="20"/>
-        <v>83.439296763202719</v>
+        <v>83.420460193072117</v>
       </c>
       <c r="C376">
         <f ca="1"/>
@@ -30192,7 +30243,7 @@
       </c>
       <c r="B377">
         <f t="shared" ca="1" si="20"/>
-        <v>78.011876631972768</v>
+        <v>77.994265311621305</v>
       </c>
       <c r="C377">
         <f ca="1"/>
@@ -30233,7 +30284,7 @@
       </c>
       <c r="B378">
         <f t="shared" ca="1" si="20"/>
-        <v>72.35717248798646</v>
+        <v>72.340837727185558</v>
       </c>
       <c r="C378">
         <f ca="1"/>
@@ -30274,7 +30325,7 @@
       </c>
       <c r="B379">
         <f t="shared" ca="1" si="20"/>
-        <v>66.947448283624084</v>
+        <v>66.932334777715255</v>
       </c>
       <c r="C379">
         <f ca="1"/>
@@ -30315,7 +30366,7 @@
       </c>
       <c r="B380">
         <f t="shared" ca="1" si="20"/>
-        <v>61.90822007959413</v>
+        <v>61.894244188444191</v>
       </c>
       <c r="C380">
         <f ca="1"/>
@@ -30356,7 +30407,7 @@
       </c>
       <c r="B381">
         <f t="shared" ca="1" si="20"/>
-        <v>56.755795703945878</v>
+        <v>56.742982981792551</v>
       </c>
       <c r="C381">
         <f ca="1"/>
@@ -30397,7 +30448,7 @@
       </c>
       <c r="B382">
         <f t="shared" ca="1" si="20"/>
-        <v>51.400532509825929</v>
+        <v>51.388928747894433</v>
       </c>
       <c r="C382">
         <f ca="1"/>
@@ -30438,7 +30489,7 @@
       </c>
       <c r="B383">
         <f t="shared" ca="1" si="20"/>
-        <v>49.348204966891892</v>
+        <v>49.337064521565317</v>
       </c>
       <c r="C383">
         <f ca="1"/>
@@ -30479,7 +30530,7 @@
       </c>
       <c r="B384">
         <f t="shared" ca="1" si="20"/>
-        <v>47.177750973971833</v>
+        <v>47.167100512507041</v>
       </c>
       <c r="C384">
         <f ca="1"/>
@@ -30520,7 +30571,7 @@
       </c>
       <c r="B385">
         <f t="shared" ca="1" si="20"/>
-        <v>45.004831792559187</v>
+        <v>44.994671871476889</v>
       </c>
       <c r="C385">
         <f ca="1"/>
@@ -30561,7 +30612,7 @@
       </c>
       <c r="B386">
         <f t="shared" ref="B386:B449" ca="1" si="24">F386*$C$669/C386</f>
-        <v>44.934912561170513</v>
+        <v>44.92476842447946</v>
       </c>
       <c r="C386">
         <f ca="1"/>
@@ -30602,7 +30653,7 @@
       </c>
       <c r="B387">
         <f t="shared" ca="1" si="24"/>
-        <v>44.865247179101125</v>
+        <v>44.855118769494382</v>
       </c>
       <c r="C387">
         <f ca="1"/>
@@ -30643,7 +30694,7 @@
       </c>
       <c r="B388">
         <f t="shared" ca="1" si="24"/>
-        <v>44.745606722689068</v>
+        <v>44.735505322128851</v>
       </c>
       <c r="C388">
         <f ca="1"/>
@@ -30684,7 +30735,7 @@
       </c>
       <c r="B389">
         <f t="shared" ca="1" si="24"/>
-        <v>45.772327495817052</v>
+        <v>45.761994311210259</v>
       </c>
       <c r="C389">
         <f ca="1"/>
@@ -30725,7 +30776,7 @@
       </c>
       <c r="B390">
         <f t="shared" ca="1" si="24"/>
-        <v>46.946327799442891</v>
+        <v>46.935729582172698</v>
       </c>
       <c r="C390">
         <f ca="1"/>
@@ -30766,7 +30817,7 @@
       </c>
       <c r="B391">
         <f t="shared" ca="1" si="24"/>
-        <v>48.144506458797323</v>
+        <v>48.133637750556794</v>
       </c>
       <c r="C391">
         <f ca="1"/>
@@ -30807,7 +30858,7 @@
       </c>
       <c r="B392">
         <f t="shared" ca="1" si="24"/>
-        <v>50.013631999999994</v>
+        <v>50.002341333333334</v>
       </c>
       <c r="C392">
         <f ca="1"/>
@@ -30848,7 +30899,7 @@
       </c>
       <c r="B393">
         <f t="shared" ca="1" si="24"/>
-        <v>51.845729418282552</v>
+        <v>51.83402515235457</v>
       </c>
       <c r="C393">
         <f ca="1"/>
@@ -30889,7 +30940,7 @@
       </c>
       <c r="B394">
         <f t="shared" ca="1" si="24"/>
-        <v>53.727071681415921</v>
+        <v>53.714942699115042</v>
       </c>
       <c r="C394">
         <f ca="1"/>
@@ -30930,7 +30981,7 @@
       </c>
       <c r="B395">
         <f t="shared" ca="1" si="24"/>
-        <v>52.151064470860931</v>
+        <v>52.139291274999998</v>
       </c>
       <c r="C395">
         <f ca="1"/>
@@ -30971,7 +31022,7 @@
       </c>
       <c r="B396">
         <f t="shared" ca="1" si="24"/>
-        <v>50.609886710082634</v>
+        <v>50.598461437851242</v>
       </c>
       <c r="C396">
         <f ca="1"/>
@@ -31012,7 +31063,7 @@
       </c>
       <c r="B397">
         <f t="shared" ca="1" si="24"/>
-        <v>49.073777557755776</v>
+        <v>49.062699064906489</v>
       </c>
       <c r="C397">
         <f ca="1"/>
@@ -31053,7 +31104,7 @@
       </c>
       <c r="B398">
         <f t="shared" ca="1" si="24"/>
-        <v>50.470284775465501</v>
+        <v>50.458891018619937</v>
       </c>
       <c r="C398">
         <f ca="1"/>
@@ -31094,7 +31145,7 @@
       </c>
       <c r="B399">
         <f t="shared" ca="1" si="24"/>
-        <v>51.798122222222219</v>
+        <v>51.786428703703706</v>
       </c>
       <c r="C399">
         <f ca="1"/>
@@ -31135,7 +31186,7 @@
       </c>
       <c r="B400">
         <f t="shared" ca="1" si="24"/>
-        <v>53.313738336052197</v>
+        <v>53.301702664491572</v>
       </c>
       <c r="C400">
         <f ca="1"/>
@@ -31176,7 +31227,7 @@
       </c>
       <c r="B401">
         <f t="shared" ca="1" si="24"/>
-        <v>56.006221179039308</v>
+        <v>55.993577674672487</v>
       </c>
       <c r="C401">
         <f ca="1"/>
@@ -31217,7 +31268,7 @@
       </c>
       <c r="B402">
         <f t="shared" ca="1" si="24"/>
-        <v>58.59094018589392</v>
+        <v>58.577713176599239</v>
       </c>
       <c r="C402">
         <f ca="1"/>
@@ -31258,7 +31309,7 @@
       </c>
       <c r="B403">
         <f t="shared" ca="1" si="24"/>
-        <v>61.017073730202071</v>
+        <v>61.003299016930633</v>
       </c>
       <c r="C403">
         <f ca="1"/>
@@ -31299,7 +31350,7 @@
       </c>
       <c r="B404">
         <f t="shared" ca="1" si="24"/>
-        <v>63.182421132934131</v>
+        <v>63.168157588622755</v>
       </c>
       <c r="C404">
         <f ca="1"/>
@@ -31340,7 +31391,7 @@
       </c>
       <c r="B405">
         <f t="shared" ca="1" si="24"/>
-        <v>65.262864812357719</v>
+        <v>65.248131604173437</v>
       </c>
       <c r="C405">
         <f ca="1"/>
@@ -31381,7 +31432,7 @@
       </c>
       <c r="B406">
         <f t="shared" ca="1" si="24"/>
-        <v>67.398071961102104</v>
+        <v>67.382856726094005</v>
       </c>
       <c r="C406">
         <f ca="1"/>
@@ -31422,7 +31473,7 @@
       </c>
       <c r="B407">
         <f t="shared" ca="1" si="24"/>
-        <v>73.393781924716052</v>
+        <v>73.377213147485122</v>
       </c>
       <c r="C407">
         <f ca="1"/>
@@ -31463,7 +31514,7 @@
       </c>
       <c r="B408">
         <f t="shared" ca="1" si="24"/>
-        <v>79.273698389837833</v>
+        <v>79.255802210972973</v>
       </c>
       <c r="C408">
         <f ca="1"/>
@@ -31504,7 +31555,7 @@
       </c>
       <c r="B409">
         <f t="shared" ca="1" si="24"/>
-        <v>84.963673099730457</v>
+        <v>84.944492398921838</v>
       </c>
       <c r="C409">
         <f ca="1"/>
@@ -31545,7 +31596,7 @@
       </c>
       <c r="B410">
         <f t="shared" ca="1" si="24"/>
-        <v>86.484977551690818</v>
+        <v>86.465453413687598</v>
       </c>
       <c r="C410">
         <f ca="1"/>
@@ -31586,7 +31637,7 @@
       </c>
       <c r="B411">
         <f t="shared" ca="1" si="24"/>
-        <v>88.1817784794858</v>
+        <v>88.161871285645432</v>
       </c>
       <c r="C411">
         <f ca="1"/>
@@ -31627,7 +31678,7 @@
       </c>
       <c r="B412">
         <f t="shared" ca="1" si="24"/>
-        <v>89.871341528594343</v>
+        <v>89.851052912880817</v>
       </c>
       <c r="C412">
         <f ca="1"/>
@@ -31668,7 +31719,7 @@
       </c>
       <c r="B413">
         <f t="shared" ca="1" si="24"/>
-        <v>92.114445689007468</v>
+        <v>92.093650688527219</v>
       </c>
       <c r="C413">
         <f ca="1"/>
@@ -31709,7 +31760,7 @@
       </c>
       <c r="B414">
         <f t="shared" ca="1" si="24"/>
-        <v>94.0997315509033</v>
+        <v>94.078488368597235</v>
       </c>
       <c r="C414">
         <f ca="1"/>
@@ -31750,7 +31801,7 @@
       </c>
       <c r="B415">
         <f t="shared" ca="1" si="24"/>
-        <v>96.119050291159326</v>
+        <v>96.097351244044461</v>
       </c>
       <c r="C415">
         <f ca="1"/>
@@ -31791,7 +31842,7 @@
       </c>
       <c r="B416">
         <f t="shared" ca="1" si="24"/>
-        <v>96.940799365415117</v>
+        <v>96.918914806980439</v>
       </c>
       <c r="C416">
         <f ca="1"/>
@@ -31832,7 +31883,7 @@
       </c>
       <c r="B417">
         <f t="shared" ca="1" si="24"/>
-        <v>97.812482663847788</v>
+        <v>97.790401321353059</v>
       </c>
       <c r="C417">
         <f ca="1"/>
@@ -31873,7 +31924,7 @@
       </c>
       <c r="B418">
         <f t="shared" ca="1" si="24"/>
-        <v>98.423278609062166</v>
+        <v>98.401059378292942</v>
       </c>
       <c r="C418">
         <f ca="1"/>
@@ -31914,7 +31965,7 @@
       </c>
       <c r="B419">
         <f t="shared" ca="1" si="24"/>
-        <v>98.34807610062893</v>
+        <v>98.325873846960164</v>
       </c>
       <c r="C419">
         <f ca="1"/>
@@ -31955,7 +32006,7 @@
       </c>
       <c r="B420">
         <f t="shared" ca="1" si="24"/>
-        <v>98.324922065727705</v>
+        <v>98.302725039123629</v>
       </c>
       <c r="C420">
         <f ca="1"/>
@@ -31996,7 +32047,7 @@
       </c>
       <c r="B421">
         <f t="shared" ca="1" si="24"/>
-        <v>98.763496087636923</v>
+        <v>98.741200052164857</v>
       </c>
       <c r="C421">
         <f ca="1"/>
@@ -32037,7 +32088,7 @@
       </c>
       <c r="B422">
         <f t="shared" ca="1" si="24"/>
-        <v>99.754536732150314</v>
+        <v>99.732016967484341</v>
       </c>
       <c r="C422">
         <f ca="1"/>
@@ -32078,7 +32129,7 @@
       </c>
       <c r="B423">
         <f t="shared" ca="1" si="24"/>
-        <v>100.27532766174636</v>
+        <v>100.25269032759874</v>
       </c>
       <c r="C423">
         <f ca="1"/>
@@ -32119,7 +32170,7 @@
       </c>
       <c r="B424">
         <f t="shared" ca="1" si="24"/>
-        <v>100.84401905748317</v>
+        <v>100.82125334023821</v>
       </c>
       <c r="C424">
         <f ca="1"/>
@@ -32160,7 +32211,7 @@
       </c>
       <c r="B425">
         <f t="shared" ca="1" si="24"/>
-        <v>102.22330677398038</v>
+        <v>102.2002296800723</v>
       </c>
       <c r="C425">
         <f ca="1"/>
@@ -32201,7 +32252,7 @@
       </c>
       <c r="B426">
         <f t="shared" ca="1" si="24"/>
-        <v>103.96865804690081</v>
+        <v>103.94518693682852</v>
       </c>
       <c r="C426">
         <f ca="1"/>
@@ -32242,7 +32293,7 @@
       </c>
       <c r="B427">
         <f t="shared" ca="1" si="24"/>
-        <v>105.60664243675788</v>
+        <v>105.58280154878679</v>
       </c>
       <c r="C427">
         <f ca="1"/>
@@ -32283,7 +32334,7 @@
       </c>
       <c r="B428">
         <f t="shared" ca="1" si="24"/>
-        <v>106.7316886608517</v>
+        <v>106.70759379168804</v>
       </c>
       <c r="C428">
         <f ca="1"/>
@@ -32324,7 +32375,7 @@
       </c>
       <c r="B429">
         <f t="shared" ca="1" si="24"/>
-        <v>107.84296583375829</v>
+        <v>107.81862009178991</v>
       </c>
       <c r="C429">
         <f ca="1"/>
@@ -32365,7 +32416,7 @@
       </c>
       <c r="B430">
         <f t="shared" ca="1" si="24"/>
-        <v>108.11873782696176</v>
+        <v>108.09432982897384</v>
       </c>
       <c r="C430">
         <f ca="1"/>
@@ -32406,7 +32457,7 @@
       </c>
       <c r="B431">
         <f t="shared" ca="1" si="24"/>
-        <v>109.77485062782522</v>
+        <v>109.75006875941739</v>
       </c>
       <c r="C431">
         <f ca="1"/>
@@ -32447,7 +32498,7 @@
       </c>
       <c r="B432">
         <f t="shared" ca="1" si="24"/>
-        <v>112.15719555779907</v>
+        <v>112.13187587077232</v>
       </c>
       <c r="C432">
         <f ca="1"/>
@@ -32488,7 +32539,7 @@
       </c>
       <c r="B433">
         <f t="shared" ca="1" si="24"/>
-        <v>113.98540191822312</v>
+        <v>113.95966951034832</v>
       </c>
       <c r="C433">
         <f ca="1"/>
@@ -32529,7 +32580,7 @@
       </c>
       <c r="B434">
         <f t="shared" ca="1" si="24"/>
-        <v>114.83505829342698</v>
+        <v>114.80913407410937</v>
       </c>
       <c r="C434">
         <f ca="1"/>
@@ -32570,7 +32621,7 @@
       </c>
       <c r="B435">
         <f t="shared" ca="1" si="24"/>
-        <v>116.31265236770311</v>
+        <v>116.28639457888666</v>
       </c>
       <c r="C435">
         <f ca="1"/>
@@ -32611,7 +32662,7 @@
       </c>
       <c r="B436">
         <f t="shared" ca="1" si="24"/>
-        <v>117.67081562343516</v>
+        <v>117.64425122684027</v>
       </c>
       <c r="C436">
         <f ca="1"/>
@@ -32652,7 +32703,7 @@
       </c>
       <c r="B437">
         <f t="shared" ca="1" si="24"/>
-        <v>118.06196869895366</v>
+        <v>118.035315998854</v>
       </c>
       <c r="C437">
         <f ca="1"/>
@@ -32693,7 +32744,7 @@
       </c>
       <c r="B438">
         <f t="shared" ca="1" si="24"/>
-        <v>118.68459573830103</v>
+        <v>118.65780247903625</v>
       </c>
       <c r="C438">
         <f ca="1"/>
@@ -32734,7 +32785,7 @@
       </c>
       <c r="B439">
         <f t="shared" ca="1" si="24"/>
-        <v>119.36265787908818</v>
+        <v>119.33571154608522</v>
       </c>
       <c r="C439">
         <f ca="1"/>
@@ -32775,7 +32826,7 @@
       </c>
       <c r="B440">
         <f t="shared" ca="1" si="24"/>
-        <v>120.88299359290289</v>
+        <v>120.85570404139969</v>
       </c>
       <c r="C440">
         <f ca="1"/>
@@ -32816,7 +32867,7 @@
       </c>
       <c r="B441">
         <f t="shared" ca="1" si="24"/>
-        <v>122.50703846908732</v>
+        <v>122.47938228655542</v>
       </c>
       <c r="C441">
         <f ca="1"/>
@@ -32857,7 +32908,7 @@
       </c>
       <c r="B442">
         <f t="shared" ca="1" si="24"/>
-        <v>125.27963254437869</v>
+        <v>125.25135044378696</v>
       </c>
       <c r="C442">
         <f ca="1"/>
@@ -32898,7 +32949,7 @@
       </c>
       <c r="B443">
         <f t="shared" ca="1" si="24"/>
-        <v>127.40765824665675</v>
+        <v>127.37889574046557</v>
       </c>
       <c r="C443">
         <f ca="1"/>
@@ -32939,7 +32990,7 @@
       </c>
       <c r="B444">
         <f t="shared" ca="1" si="24"/>
-        <v>128.91338079207921</v>
+        <v>128.88427836633664</v>
       </c>
       <c r="C444">
         <f ca="1"/>
@@ -32980,7 +33031,7 @@
       </c>
       <c r="B445">
         <f t="shared" ca="1" si="24"/>
-        <v>129.77547828655835</v>
+        <v>129.7461812407681</v>
       </c>
       <c r="C445">
         <f ca="1"/>
@@ -33021,7 +33072,7 @@
       </c>
       <c r="B446">
         <f t="shared" ca="1" si="24"/>
-        <v>130.42943534303001</v>
+        <v>130.39999066526735</v>
       </c>
       <c r="C446">
         <f ca="1"/>
@@ -33062,7 +33113,7 @@
       </c>
       <c r="B447">
         <f t="shared" ca="1" si="24"/>
-        <v>130.79110006620115</v>
+        <v>130.76157374198192</v>
       </c>
       <c r="C447">
         <f ca="1"/>
@@ -33103,7 +33154,7 @@
       </c>
       <c r="B448">
         <f t="shared" ca="1" si="24"/>
-        <v>130.97558844160397</v>
+        <v>130.94602046880482</v>
       </c>
       <c r="C448">
         <f ca="1"/>
@@ -33144,7 +33195,7 @@
       </c>
       <c r="B449">
         <f t="shared" ca="1" si="24"/>
-        <v>131.51032209184859</v>
+        <v>131.48063340197373</v>
       </c>
       <c r="C449">
         <f ca="1"/>
@@ -33185,7 +33236,7 @@
       </c>
       <c r="B450">
         <f t="shared" ref="B450:B513" ca="1" si="28">F450*$C$669/C450</f>
-        <v>131.89178554327586</v>
+        <v>131.86201073734614</v>
       </c>
       <c r="C450">
         <f ca="1"/>
@@ -33226,7 +33277,7 @@
       </c>
       <c r="B451">
         <f t="shared" ca="1" si="28"/>
-        <v>132.50755609600739</v>
+        <v>132.47764227877664</v>
       </c>
       <c r="C451">
         <f ca="1"/>
@@ -33267,7 +33318,7 @@
       </c>
       <c r="B452">
         <f t="shared" ca="1" si="28"/>
-        <v>128.99066796780392</v>
+        <v>128.96154809434353</v>
       </c>
       <c r="C452">
         <f ca="1"/>
@@ -33308,7 +33359,7 @@
       </c>
       <c r="B453">
         <f t="shared" ca="1" si="28"/>
-        <v>125.6705766341306</v>
+        <v>125.64220627721305</v>
       </c>
       <c r="C453">
         <f ca="1"/>
@@ -33349,7 +33400,7 @@
       </c>
       <c r="B454">
         <f t="shared" ca="1" si="28"/>
-        <v>121.87377617515475</v>
+        <v>121.84626295271569</v>
       </c>
       <c r="C454">
         <f ca="1"/>
@@ -33390,7 +33441,7 @@
       </c>
       <c r="B455">
         <f t="shared" ca="1" si="28"/>
-        <v>115.09959099383335</v>
+        <v>115.07360705578661</v>
       </c>
       <c r="C455">
         <f ca="1"/>
@@ -33431,7 +33482,7 @@
       </c>
       <c r="B456">
         <f t="shared" ca="1" si="28"/>
-        <v>107.85241697259454</v>
+        <v>107.8280690970147</v>
       </c>
       <c r="C456">
         <f ca="1"/>
@@ -33472,7 +33523,7 @@
       </c>
       <c r="B457">
         <f t="shared" ca="1" si="28"/>
-        <v>101.20943753694814</v>
+        <v>101.18658932582943</v>
       </c>
       <c r="C457">
         <f ca="1"/>
@@ -33513,7 +33564,7 @@
       </c>
       <c r="B458">
         <f t="shared" ca="1" si="28"/>
-        <v>97.920277696607499</v>
+        <v>97.89817201919179</v>
       </c>
       <c r="C458">
         <f ca="1"/>
@@ -33554,7 +33605,7 @@
       </c>
       <c r="B459">
         <f t="shared" ca="1" si="28"/>
-        <v>94.749770695905227</v>
+        <v>94.728380766102291</v>
       </c>
       <c r="C459">
         <f ca="1"/>
@@ -33595,7 +33646,7 @@
       </c>
       <c r="B460">
         <f t="shared" ca="1" si="28"/>
-        <v>91.488099958772153</v>
+        <v>91.467446356958135</v>
       </c>
       <c r="C460">
         <f ca="1"/>
@@ -33636,7 +33687,7 @@
       </c>
       <c r="B461">
         <f t="shared" ca="1" si="28"/>
-        <v>86.732400006169883</v>
+        <v>86.712820012106093</v>
       </c>
       <c r="C461">
         <f ca="1"/>
@@ -33677,7 +33728,7 @@
       </c>
       <c r="B462">
         <f t="shared" ca="1" si="28"/>
-        <v>81.70447900579903</v>
+        <v>81.686034073872719</v>
       </c>
       <c r="C462">
         <f ca="1"/>
@@ -33718,7 +33769,7 @@
       </c>
       <c r="B463">
         <f t="shared" ca="1" si="28"/>
-        <v>76.386367703931242</v>
+        <v>76.369123345120784</v>
       </c>
       <c r="C463">
         <f ca="1"/>
@@ -33759,7 +33810,7 @@
       </c>
       <c r="B464">
         <f t="shared" ca="1" si="28"/>
-        <v>73.177286783248704</v>
+        <v>73.16076688018228</v>
       </c>
       <c r="C464">
         <f ca="1"/>
@@ -33800,7 +33851,7 @@
       </c>
       <c r="B465">
         <f t="shared" ca="1" si="28"/>
-        <v>70.614970222140926</v>
+        <v>70.599028766610274</v>
       </c>
       <c r="C465">
         <f ca="1"/>
@@ -33841,7 +33892,7 @@
       </c>
       <c r="B466">
         <f t="shared" ca="1" si="28"/>
-        <v>67.88550555791609</v>
+        <v>67.87018028390375</v>
       </c>
       <c r="C466">
         <f ca="1"/>
@@ -33882,7 +33933,7 @@
       </c>
       <c r="B467">
         <f t="shared" ca="1" si="28"/>
-        <v>53.040860674762094</v>
+        <v>53.028886605820411</v>
       </c>
       <c r="C467">
         <f ca="1"/>
@@ -33923,7 +33974,7 @@
       </c>
       <c r="B468">
         <f t="shared" ca="1" si="28"/>
-        <v>38.285318798609445</v>
+        <v>38.276675819575615</v>
       </c>
       <c r="C468">
         <f ca="1"/>
@@ -33964,7 +34015,7 @@
       </c>
       <c r="B469">
         <f t="shared" ca="1" si="28"/>
-        <v>22.761125081599637</v>
+        <v>22.755986716998272</v>
       </c>
       <c r="C469">
         <f ca="1"/>
@@ -34005,7 +34056,7 @@
       </c>
       <c r="B470">
         <f t="shared" ca="1" si="28"/>
-        <v>18.624742904030992</v>
+        <v>18.620538335087033</v>
       </c>
       <c r="C470">
         <f ca="1"/>
@@ -34046,7 +34097,7 @@
       </c>
       <c r="B471">
         <f t="shared" ca="1" si="28"/>
-        <v>14.493010141369499</v>
+        <v>14.489738318469239</v>
       </c>
       <c r="C471">
         <f ca="1"/>
@@ -34087,7 +34138,7 @@
       </c>
       <c r="B472">
         <f t="shared" ca="1" si="28"/>
-        <v>10.439196404621285</v>
+        <v>10.436839737405586</v>
       </c>
       <c r="C472">
         <f ca="1"/>
@@ -34128,7 +34179,7 @@
       </c>
       <c r="B473">
         <f t="shared" ca="1" si="28"/>
-        <v>10.758079431899919</v>
+        <v>10.755650776271809</v>
       </c>
       <c r="C473">
         <f ca="1"/>
@@ -34169,7 +34220,7 @@
       </c>
       <c r="B474">
         <f t="shared" ca="1" si="28"/>
-        <v>11.071158669620978</v>
+        <v>11.068659335796303</v>
       </c>
       <c r="C474">
         <f ca="1"/>
@@ -34210,7 +34261,7 @@
       </c>
       <c r="B475">
         <f t="shared" ca="1" si="28"/>
-        <v>11.30622300851995</v>
+        <v>11.303670608501328</v>
       </c>
       <c r="C475">
         <f ca="1"/>
@@ -34251,7 +34302,7 @@
       </c>
       <c r="B476">
         <f t="shared" ca="1" si="28"/>
-        <v>13.834553607294877</v>
+        <v>13.831430432132111</v>
       </c>
       <c r="C476">
         <f ca="1"/>
@@ -34292,7 +34343,7 @@
       </c>
       <c r="B477">
         <f t="shared" ca="1" si="28"/>
-        <v>16.304903070946182</v>
+        <v>16.301222209983987</v>
       </c>
       <c r="C477">
         <f ca="1"/>
@@ -34333,7 +34384,7 @@
       </c>
       <c r="B478">
         <f t="shared" ca="1" si="28"/>
-        <v>18.785165268390305</v>
+        <v>18.78092448381134</v>
       </c>
       <c r="C478">
         <f ca="1"/>
@@ -34374,7 +34425,7 @@
       </c>
       <c r="B479">
         <f t="shared" ca="1" si="28"/>
-        <v>37.86113925979982</v>
+        <v>37.852592040053764</v>
       </c>
       <c r="C479">
         <f ca="1"/>
@@ -34415,7 +34466,7 @@
       </c>
       <c r="B480">
         <f t="shared" ca="1" si="28"/>
-        <v>56.803125845862048</v>
+        <v>56.790302438844741</v>
       </c>
       <c r="C480">
         <f ca="1"/>
@@ -34456,7 +34507,7 @@
       </c>
       <c r="B481">
         <f t="shared" ca="1" si="28"/>
-        <v>75.83202473464091</v>
+        <v>75.814905519744926</v>
       </c>
       <c r="C481">
         <f ca="1"/>
@@ -34497,7 +34548,7 @@
       </c>
       <c r="B482">
         <f t="shared" ca="1" si="28"/>
-        <v>80.719081328625009</v>
+        <v>80.70085885198263</v>
       </c>
       <c r="C482">
         <f ca="1"/>
@@ -34538,7 +34589,7 @@
       </c>
       <c r="B483">
         <f t="shared" ca="1" si="28"/>
-        <v>85.736903088627159</v>
+        <v>85.717547829768819</v>
       </c>
       <c r="C483">
         <f ca="1"/>
@@ -34579,7 +34630,7 @@
       </c>
       <c r="B484">
         <f t="shared" ca="1" si="28"/>
-        <v>90.647787332127905</v>
+        <v>90.627323432388792</v>
       </c>
       <c r="C484">
         <f ca="1"/>
@@ -34620,7 +34671,7 @@
       </c>
       <c r="B485">
         <f t="shared" ca="1" si="28"/>
-        <v>93.6860188584334</v>
+        <v>93.664869072505908</v>
       </c>
       <c r="C485">
         <f ca="1"/>
@@ -34661,7 +34712,7 @@
       </c>
       <c r="B486">
         <f t="shared" ca="1" si="28"/>
-        <v>96.795394919784599</v>
+        <v>96.773543186662991</v>
       </c>
       <c r="C486">
         <f ca="1"/>
@@ -34702,7 +34753,7 @@
       </c>
       <c r="B487">
         <f t="shared" ca="1" si="28"/>
-        <v>99.897901924041975</v>
+        <v>99.875349794428132</v>
       </c>
       <c r="C487">
         <f ca="1"/>
@@ -34743,7 +34794,7 @@
       </c>
       <c r="B488">
         <f t="shared" ca="1" si="28"/>
-        <v>102.06932909574689</v>
+        <v>102.04628676257441</v>
       </c>
       <c r="C488">
         <f ca="1"/>
@@ -34784,7 +34835,7 @@
       </c>
       <c r="B489">
         <f t="shared" ca="1" si="28"/>
-        <v>104.27474420836717</v>
+        <v>104.25120399879773</v>
       </c>
       <c r="C489">
         <f ca="1"/>
@@ -34825,7 +34876,7 @@
       </c>
       <c r="B490">
         <f t="shared" ca="1" si="28"/>
-        <v>106.45716202038712</v>
+        <v>106.43312912610239</v>
       </c>
       <c r="C490">
         <f ca="1"/>
@@ -34866,7 +34917,7 @@
       </c>
       <c r="B491">
         <f t="shared" ca="1" si="28"/>
-        <v>108.78943164334467</v>
+        <v>108.76487223503094</v>
       </c>
       <c r="C491">
         <f ca="1"/>
@@ -34907,7 +34958,7 @@
       </c>
       <c r="B492">
         <f t="shared" ca="1" si="28"/>
-        <v>111.2092958695751</v>
+        <v>111.18419017259437</v>
       </c>
       <c r="C492">
         <f ca="1"/>
@@ -34948,7 +34999,7 @@
       </c>
       <c r="B493">
         <f t="shared" ca="1" si="28"/>
-        <v>113.44844424688847</v>
+        <v>113.42283305816611</v>
       </c>
       <c r="C493">
         <f ca="1"/>
@@ -34989,7 +35040,7 @@
       </c>
       <c r="B494">
         <f t="shared" ca="1" si="28"/>
-        <v>115.01148747439947</v>
+        <v>114.98552342587945</v>
       </c>
       <c r="C494">
         <f ca="1"/>
@@ -35030,7 +35081,7 @@
       </c>
       <c r="B495">
         <f t="shared" ca="1" si="28"/>
-        <v>116.56655922991644</v>
+        <v>116.54024412117278</v>
       </c>
       <c r="C495">
         <f ca="1"/>
@@ -35071,7 +35122,7 @@
       </c>
       <c r="B496">
         <f t="shared" ca="1" si="28"/>
-        <v>117.88028855034388</v>
+        <v>117.85367686486195</v>
       </c>
       <c r="C496">
         <f ca="1"/>
@@ -35112,7 +35163,7 @@
       </c>
       <c r="B497">
         <f t="shared" ca="1" si="28"/>
-        <v>118.56087893026556</v>
+        <v>118.53411360029095</v>
       </c>
       <c r="C497">
         <f ca="1"/>
@@ -35153,7 +35204,7 @@
       </c>
       <c r="B498">
         <f t="shared" ca="1" si="28"/>
-        <v>119.41230428849762</v>
+        <v>119.38534674772914</v>
       </c>
       <c r="C498">
         <f ca="1"/>
@@ -35194,7 +35245,7 @@
       </c>
       <c r="B499">
         <f t="shared" ca="1" si="28"/>
-        <v>120.63974573632375</v>
+        <v>120.61251109845823</v>
       </c>
       <c r="C499">
         <f ca="1"/>
@@ -35235,7 +35286,7 @@
       </c>
       <c r="B500">
         <f t="shared" ca="1" si="28"/>
-        <v>121.81175464353689</v>
+        <v>121.78425542256926</v>
       </c>
       <c r="C500">
         <f ca="1"/>
@@ -35276,7 +35327,7 @@
       </c>
       <c r="B501">
         <f t="shared" ca="1" si="28"/>
-        <v>122.91128480500296</v>
+        <v>122.88353736313942</v>
       </c>
       <c r="C501">
         <f ca="1"/>
@@ -35317,7 +35368,7 @@
       </c>
       <c r="B502">
         <f t="shared" ca="1" si="28"/>
-        <v>124.12432962484057</v>
+        <v>124.09630833594443</v>
       </c>
       <c r="C502">
         <f ca="1"/>
@@ -35358,7 +35409,7 @@
       </c>
       <c r="B503">
         <f t="shared" ca="1" si="28"/>
-        <v>124.02631567805953</v>
+        <v>123.99831651598676</v>
       </c>
       <c r="C503">
         <f ca="1"/>
@@ -35399,7 +35450,7 @@
       </c>
       <c r="B504">
         <f t="shared" ca="1" si="28"/>
-        <v>123.78332184408961</v>
+        <v>123.75537753830847</v>
       </c>
       <c r="C504">
         <f ca="1"/>
@@ -35440,7 +35491,7 @@
       </c>
       <c r="B505">
         <f t="shared" ca="1" si="28"/>
-        <v>123.73967336053127</v>
+        <v>123.71173890847318</v>
       </c>
       <c r="C505">
         <f ca="1"/>
@@ -35481,7 +35532,7 @@
       </c>
       <c r="B506">
         <f t="shared" ca="1" si="28"/>
-        <v>124.15569877371159</v>
+        <v>124.12767040317412</v>
       </c>
       <c r="C506">
         <f ca="1"/>
@@ -35522,7 +35573,7 @@
       </c>
       <c r="B507">
         <f t="shared" ca="1" si="28"/>
-        <v>124.64148505008123</v>
+        <v>124.61334701242507</v>
       </c>
       <c r="C507">
         <f ca="1"/>
@@ -35563,7 +35614,7 @@
       </c>
       <c r="B508">
         <f t="shared" ca="1" si="28"/>
-        <v>125.13012521470061</v>
+        <v>125.10187686565534</v>
       </c>
       <c r="C508">
         <f ca="1"/>
@@ -35604,7 +35655,7 @@
       </c>
       <c r="B509">
         <f t="shared" ca="1" si="28"/>
-        <v>124.63106075876902</v>
+        <v>124.60292507441521</v>
       </c>
       <c r="C509">
         <f ca="1"/>
@@ -35645,7 +35696,7 @@
       </c>
       <c r="B510">
         <f t="shared" ca="1" si="28"/>
-        <v>124.59716989362214</v>
+        <v>124.56904186019159</v>
       </c>
       <c r="C510">
         <f ca="1"/>
@@ -35686,7 +35737,7 @@
       </c>
       <c r="B511">
         <f t="shared" ca="1" si="28"/>
-        <v>124.40777721377185</v>
+        <v>124.37969193607672</v>
       </c>
       <c r="C511">
         <f ca="1"/>
@@ -35727,7 +35778,7 @@
       </c>
       <c r="B512">
         <f t="shared" ca="1" si="28"/>
-        <v>123.70228355518613</v>
+        <v>123.6743575439433</v>
       </c>
       <c r="C512">
         <f ca="1"/>
@@ -35768,7 +35819,7 @@
       </c>
       <c r="B513">
         <f t="shared" ca="1" si="28"/>
-        <v>122.32206213571796</v>
+        <v>122.29444771192338</v>
       </c>
       <c r="C513">
         <f ca="1"/>
@@ -35809,7 +35860,7 @@
       </c>
       <c r="B514">
         <f t="shared" ref="B514:B577" ca="1" si="32">F514*$C$669/C514</f>
-        <v>121.07865723005</v>
+        <v>121.05132350713158</v>
       </c>
       <c r="C514">
         <f ca="1"/>
@@ -35850,7 +35901,7 @@
       </c>
       <c r="B515">
         <f t="shared" ca="1" si="32"/>
-        <v>120.75765980590403</v>
+        <v>120.7303985487269</v>
       </c>
       <c r="C515">
         <f ca="1"/>
@@ -35891,7 +35942,7 @@
       </c>
       <c r="B516">
         <f t="shared" ca="1" si="32"/>
-        <v>120.96546509554635</v>
+        <v>120.93815692595427</v>
       </c>
       <c r="C516">
         <f ca="1"/>
@@ -35932,7 +35983,7 @@
       </c>
       <c r="B517">
         <f t="shared" ca="1" si="32"/>
-        <v>120.98477058744663</v>
+        <v>120.95745805960533</v>
       </c>
       <c r="C517">
         <f ca="1"/>
@@ -35973,7 +36024,7 @@
       </c>
       <c r="B518">
         <f t="shared" ca="1" si="32"/>
-        <v>121.29924782945368</v>
+        <v>121.27186430781384</v>
       </c>
       <c r="C518">
         <f ca="1"/>
@@ -36014,7 +36065,7 @@
       </c>
       <c r="B519">
         <f t="shared" ca="1" si="32"/>
-        <v>121.19480375431984</v>
+        <v>121.1674438111163</v>
       </c>
       <c r="C519">
         <f ca="1"/>
@@ -36055,7 +36106,7 @@
       </c>
       <c r="B520">
         <f t="shared" ca="1" si="32"/>
-        <v>122.08876624103459</v>
+        <v>122.06120448420454</v>
       </c>
       <c r="C520">
         <f ca="1"/>
@@ -36096,7 +36147,7 @@
       </c>
       <c r="B521">
         <f t="shared" ca="1" si="32"/>
-        <v>123.85549736243351</v>
+        <v>123.82753676290031</v>
       </c>
       <c r="C521">
         <f ca="1"/>
@@ -36137,7 +36188,7 @@
       </c>
       <c r="B522">
         <f t="shared" ca="1" si="32"/>
-        <v>125.31489039289671</v>
+        <v>125.2866003327828</v>
       </c>
       <c r="C522">
         <f ca="1"/>
@@ -36178,7 +36229,7 @@
       </c>
       <c r="B523">
         <f t="shared" ca="1" si="32"/>
-        <v>126.52436404310697</v>
+        <v>126.49580094215837</v>
       </c>
       <c r="C523">
         <f ca="1"/>
@@ -36219,7 +36270,7 @@
       </c>
       <c r="B524">
         <f t="shared" ca="1" si="32"/>
-        <v>127.85998608844997</v>
+        <v>127.8311214684414</v>
       </c>
       <c r="C524">
         <f ca="1"/>
@@ -36260,7 +36311,7 @@
       </c>
       <c r="B525">
         <f t="shared" ca="1" si="32"/>
-        <v>129.13450808717704</v>
+        <v>129.10535574155301</v>
       </c>
       <c r="C525">
         <f ca="1"/>
@@ -36301,7 +36352,7 @@
       </c>
       <c r="B526">
         <f t="shared" ca="1" si="32"/>
-        <v>130.66428887061966</v>
+        <v>130.6347911742541</v>
       </c>
       <c r="C526">
         <f ca="1"/>
@@ -36342,7 +36393,7 @@
       </c>
       <c r="B527">
         <f t="shared" ca="1" si="32"/>
-        <v>133.28367751871235</v>
+        <v>133.25358849068553</v>
       </c>
       <c r="C527">
         <f ca="1"/>
@@ -36383,7 +36434,7 @@
       </c>
       <c r="B528">
         <f t="shared" ca="1" si="32"/>
-        <v>135.72263920495516</v>
+        <v>135.69199957697566</v>
       </c>
       <c r="C528">
         <f ca="1"/>
@@ -36424,7 +36475,7 @@
       </c>
       <c r="B529">
         <f t="shared" ca="1" si="32"/>
-        <v>138.0419684814608</v>
+        <v>138.01080526075862</v>
       </c>
       <c r="C529">
         <f ca="1"/>
@@ -36465,7 +36516,7 @@
       </c>
       <c r="B530">
         <f t="shared" ca="1" si="32"/>
-        <v>138.00591648481858</v>
+        <v>137.97476140291897</v>
       </c>
       <c r="C530">
         <f ca="1"/>
@@ -36506,7 +36557,7 @@
       </c>
       <c r="B531">
         <f t="shared" ca="1" si="32"/>
-        <v>138.15160508144871</v>
+        <v>138.12041711008843</v>
       </c>
       <c r="C531">
         <f ca="1"/>
@@ -36547,7 +36598,7 @@
       </c>
       <c r="B532">
         <f t="shared" ca="1" si="32"/>
-        <v>138.16690985815239</v>
+        <v>138.1357184317115</v>
       </c>
       <c r="C532">
         <f ca="1"/>
@@ -36588,7 +36639,7 @@
       </c>
       <c r="B533">
         <f t="shared" ca="1" si="32"/>
-        <v>138.94454741394185</v>
+        <v>138.91318043443511</v>
       </c>
       <c r="C533">
         <f ca="1"/>
@@ -36629,7 +36680,7 @@
       </c>
       <c r="B534">
         <f t="shared" ca="1" si="32"/>
-        <v>139.71338539967414</v>
+        <v>139.68184485362025</v>
       </c>
       <c r="C534">
         <f ca="1"/>
@@ -36670,7 +36721,7 @@
       </c>
       <c r="B535">
         <f t="shared" ca="1" si="32"/>
-        <v>140.56044817077026</v>
+        <v>140.5287163987843</v>
       </c>
       <c r="C535">
         <f ca="1"/>
@@ -36711,7 +36762,7 @@
       </c>
       <c r="B536">
         <f t="shared" ca="1" si="32"/>
-        <v>141.69136025516005</v>
+        <v>141.65937317775308</v>
       </c>
       <c r="C536">
         <f ca="1"/>
@@ -36752,7 +36803,7 @@
       </c>
       <c r="B537">
         <f t="shared" ca="1" si="32"/>
-        <v>143.00316028855386</v>
+        <v>142.97087706994861</v>
       </c>
       <c r="C537">
         <f ca="1"/>
@@ -36793,7 +36844,7 @@
       </c>
       <c r="B538">
         <f t="shared" ca="1" si="32"/>
-        <v>144.28197021185207</v>
+        <v>144.24939829962477</v>
       </c>
       <c r="C538">
         <f ca="1"/>
@@ -36834,7 +36885,7 @@
       </c>
       <c r="B539">
         <f t="shared" ca="1" si="32"/>
-        <v>142.65350697940445</v>
+        <v>142.62130269565768</v>
       </c>
       <c r="C539">
         <f ca="1"/>
@@ -36875,7 +36926,7 @@
       </c>
       <c r="B540">
         <f t="shared" ca="1" si="32"/>
-        <v>141.26244548292493</v>
+        <v>141.23055523379315</v>
       </c>
       <c r="C540">
         <f ca="1"/>
@@ -36916,7 +36967,7 @@
       </c>
       <c r="B541">
         <f t="shared" ca="1" si="32"/>
-        <v>140.03424665188018</v>
+        <v>140.00263367082607</v>
       </c>
       <c r="C541">
         <f ca="1"/>
@@ -36957,7 +37008,7 @@
       </c>
       <c r="B542">
         <f t="shared" ca="1" si="32"/>
-        <v>139.52697823614358</v>
+        <v>139.49547977183946</v>
       </c>
       <c r="C542">
         <f ca="1"/>
@@ -36998,7 +37049,7 @@
       </c>
       <c r="B543">
         <f t="shared" ca="1" si="32"/>
-        <v>137.77272344077977</v>
+        <v>137.74162100262595</v>
       </c>
       <c r="C543">
         <f ca="1"/>
@@ -37039,7 +37090,7 @@
       </c>
       <c r="B544">
         <f t="shared" ca="1" si="32"/>
-        <v>136.00483523748176</v>
+        <v>135.9741319032444</v>
       </c>
       <c r="C544">
         <f ca="1"/>
@@ -37080,7 +37131,7 @@
       </c>
       <c r="B545">
         <f t="shared" ca="1" si="32"/>
-        <v>133.88285596650607</v>
+        <v>133.85263167287553</v>
       </c>
       <c r="C545">
         <f ca="1"/>
@@ -37121,7 +37172,7 @@
       </c>
       <c r="B546">
         <f t="shared" ca="1" si="32"/>
-        <v>131.46897370846534</v>
+        <v>131.4392943530618</v>
       </c>
       <c r="C546">
         <f ca="1"/>
@@ -37162,7 +37213,7 @@
       </c>
       <c r="B547">
         <f t="shared" ca="1" si="32"/>
-        <v>129.13769524987691</v>
+        <v>129.10854218474523</v>
       </c>
       <c r="C547">
         <f ca="1"/>
@@ -37203,7 +37254,7 @@
       </c>
       <c r="B548">
         <f t="shared" ca="1" si="32"/>
-        <v>127.00865070586555</v>
+        <v>126.97997827633868</v>
       </c>
       <c r="C548">
         <f ca="1"/>
@@ -37244,7 +37295,7 @@
       </c>
       <c r="B549">
         <f t="shared" ca="1" si="32"/>
-        <v>125.08467446900218</v>
+        <v>125.05643638054387</v>
       </c>
       <c r="C549">
         <f ca="1"/>
@@ -37285,7 +37336,7 @@
       </c>
       <c r="B550">
         <f t="shared" ca="1" si="32"/>
-        <v>123.4375878533714</v>
+        <v>123.40972159765556</v>
       </c>
       <c r="C550">
         <f ca="1"/>
@@ -37326,7 +37377,7 @@
       </c>
       <c r="B551">
         <f t="shared" ca="1" si="32"/>
-        <v>121.44302525152166</v>
+        <v>121.41560927187223</v>
       </c>
       <c r="C551">
         <f ca="1"/>
@@ -37367,7 +37418,7 @@
       </c>
       <c r="B552">
         <f t="shared" ca="1" si="32"/>
-        <v>119.4278242221354</v>
+        <v>119.4008631777142</v>
       </c>
       <c r="C552">
         <f ca="1"/>
@@ -37408,7 +37459,7 @@
       </c>
       <c r="B553">
         <f t="shared" ca="1" si="32"/>
-        <v>117.68408998952729</v>
+        <v>117.65752259622057</v>
       </c>
       <c r="C553">
         <f ca="1"/>
@@ -37449,7 +37500,7 @@
       </c>
       <c r="B554">
         <f t="shared" ca="1" si="32"/>
-        <v>117.69724639388686</v>
+        <v>117.67067603049838</v>
       </c>
       <c r="C554">
         <f ca="1"/>
@@ -37490,7 +37541,7 @@
       </c>
       <c r="B555">
         <f t="shared" ca="1" si="32"/>
-        <v>117.81307968449791</v>
+        <v>117.7864831715374</v>
       </c>
       <c r="C555">
         <f ca="1"/>
@@ -37531,7 +37582,7 @@
       </c>
       <c r="B556">
         <f t="shared" ca="1" si="32"/>
-        <v>117.40416733870967</v>
+        <v>117.37766313844085</v>
       </c>
       <c r="C556">
         <f ca="1"/>
@@ -37572,7 +37623,7 @@
       </c>
       <c r="B557">
         <f t="shared" ca="1" si="32"/>
-        <v>117.17263506728258</v>
+        <v>117.14618313583719</v>
       </c>
       <c r="C557">
         <f ca="1"/>
@@ -37613,7 +37664,7 @@
       </c>
       <c r="B558">
         <f t="shared" ca="1" si="32"/>
-        <v>117.11225570532275</v>
+        <v>117.08581740462606</v>
       </c>
       <c r="C558">
         <f ca="1"/>
@@ -37654,7 +37705,7 @@
       </c>
       <c r="B559">
         <f t="shared" ca="1" si="32"/>
-        <v>117.00343382371305</v>
+        <v>116.97702008975031</v>
       </c>
       <c r="C559">
         <f ca="1"/>
@@ -37695,7 +37746,7 @@
       </c>
       <c r="B560">
         <f t="shared" ca="1" si="32"/>
-        <v>118.0365669535737</v>
+        <v>118.00991998796341</v>
       </c>
       <c r="C560">
         <f ca="1"/>
@@ -37736,7 +37787,7 @@
       </c>
       <c r="B561">
         <f t="shared" ca="1" si="32"/>
-        <v>118.7910780846827</v>
+        <v>118.76426078683822</v>
       </c>
       <c r="C561">
         <f ca="1"/>
@@ -37777,7 +37828,7 @@
       </c>
       <c r="B562">
         <f t="shared" ca="1" si="32"/>
-        <v>119.4501059806946</v>
+        <v>119.42313990612666</v>
       </c>
       <c r="C562">
         <f ca="1"/>
@@ -37818,7 +37869,7 @@
       </c>
       <c r="B563">
         <f t="shared" ca="1" si="32"/>
-        <v>121.60544235359329</v>
+        <v>121.57798970799325</v>
       </c>
       <c r="C563">
         <f ca="1"/>
@@ -37859,7 +37910,7 @@
       </c>
       <c r="B564">
         <f t="shared" ca="1" si="32"/>
-        <v>123.89389454025599</v>
+        <v>123.86592527249138</v>
       </c>
       <c r="C564">
         <f ca="1"/>
@@ -37900,7 +37951,7 @@
       </c>
       <c r="B565">
         <f t="shared" ca="1" si="32"/>
-        <v>126.00743579915675</v>
+        <v>125.97898939568161</v>
       </c>
       <c r="C565">
         <f ca="1"/>
@@ -37941,7 +37992,7 @@
       </c>
       <c r="B566">
         <f t="shared" ca="1" si="32"/>
-        <v>128.03861851292996</v>
+        <v>128.00971356633281</v>
       </c>
       <c r="C566">
         <f ca="1"/>
@@ -37982,7 +38033,7 @@
       </c>
       <c r="B567">
         <f t="shared" ca="1" si="32"/>
-        <v>130.44332074973755</v>
+        <v>130.41387293731958</v>
       </c>
       <c r="C567">
         <f ca="1"/>
@@ -38023,7 +38074,7 @@
       </c>
       <c r="B568">
         <f t="shared" ca="1" si="32"/>
-        <v>133.03814133226126</v>
+        <v>133.00810773446668</v>
       </c>
       <c r="C568">
         <f ca="1"/>
@@ -38064,7 +38115,7 @@
       </c>
       <c r="B569">
         <f t="shared" ca="1" si="32"/>
-        <v>134.40736108681233</v>
+        <v>134.37701838521497</v>
       </c>
       <c r="C569">
         <f ca="1"/>
@@ -38105,7 +38156,7 @@
       </c>
       <c r="B570">
         <f t="shared" ca="1" si="32"/>
-        <v>136.16753917080825</v>
+        <v>136.1367991058676</v>
       </c>
       <c r="C570">
         <f ca="1"/>
@@ -38146,7 +38197,7 @@
       </c>
       <c r="B571">
         <f t="shared" ca="1" si="32"/>
-        <v>137.73072943026312</v>
+        <v>137.69963647233212</v>
       </c>
       <c r="C571">
         <f ca="1"/>
@@ -38187,7 +38238,7 @@
       </c>
       <c r="B572">
         <f t="shared" ca="1" si="32"/>
-        <v>139.04599050270184</v>
+        <v>139.0146006222368</v>
       </c>
       <c r="C572">
         <f ca="1"/>
@@ -38228,7 +38279,7 @@
       </c>
       <c r="B573">
         <f t="shared" ca="1" si="32"/>
-        <v>139.86658444974614</v>
+        <v>139.83500931873328</v>
       </c>
       <c r="C573">
         <f ca="1"/>
@@ -38269,7 +38320,7 @@
       </c>
       <c r="B574">
         <f t="shared" ca="1" si="32"/>
-        <v>140.44078961350797</v>
+        <v>140.40908485465482</v>
       </c>
       <c r="C574">
         <f ca="1"/>
@@ -38310,7 +38361,7 @@
       </c>
       <c r="B575">
         <f t="shared" ca="1" si="32"/>
-        <v>141.60401870662497</v>
+        <v>141.57205134672844</v>
       </c>
       <c r="C575">
         <f ca="1"/>
@@ -38351,7 +38402,7 @@
       </c>
       <c r="B576">
         <f t="shared" ca="1" si="32"/>
-        <v>142.41133406317456</v>
+        <v>142.37918445039574</v>
       </c>
       <c r="C576">
         <f ca="1"/>
@@ -38392,7 +38443,7 @@
       </c>
       <c r="B577">
         <f t="shared" ca="1" si="32"/>
-        <v>143.42379113249586</v>
+        <v>143.39141295572708</v>
       </c>
       <c r="C577">
         <f ca="1"/>
@@ -38433,7 +38484,7 @@
       </c>
       <c r="B578">
         <f t="shared" ref="B578:B641" ca="1" si="36">F578*$C$669/C578</f>
-        <v>145.26532348342116</v>
+        <v>145.23252957743816</v>
       </c>
       <c r="C578">
         <f ca="1"/>
@@ -38474,7 +38525,7 @@
       </c>
       <c r="B579">
         <f t="shared" ca="1" si="36"/>
-        <v>147.33188912105894</v>
+        <v>147.29862868419573</v>
       </c>
       <c r="C579">
         <f ca="1"/>
@@ -38515,7 +38566,7 @@
       </c>
       <c r="B580">
         <f t="shared" ca="1" si="36"/>
-        <v>149.60559865660454</v>
+        <v>149.57182492575657</v>
       </c>
       <c r="C580">
         <f ca="1"/>
@@ -38556,7 +38607,7 @@
       </c>
       <c r="B581">
         <f t="shared" ca="1" si="36"/>
-        <v>152.18447211219657</v>
+        <v>152.15011619606432</v>
       </c>
       <c r="C581">
         <f ca="1"/>
@@ -38597,7 +38648,7 @@
       </c>
       <c r="B582">
         <f t="shared" ca="1" si="36"/>
-        <v>154.90017035289048</v>
+        <v>154.8652013630346</v>
       </c>
       <c r="C582">
         <f ca="1"/>
@@ -38638,7 +38689,7 @@
       </c>
       <c r="B583">
         <f t="shared" ca="1" si="36"/>
-        <v>157.69582850226158</v>
+        <v>157.66022838759</v>
       </c>
       <c r="C583">
         <f ca="1"/>
@@ -38679,7 +38730,7 @@
       </c>
       <c r="B584">
         <f t="shared" ca="1" si="36"/>
-        <v>160.9669055596093</v>
+        <v>160.93056699345522</v>
       </c>
       <c r="C584">
         <f ca="1"/>
@@ -38720,7 +38771,7 @@
       </c>
       <c r="B585">
         <f t="shared" ca="1" si="36"/>
-        <v>164.10442648864878</v>
+        <v>164.06737962154645</v>
       </c>
       <c r="C585">
         <f ca="1"/>
@@ -38761,7 +38812,7 @@
       </c>
       <c r="B586">
         <f t="shared" ca="1" si="36"/>
-        <v>167.19379165130081</v>
+        <v>167.15604735450049</v>
       </c>
       <c r="C586">
         <f ca="1"/>
@@ -38802,7 +38853,7 @@
       </c>
       <c r="B587">
         <f t="shared" ca="1" si="36"/>
-        <v>167.57286125243672</v>
+        <v>167.53503137999755</v>
       </c>
       <c r="C587">
         <f ca="1"/>
@@ -38843,7 +38894,7 @@
       </c>
       <c r="B588">
         <f t="shared" ca="1" si="36"/>
-        <v>168.47656802857344</v>
+        <v>168.438534142717</v>
       </c>
       <c r="C588">
         <f ca="1"/>
@@ -38884,7 +38935,7 @@
       </c>
       <c r="B589">
         <f t="shared" ca="1" si="36"/>
-        <v>169.54988835334046</v>
+        <v>169.5116121635055</v>
       </c>
       <c r="C589">
         <f ca="1"/>
@@ -38925,7 +38976,7 @@
       </c>
       <c r="B590">
         <f t="shared" ca="1" si="36"/>
-        <v>170.43878386585379</v>
+        <v>170.40030700627076</v>
       </c>
       <c r="C590">
         <f ca="1"/>
@@ -38966,7 +39017,7 @@
       </c>
       <c r="B591">
         <f t="shared" ca="1" si="36"/>
-        <v>170.93521689266274</v>
+        <v>170.89662796243809</v>
       </c>
       <c r="C591">
         <f ca="1"/>
@@ -39007,7 +39058,7 @@
       </c>
       <c r="B592">
         <f t="shared" ca="1" si="36"/>
-        <v>170.99115063329489</v>
+        <v>170.95254907592849</v>
       </c>
       <c r="C592">
         <f ca="1"/>
@@ -39048,7 +39099,7 @@
       </c>
       <c r="B593">
         <f t="shared" ca="1" si="36"/>
-        <v>170.57307255085655</v>
+        <v>170.53456537536329</v>
       </c>
       <c r="C593">
         <f ca="1"/>
@@ -39089,7 +39140,7 @@
       </c>
       <c r="B594">
         <f t="shared" ca="1" si="36"/>
-        <v>170.91445746729269</v>
+        <v>170.87587322354537</v>
       </c>
       <c r="C594">
         <f ca="1"/>
@@ -39130,7 +39181,7 @@
       </c>
       <c r="B595">
         <f t="shared" ca="1" si="36"/>
-        <v>171.25101607920976</v>
+        <v>171.21235585675527</v>
       </c>
       <c r="C595">
         <f ca="1"/>
@@ -39171,7 +39222,7 @@
       </c>
       <c r="B596">
         <f t="shared" ca="1" si="36"/>
-        <v>169.91693160105496</v>
+        <v>169.87857255055192</v>
       </c>
       <c r="C596">
         <f ca="1"/>
@@ -39212,7 +39263,7 @@
       </c>
       <c r="B597">
         <f t="shared" ca="1" si="36"/>
-        <v>168.79146783904295</v>
+        <v>168.75336286399238</v>
       </c>
       <c r="C597">
         <f ca="1"/>
@@ -39253,7 +39304,7 @@
       </c>
       <c r="B598">
         <f t="shared" ca="1" si="36"/>
-        <v>167.52325479862162</v>
+        <v>167.4854361249279</v>
       </c>
       <c r="C598">
         <f ca="1"/>
@@ -39294,7 +39345,7 @@
       </c>
       <c r="B599">
         <f t="shared" ca="1" si="36"/>
-        <v>169.71813945537266</v>
+        <v>169.67982528255118</v>
       </c>
       <c r="C599">
         <f ca="1"/>
@@ -39335,7 +39386,7 @@
       </c>
       <c r="B600">
         <f t="shared" ca="1" si="36"/>
-        <v>172.06706456476829</v>
+        <v>172.02822011791201</v>
       </c>
       <c r="C600">
         <f ca="1"/>
@@ -39376,7 +39427,7 @@
       </c>
       <c r="B601">
         <f t="shared" ca="1" si="36"/>
-        <v>174.66713043612972</v>
+        <v>174.62769901976355</v>
       </c>
       <c r="C601">
         <f ca="1"/>
@@ -39417,7 +39468,7 @@
       </c>
       <c r="B602">
         <f t="shared" ca="1" si="36"/>
-        <v>164.70169489133377</v>
+        <v>164.66451318982379</v>
       </c>
       <c r="C602">
         <f ca="1"/>
@@ -39458,7 +39509,7 @@
       </c>
       <c r="B603">
         <f t="shared" ca="1" si="36"/>
-        <v>154.86510929094578</v>
+        <v>154.83014821618718</v>
       </c>
       <c r="C603">
         <f ca="1"/>
@@ -39499,7 +39550,7 @@
       </c>
       <c r="B604">
         <f t="shared" ca="1" si="36"/>
-        <v>145.7088843181686</v>
+        <v>145.67599027753567</v>
       </c>
       <c r="C604">
         <f ca="1"/>
@@ -39540,7 +39591,7 @@
       </c>
       <c r="B605">
         <f t="shared" ca="1" si="36"/>
-        <v>139.68995493842104</v>
+        <v>139.65841968183557</v>
       </c>
       <c r="C605">
         <f ca="1"/>
@@ -39581,7 +39632,7 @@
       </c>
       <c r="B606">
         <f t="shared" ca="1" si="36"/>
-        <v>132.57034554433781</v>
+        <v>132.54041755227706</v>
       </c>
       <c r="C606">
         <f ca="1"/>
@@ -39622,7 +39673,7 @@
       </c>
       <c r="B607">
         <f t="shared" ca="1" si="36"/>
-        <v>124.74840201075357</v>
+        <v>124.72023983640273</v>
       </c>
       <c r="C607">
         <f ca="1"/>
@@ -39663,7 +39714,7 @@
       </c>
       <c r="B608">
         <f t="shared" ca="1" si="36"/>
-        <v>123.68752107819589</v>
+        <v>123.65959839960858</v>
       </c>
       <c r="C608">
         <f ca="1"/>
@@ -39704,7 +39755,7 @@
       </c>
       <c r="B609">
         <f t="shared" ca="1" si="36"/>
-        <v>122.77401586362585</v>
+        <v>122.74629941047077</v>
       </c>
       <c r="C609">
         <f ca="1"/>
@@ -39745,7 +39796,7 @@
       </c>
       <c r="B610">
         <f t="shared" ca="1" si="36"/>
-        <v>122.06776617087512</v>
+        <v>122.04020915484838</v>
       </c>
       <c r="C610">
         <f ca="1"/>
@@ -39786,7 +39837,7 @@
       </c>
       <c r="B611">
         <f t="shared" ca="1" si="36"/>
-        <v>120.29851984190634</v>
+        <v>120.27136223639535</v>
       </c>
       <c r="C611">
         <f ca="1"/>
@@ -39827,7 +39878,7 @@
       </c>
       <c r="B612">
         <f t="shared" ca="1" si="36"/>
-        <v>118.43735319410403</v>
+        <v>118.41061575028479</v>
       </c>
       <c r="C612">
         <f ca="1"/>
@@ -39868,7 +39919,7 @@
       </c>
       <c r="B613">
         <f t="shared" ca="1" si="36"/>
-        <v>116.37019360462446</v>
+        <v>116.34392282577112</v>
       </c>
       <c r="C613">
         <f ca="1"/>
@@ -39909,7 +39960,7 @@
       </c>
       <c r="B614">
         <f t="shared" ca="1" si="36"/>
-        <v>129.87089875454026</v>
+        <v>129.84158016740912</v>
       </c>
       <c r="C614">
         <f ca="1"/>
@@ -39950,7 +40001,7 @@
       </c>
       <c r="B615">
         <f t="shared" ca="1" si="36"/>
-        <v>143.31365949567208</v>
+        <v>143.28130618131681</v>
       </c>
       <c r="C615">
         <f ca="1"/>
@@ -39991,7 +40042,7 @@
       </c>
       <c r="B616">
         <f t="shared" ca="1" si="36"/>
-        <v>156.48574556271089</v>
+        <v>156.45041862642216</v>
       </c>
       <c r="C616">
         <f ca="1"/>
@@ -40032,7 +40083,7 @@
       </c>
       <c r="B617">
         <f t="shared" ca="1" si="36"/>
-        <v>167.8076542463719</v>
+        <v>167.76977136899538</v>
       </c>
       <c r="C617">
         <f ca="1"/>
@@ -40073,7 +40124,7 @@
       </c>
       <c r="B618">
         <f t="shared" ca="1" si="36"/>
-        <v>178.96941739103872</v>
+        <v>178.92901472571558</v>
       </c>
       <c r="C618">
         <f ca="1"/>
@@ -40114,7 +40165,7 @@
       </c>
       <c r="B619">
         <f t="shared" ca="1" si="36"/>
-        <v>189.74518918239642</v>
+        <v>189.70235386736348</v>
       </c>
       <c r="C619">
         <f ca="1"/>
@@ -40155,7 +40206,7 @@
       </c>
       <c r="B620">
         <f t="shared" ca="1" si="36"/>
-        <v>195.51557850885325</v>
+        <v>195.47144051813333</v>
       </c>
       <c r="C620">
         <f ca="1"/>
@@ -40196,7 +40247,7 @@
       </c>
       <c r="B621">
         <f t="shared" ca="1" si="36"/>
-        <v>201.30802023718255</v>
+        <v>201.26257459240665</v>
       </c>
       <c r="C621">
         <f ca="1"/>
@@ -40237,7 +40288,7 @@
       </c>
       <c r="B622">
         <f t="shared" ca="1" si="36"/>
-        <v>207.01441648298712</v>
+        <v>206.96768260907643</v>
       </c>
       <c r="C622">
         <f ca="1"/>
@@ -40278,7 +40329,7 @@
       </c>
       <c r="B623">
         <f t="shared" ca="1" si="36"/>
-        <v>213.89440709961593</v>
+        <v>213.84612005554712</v>
       </c>
       <c r="C623">
         <f ca="1"/>
@@ -40319,7 +40370,7 @@
       </c>
       <c r="B624">
         <f t="shared" ca="1" si="36"/>
-        <v>220.89286737875429</v>
+        <v>220.84300041978966</v>
       </c>
       <c r="C624">
         <f ca="1"/>
@@ -40360,7 +40411,7 @@
       </c>
       <c r="B625">
         <f t="shared" ca="1" si="36"/>
-        <v>227.79279454015315</v>
+        <v>227.74136991031983</v>
       </c>
       <c r="C625">
         <f ca="1"/>
@@ -40401,7 +40452,7 @@
       </c>
       <c r="B626">
         <f t="shared" ca="1" si="36"/>
-        <v>226.59564829533622</v>
+        <v>226.54449392340382</v>
       </c>
       <c r="C626">
         <f ca="1"/>
@@ -40442,7 +40493,7 @@
       </c>
       <c r="B627">
         <f t="shared" ca="1" si="36"/>
-        <v>224.90259123791446</v>
+        <v>224.85181907663377</v>
       </c>
       <c r="C627">
         <f ca="1"/>
@@ -40483,7 +40534,7 @@
       </c>
       <c r="B628">
         <f t="shared" ca="1" si="36"/>
-        <v>222.55712595591072</v>
+        <v>222.50688328760262</v>
       </c>
       <c r="C628">
         <f ca="1"/>
@@ -40524,7 +40575,7 @@
       </c>
       <c r="B629">
         <f t="shared" ca="1" si="36"/>
-        <v>219.51478757005719</v>
+        <v>219.46523171506834</v>
       </c>
       <c r="C629">
         <f ca="1"/>
@@ -40565,7 +40616,7 @@
       </c>
       <c r="B630">
         <f t="shared" ca="1" si="36"/>
-        <v>215.46945095953788</v>
+        <v>215.42080834650721</v>
       </c>
       <c r="C630">
         <f ca="1"/>
@@ -40606,7 +40657,7 @@
       </c>
       <c r="B631">
         <f t="shared" ca="1" si="36"/>
-        <v>210.74849367449048</v>
+        <v>210.70091682599084</v>
       </c>
       <c r="C631">
         <f ca="1"/>
@@ -40647,7 +40698,7 @@
       </c>
       <c r="B632">
         <f t="shared" ca="1" si="36"/>
-        <v>208.92404466151598</v>
+        <v>208.87687968563651</v>
       </c>
       <c r="C632">
         <f ca="1"/>
@@ -40688,7 +40739,7 @@
       </c>
       <c r="B633">
         <f t="shared" ca="1" si="36"/>
-        <v>206.92328634248955</v>
+        <v>206.87657304137068</v>
       </c>
       <c r="C633">
         <f ca="1"/>
@@ -40729,7 +40780,7 @@
       </c>
       <c r="B634">
         <f t="shared" ca="1" si="36"/>
-        <v>204.30329154588799</v>
+        <v>204.25716971326949</v>
       </c>
       <c r="C634">
         <f ca="1"/>
@@ -40770,7 +40821,7 @@
       </c>
       <c r="B635">
         <f t="shared" ca="1" si="36"/>
-        <v>198.01945996018304</v>
+        <v>197.97475671375767</v>
       </c>
       <c r="C635">
         <f ca="1"/>
@@ -40811,7 +40862,7 @@
       </c>
       <c r="B636">
         <f t="shared" ca="1" si="36"/>
-        <v>192.27285070678522</v>
+        <v>192.22944476765289</v>
       </c>
       <c r="C636">
         <f ca="1"/>
@@ -40852,7 +40903,7 @@
       </c>
       <c r="B637">
         <f t="shared" ca="1" si="36"/>
-        <v>186.94406851130475</v>
+        <v>186.90186555426155</v>
       </c>
       <c r="C637">
         <f ca="1"/>
@@ -40893,7 +40944,7 @@
       </c>
       <c r="B638">
         <f t="shared" ca="1" si="36"/>
-        <v>186.78934365724098</v>
+        <v>186.74717562960964</v>
       </c>
       <c r="C638">
         <f ca="1"/>
@@ -40934,7 +40985,7 @@
       </c>
       <c r="B639">
         <f t="shared" ca="1" si="36"/>
-        <v>187.02259497313216</v>
+        <v>186.98037428860007</v>
       </c>
       <c r="C639">
         <f ca="1"/>
@@ -40975,7 +41026,7 @@
       </c>
       <c r="B640">
         <f t="shared" ca="1" si="36"/>
-        <v>187.78381026577776</v>
+        <v>187.74141773553507</v>
       </c>
       <c r="C640">
         <f ca="1"/>
@@ -41016,7 +41067,7 @@
       </c>
       <c r="B641">
         <f t="shared" ca="1" si="36"/>
-        <v>189.10893843940065</v>
+        <v>189.06624675910822</v>
       </c>
       <c r="C641">
         <f ca="1"/>
@@ -41057,7 +41108,7 @@
       </c>
       <c r="B642">
         <f t="shared" ref="B642:B669" ca="1" si="40">F642*$C$669/C642</f>
-        <v>190.89871501048412</v>
+        <v>190.85561928493718</v>
       </c>
       <c r="C642">
         <f ca="1"/>
@@ -41098,7 +41149,7 @@
       </c>
       <c r="B643">
         <f t="shared" ca="1" si="40"/>
-        <v>192.4771789450146</v>
+        <v>192.43372687841787</v>
       </c>
       <c r="C643">
         <f ca="1"/>
@@ -41139,7 +41190,7 @@
       </c>
       <c r="B644">
         <f t="shared" ca="1" si="40"/>
-        <v>193.29760766869651</v>
+        <v>193.25397038885151</v>
       </c>
       <c r="C644">
         <f ca="1"/>
@@ -41180,7 +41231,7 @@
       </c>
       <c r="B645">
         <f t="shared" ca="1" si="40"/>
-        <v>193.47674538933421</v>
+        <v>193.4330676688291</v>
       </c>
       <c r="C645">
         <f ca="1"/>
@@ -41221,7 +41272,7 @@
       </c>
       <c r="B646">
         <f t="shared" ca="1" si="40"/>
-        <v>193.83492748248059</v>
+        <v>193.79116890172884</v>
       </c>
       <c r="C646">
         <f ca="1"/>
@@ -41262,7 +41313,7 @@
       </c>
       <c r="B647">
         <f t="shared" ca="1" si="40"/>
-        <v>196.52505880937287</v>
+        <v>196.4806929266739</v>
       </c>
       <c r="C647">
         <f ca="1"/>
@@ -41303,7 +41354,7 @@
       </c>
       <c r="B648">
         <f t="shared" ca="1" si="40"/>
-        <v>199.11008125016633</v>
+        <v>199.06513179403871</v>
       </c>
       <c r="C648">
         <f ca="1"/>
@@ -41344,7 +41395,7 @@
       </c>
       <c r="B649">
         <f t="shared" ca="1" si="40"/>
-        <v>201.54804126516265</v>
+        <v>201.50254143521144</v>
       </c>
       <c r="C649">
         <f ca="1"/>
@@ -41376,7 +41427,7 @@
       </c>
       <c r="J649">
         <f ca="1"/>
-        <v>74.098770000000002</v>
+        <v>74.751050000000006</v>
       </c>
     </row>
     <row r="650" spans="1:10" x14ac:dyDescent="0.25">
@@ -41385,11 +41436,11 @@
       </c>
       <c r="B650">
         <f t="shared" ca="1" si="40"/>
-        <v>200.49721402648211</v>
+        <v>200.51408739814269</v>
       </c>
       <c r="C650">
         <f ca="1"/>
-        <v>309.79399999999998</v>
+        <v>309.69799999999998</v>
       </c>
       <c r="D650">
         <f ca="1"/>
@@ -41405,11 +41456,11 @@
       </c>
       <c r="G650">
         <f t="shared" ca="1" si="43"/>
-        <v>3.4301261599751776E-3</v>
+        <v>3.1191798791843084E-3</v>
       </c>
       <c r="H650">
         <f t="shared" ca="1" si="42"/>
-        <v>-4.6792826641844313E-5</v>
+        <v>2.6415345414902485E-4</v>
       </c>
       <c r="I650">
         <f ca="1"/>
@@ -41417,7 +41468,7 @@
       </c>
       <c r="J650">
         <f ca="1"/>
-        <v>73.879400000000004</v>
+        <v>74.529740000000004</v>
       </c>
     </row>
     <row r="651" spans="1:10" x14ac:dyDescent="0.25">
@@ -41426,11 +41477,11 @@
       </c>
       <c r="B651">
         <f t="shared" ca="1" si="40"/>
-        <v>199.34517994829946</v>
+        <v>199.33542717063224</v>
       </c>
       <c r="C651">
         <f ca="1"/>
-        <v>311.02199999999999</v>
+        <v>310.96699999999998</v>
       </c>
       <c r="D651">
         <f ca="1"/>
@@ -41446,11 +41497,11 @@
       </c>
       <c r="G651">
         <f t="shared" ca="1" si="43"/>
-        <v>3.9639244142881669E-3</v>
+        <v>4.0975401843086345E-3</v>
       </c>
       <c r="H651">
         <f t="shared" ca="1" si="42"/>
-        <v>-4.5559108095483353E-4</v>
+        <v>-5.8920685097530118E-4</v>
       </c>
       <c r="I651">
         <f ca="1"/>
@@ -41458,7 +41509,7 @@
       </c>
       <c r="J651">
         <f ca="1"/>
-        <v>73.605900000000005</v>
+        <v>74.253839999999997</v>
       </c>
     </row>
     <row r="652" spans="1:10" x14ac:dyDescent="0.25">
@@ -41467,11 +41518,11 @@
       </c>
       <c r="B652">
         <f t="shared" ca="1" si="40"/>
-        <v>198.29300835931264</v>
+        <v>198.09718257055496</v>
       </c>
       <c r="C652">
         <f ca="1"/>
-        <v>312.10700000000003</v>
+        <v>312.34500000000003</v>
       </c>
       <c r="D652">
         <f ca="1"/>
@@ -41487,11 +41538,11 @@
       </c>
       <c r="G652">
         <f t="shared" ca="1" si="43"/>
-        <v>3.4884992058441533E-3</v>
+        <v>4.4313383735252732E-3</v>
       </c>
       <c r="H652">
         <f t="shared" ca="1" si="42"/>
-        <v>1.9834127489180061E-5</v>
+        <v>-9.230050401919398E-4</v>
       </c>
       <c r="I652">
         <f ca="1"/>
@@ -41499,7 +41550,7 @@
       </c>
       <c r="J652">
         <f ca="1"/>
-        <v>73.312960000000004</v>
+        <v>74.362930000000006</v>
       </c>
     </row>
     <row r="653" spans="1:10" x14ac:dyDescent="0.25">
@@ -41508,11 +41559,11 @@
       </c>
       <c r="B653">
         <f t="shared" ca="1" si="40"/>
-        <v>199.56634012318855</v>
+        <v>199.51682585624698</v>
       </c>
       <c r="C653">
         <f ca="1"/>
-        <v>313.01600000000002</v>
+        <v>313.02300000000002</v>
       </c>
       <c r="D653">
         <f ca="1"/>
@@ -41528,11 +41579,11 @@
       </c>
       <c r="G653">
         <f t="shared" ca="1" si="43"/>
-        <v>2.9124627131080771E-3</v>
+        <v>2.1706766556210955E-3</v>
       </c>
       <c r="H653">
         <f t="shared" ca="1" si="42"/>
-        <v>8.7087062022525629E-4</v>
+        <v>1.612656677712238E-3</v>
       </c>
       <c r="I653">
         <f ca="1"/>
@@ -41540,7 +41591,7 @@
       </c>
       <c r="J653">
         <f ca="1"/>
-        <v>73.424239999999998</v>
+        <v>74.475790000000003</v>
       </c>
     </row>
     <row r="654" spans="1:10" x14ac:dyDescent="0.25">
@@ -41549,11 +41600,11 @@
       </c>
       <c r="B654">
         <f t="shared" ca="1" si="40"/>
-        <v>201.335757424794</v>
+        <v>201.2678095952742</v>
       </c>
       <c r="C654">
         <f ca="1"/>
-        <v>313.14</v>
+        <v>313.17500000000001</v>
       </c>
       <c r="D654">
         <f ca="1"/>
@@ -41569,11 +41620,11 @@
       </c>
       <c r="G654">
         <f t="shared" ca="1" si="43"/>
-        <v>3.9614588391634342E-4</v>
+        <v>4.8558732105941083E-4</v>
       </c>
       <c r="H654">
         <f t="shared" ca="1" si="42"/>
-        <v>3.3371874494169899E-3</v>
+        <v>3.2477460122739225E-3</v>
       </c>
       <c r="I654">
         <f ca="1"/>
@@ -41581,7 +41632,7 @@
       </c>
       <c r="J654">
         <f ca="1"/>
-        <v>73.697379999999995</v>
+        <v>74.752840000000006</v>
       </c>
     </row>
     <row r="655" spans="1:10" x14ac:dyDescent="0.25">
@@ -41590,11 +41641,11 @@
       </c>
       <c r="B655">
         <f t="shared" ca="1" si="40"/>
-        <v>203.19004071778264</v>
+        <v>203.20062726006569</v>
       </c>
       <c r="C655">
         <f ca="1"/>
-        <v>313.13099999999997</v>
+        <v>313.04399999999998</v>
       </c>
       <c r="D655">
         <f ca="1"/>
@@ -41610,11 +41661,11 @@
       </c>
       <c r="G655">
         <f t="shared" ca="1" si="43"/>
-        <v>-2.8741138149102063E-5</v>
+        <v>-4.1829647960411886E-4</v>
       </c>
       <c r="H655">
         <f t="shared" ca="1" si="42"/>
-        <v>3.6204078048157687E-3</v>
+        <v>4.0099631462707855E-3</v>
       </c>
       <c r="I655">
         <f ca="1"/>
@@ -41622,7 +41673,7 @@
       </c>
       <c r="J655">
         <f ca="1"/>
-        <v>74.067319999999995</v>
+        <v>75.128079999999997</v>
       </c>
     </row>
     <row r="656" spans="1:10" x14ac:dyDescent="0.25">
@@ -41631,11 +41682,11 @@
       </c>
       <c r="B656">
         <f t="shared" ca="1" si="40"/>
-        <v>204.11472072865044</v>
+        <v>204.0666890859747</v>
       </c>
       <c r="C656">
         <f ca="1"/>
-        <v>313.56599999999997</v>
+        <v>313.56900000000002</v>
       </c>
       <c r="D656">
         <f ca="1"/>
@@ -41651,11 +41702,11 @@
       </c>
       <c r="G656">
         <f t="shared" ca="1" si="43"/>
-        <v>1.389194937581939E-3</v>
+        <v>1.6770805381991494E-3</v>
       </c>
       <c r="H656">
         <f t="shared" ca="1" si="42"/>
-        <v>2.1524717290847279E-3</v>
+        <v>1.8645861284675175E-3</v>
       </c>
       <c r="I656">
         <f ca="1"/>
@@ -41663,7 +41714,7 @@
       </c>
       <c r="J656">
         <f ca="1"/>
-        <v>74.469329999999999</v>
+        <v>75.535849999999996</v>
       </c>
     </row>
     <row r="657" spans="1:10" x14ac:dyDescent="0.25">
@@ -41672,11 +41723,11 @@
       </c>
       <c r="B657">
         <f t="shared" ca="1" si="40"/>
-        <v>204.95198627324268</v>
+        <v>204.95073616037595</v>
       </c>
       <c r="C657">
         <f ca="1"/>
-        <v>314.13099999999997</v>
+        <v>314.06200000000001</v>
       </c>
       <c r="D657">
         <f ca="1"/>
@@ -41692,11 +41743,11 @@
       </c>
       <c r="G657">
         <f t="shared" ca="1" si="43"/>
-        <v>1.8018535172819039E-3</v>
+        <v>1.5722217438585151E-3</v>
       </c>
       <c r="H657">
         <f t="shared" ca="1" si="42"/>
-        <v>1.4231464827180961E-3</v>
+        <v>1.6527782561414849E-3</v>
       </c>
       <c r="I657">
         <f ca="1"/>
@@ -41704,7 +41755,7 @@
       </c>
       <c r="J657">
         <f ca="1"/>
-        <v>74.896339999999995</v>
+        <v>75.968969999999999</v>
       </c>
     </row>
     <row r="658" spans="1:10" x14ac:dyDescent="0.25">
@@ -41713,11 +41764,11 @@
       </c>
       <c r="B658">
         <f t="shared" ca="1" si="40"/>
-        <v>205.68493757364595</v>
+        <v>205.71625563971887</v>
       </c>
       <c r="C658">
         <f ca="1"/>
-        <v>314.851</v>
+        <v>314.73200000000003</v>
       </c>
       <c r="D658">
         <f ca="1"/>
@@ -41733,11 +41784,11 @@
       </c>
       <c r="G658">
         <f t="shared" ca="1" si="43"/>
-        <v>2.2920373984103293E-3</v>
+        <v>2.1333367296902939E-3</v>
       </c>
       <c r="H658">
         <f t="shared" ca="1" si="42"/>
-        <v>8.0796260158967062E-4</v>
+        <v>9.6666327030970603E-4</v>
       </c>
       <c r="I658">
         <f ca="1"/>
@@ -41745,7 +41796,7 @@
       </c>
       <c r="J658">
         <f ca="1"/>
-        <v>75.263159999999999</v>
+        <v>76.341049999999996</v>
       </c>
     </row>
     <row r="659" spans="1:10" x14ac:dyDescent="0.25">
@@ -41754,11 +41805,11 @@
       </c>
       <c r="B659">
         <f t="shared" ca="1" si="40"/>
-        <v>208.60177168498302</v>
+        <v>208.51040889519726</v>
       </c>
       <c r="C659">
         <f ca="1"/>
-        <v>315.56400000000002</v>
+        <v>315.63099999999997</v>
       </c>
       <c r="D659">
         <f ca="1"/>
@@ -41774,11 +41825,11 @@
       </c>
       <c r="G659">
         <f t="shared" ca="1" si="43"/>
-        <v>2.264563237849071E-3</v>
+        <v>2.8563984596416958E-3</v>
       </c>
       <c r="H659">
         <f t="shared" ca="1" si="42"/>
-        <v>1.1521034288175958E-3</v>
+        <v>5.60268207024971E-4</v>
       </c>
       <c r="I659">
         <f ca="1"/>
@@ -41786,7 +41837,7 @@
       </c>
       <c r="J659">
         <f ca="1"/>
-        <v>75.665589999999995</v>
+        <v>76.74924</v>
       </c>
     </row>
     <row r="660" spans="1:10" x14ac:dyDescent="0.25">
@@ -41795,11 +41846,11 @@
       </c>
       <c r="B660">
         <f t="shared" ca="1" si="40"/>
-        <v>211.39049477166935</v>
+        <v>211.29002543218925</v>
       </c>
       <c r="C660">
         <f ca="1"/>
-        <v>316.44900000000001</v>
+        <v>316.52800000000002</v>
       </c>
       <c r="D660">
         <f ca="1"/>
@@ -41815,11 +41866,11 @@
       </c>
       <c r="G660">
         <f t="shared" ca="1" si="43"/>
-        <v>2.8045024147240749E-3</v>
+        <v>2.8419261732848256E-3</v>
       </c>
       <c r="H660">
         <f t="shared" ca="1" si="42"/>
-        <v>8.2883091860925856E-4</v>
+        <v>7.9140716004850791E-4</v>
       </c>
       <c r="I660">
         <f ca="1"/>
@@ -41827,7 +41878,7 @@
       </c>
       <c r="J660">
         <f ca="1"/>
-        <v>76.195840000000004</v>
+        <v>77.287090000000006</v>
       </c>
     </row>
     <row r="661" spans="1:10" x14ac:dyDescent="0.25">
@@ -41836,11 +41887,11 @@
       </c>
       <c r="B661">
         <f t="shared" ca="1" si="40"/>
-        <v>213.98227308935992</v>
+        <v>213.93329262225919</v>
       </c>
       <c r="C661">
         <f ca="1"/>
-        <v>317.60300000000001</v>
+        <v>317.60399999999998</v>
       </c>
       <c r="D661">
         <f ca="1"/>
@@ -41856,11 +41907,11 @@
       </c>
       <c r="G661">
         <f t="shared" ca="1" si="43"/>
-        <v>3.6467171645351293E-3</v>
+        <v>3.399383308901438E-3</v>
       </c>
       <c r="H661">
         <f t="shared" ca="1" si="42"/>
-        <v>1.161616879820403E-5</v>
+        <v>2.5895002443189529E-4</v>
       </c>
       <c r="I661">
         <f ca="1"/>
@@ -41868,7 +41919,7 @@
       </c>
       <c r="J661">
         <f ca="1"/>
-        <v>76.657859999999999</v>
+        <v>77.75573</v>
       </c>
     </row>
     <row r="662" spans="1:10" x14ac:dyDescent="0.25">
@@ -41877,11 +41928,11 @@
       </c>
       <c r="B662">
         <f t="shared" ca="1" si="40"/>
-        <v>215.19022634061034</v>
+        <v>215.22596022407126</v>
       </c>
       <c r="C662">
         <f ca="1"/>
-        <v>319.08600000000001</v>
+        <v>318.96100000000001</v>
       </c>
       <c r="D662">
         <f ca="1"/>
@@ -41897,11 +41948,11 @@
       </c>
       <c r="G662">
         <f t="shared" ca="1" si="43"/>
-        <v>4.6693513600313263E-3</v>
+        <v>4.2726162139017365E-3</v>
       </c>
       <c r="H662">
         <f t="shared" ca="1" si="42"/>
-        <v>-8.1101802669799293E-4</v>
+        <v>-4.1428288056840311E-4</v>
       </c>
       <c r="I662">
         <f ca="1"/>
@@ -41909,7 +41960,7 @@
       </c>
       <c r="J662">
         <f ca="1"/>
-        <v>76.604759999999999</v>
+        <v>77.701859999999996</v>
       </c>
     </row>
     <row r="663" spans="1:10" x14ac:dyDescent="0.25">
@@ -41918,11 +41969,11 @@
       </c>
       <c r="B663">
         <f t="shared" ca="1" si="40"/>
-        <v>216.92430139279182</v>
+        <v>216.94045827523863</v>
       </c>
       <c r="C663">
         <f ca="1"/>
-        <v>319.77499999999998</v>
+        <v>319.67899999999997</v>
       </c>
       <c r="D663">
         <f ca="1"/>
@@ -41938,11 +41989,11 @@
       </c>
       <c r="G663">
         <f t="shared" ca="1" si="43"/>
-        <v>2.159292479143371E-3</v>
+        <v>2.2510589068882592E-3</v>
       </c>
       <c r="H663">
         <f t="shared" ca="1" si="42"/>
-        <v>1.549040854189962E-3</v>
+        <v>1.4572744264450739E-3</v>
       </c>
       <c r="I663">
         <f ca="1"/>
@@ -41950,7 +42001,7 @@
       </c>
       <c r="J663">
         <f ca="1"/>
-        <v>76.709479999999999</v>
+        <v>77.808080000000004</v>
       </c>
     </row>
     <row r="664" spans="1:10" x14ac:dyDescent="0.25">
@@ -41959,11 +42010,11 @@
       </c>
       <c r="B664">
         <f t="shared" ca="1" si="40"/>
-        <v>219.23171678425604</v>
+        <v>219.06570598996197</v>
       </c>
       <c r="C664">
         <f ca="1"/>
-        <v>319.61500000000001</v>
+        <v>319.78500000000003</v>
       </c>
       <c r="D664">
         <f ca="1"/>
@@ -41979,11 +42030,11 @@
       </c>
       <c r="G664">
         <f t="shared" ca="1" si="43"/>
-        <v>-5.0035180986618411E-4</v>
+        <v>3.315826188146076E-4</v>
       </c>
       <c r="H664">
         <f t="shared" ca="1" si="42"/>
-        <v>4.06701847653285E-3</v>
+        <v>3.2350840478520587E-3</v>
       </c>
       <c r="I664">
         <f ca="1"/>
@@ -41991,7 +42042,7 @@
       </c>
       <c r="J664">
         <f ca="1"/>
-        <v>76.979969999999994</v>
+        <v>78.082449999999994</v>
       </c>
     </row>
     <row r="665" spans="1:10" x14ac:dyDescent="0.25">
@@ -42000,11 +42051,11 @@
       </c>
       <c r="B665">
         <f t="shared" ca="1" si="40"/>
-        <v>220.71368457853214</v>
+        <v>220.67694763370196</v>
       </c>
       <c r="C665">
         <f ca="1"/>
-        <v>320.32100000000003</v>
+        <v>320.30200000000002</v>
       </c>
       <c r="D665">
         <f ca="1"/>
@@ -42020,11 +42071,11 @@
       </c>
       <c r="G665">
         <f t="shared" ca="1" si="43"/>
-        <v>2.2089075919466961E-3</v>
+        <v>1.6167112278562268E-3</v>
       </c>
       <c r="H665">
         <f t="shared" ca="1" si="42"/>
-        <v>1.3577590747199703E-3</v>
+        <v>1.9499554388104396E-3</v>
       </c>
       <c r="I665">
         <f ca="1"/>
@@ -42032,7 +42083,7 @@
       </c>
       <c r="J665">
         <f ca="1"/>
-        <v>77.145669999999996</v>
+        <v>78.250529999999998</v>
       </c>
     </row>
     <row r="666" spans="1:10" x14ac:dyDescent="0.25">
@@ -42041,11 +42092,11 @@
       </c>
       <c r="B666">
         <f t="shared" ca="1" si="40"/>
-        <v>222.49893294067004</v>
+        <v>222.42095109172851</v>
       </c>
       <c r="C666">
         <f ca="1"/>
-        <v>320.58</v>
+        <v>320.62</v>
       </c>
       <c r="D666">
         <f ca="1"/>
@@ -42061,11 +42112,11 @@
       </c>
       <c r="G666">
         <f t="shared" ca="1" si="43"/>
-        <v>8.0856390932826372E-4</v>
+        <v>9.9281303270037924E-4</v>
       </c>
       <c r="H666">
         <f t="shared" ca="1" si="42"/>
-        <v>2.8747694240050699E-3</v>
+        <v>2.6905203006329544E-3</v>
       </c>
       <c r="I666">
         <f ca="1"/>
@@ -42073,7 +42124,7 @@
       </c>
       <c r="J666">
         <f ca="1"/>
-        <v>77.388750000000002</v>
+        <v>78.497079999999997</v>
       </c>
     </row>
     <row r="667" spans="1:10" x14ac:dyDescent="0.25">
@@ -42082,11 +42133,11 @@
       </c>
       <c r="B667">
         <f t="shared" ca="1" si="40"/>
-        <v>223.82018948678069</v>
+        <v>223.81491197287167</v>
       </c>
       <c r="C667">
         <f ca="1"/>
-        <v>321.5</v>
+        <v>321.435</v>
       </c>
       <c r="D667">
         <f ca="1"/>
@@ -42102,11 +42153,11 @@
       </c>
       <c r="G667">
         <f t="shared" ca="1" si="43"/>
-        <v>2.869798490236386E-3</v>
+        <v>2.5419499719294691E-3</v>
       </c>
       <c r="H667">
         <f t="shared" ca="1" si="42"/>
-        <v>7.8020150976361403E-4</v>
+        <v>1.1080500280705309E-3</v>
       </c>
       <c r="I667">
         <f ca="1"/>
@@ -42114,7 +42165,7 @@
       </c>
       <c r="J667">
         <f ca="1"/>
-        <v>77.528289999999998</v>
+        <v>78.638620000000003</v>
       </c>
     </row>
     <row r="668" spans="1:10" x14ac:dyDescent="0.25">
@@ -42123,11 +42174,11 @@
       </c>
       <c r="B668">
         <f t="shared" ca="1" si="40"/>
-        <v>227.63728620565479</v>
+        <v>227.559759225748</v>
       </c>
       <c r="C668">
         <f ca="1"/>
-        <v>322.13200000000001</v>
+        <v>322.16899999999998</v>
       </c>
       <c r="D668">
         <f ca="1"/>
@@ -42143,11 +42194,11 @@
       </c>
       <c r="G668">
         <f t="shared" ca="1" si="43"/>
-        <v>1.9657853810264303E-3</v>
+        <v>2.2835098853577485E-3</v>
       </c>
       <c r="H668">
         <f t="shared" ca="1" si="42"/>
-        <v>1.692547952306903E-3</v>
+        <v>1.3748234479755849E-3</v>
       </c>
       <c r="I668">
         <f ca="1"/>
@@ -42155,7 +42206,7 @@
       </c>
       <c r="J668">
         <f ca="1"/>
-        <v>77.788380000000004</v>
+        <v>78.902439999999999</v>
       </c>
     </row>
     <row r="669" spans="1:10" x14ac:dyDescent="0.25">
@@ -42168,7 +42219,7 @@
       </c>
       <c r="C669">
         <f ca="1"/>
-        <v>323.36399999999998</v>
+        <v>323.291</v>
       </c>
       <c r="D669">
         <f ca="1"/>
@@ -42184,11 +42235,11 @@
       </c>
       <c r="G669">
         <f t="shared" ca="1" si="43"/>
-        <v>3.8245191412216162E-3</v>
+        <v>3.4826442022666271E-3</v>
       </c>
       <c r="H669">
         <f t="shared" ca="1" si="42"/>
-        <v>-2.7451914122161641E-4</v>
+        <v>6.7355797733372694E-5</v>
       </c>
       <c r="I669">
         <f ca="1"/>
@@ -42196,7 +42247,7 @@
       </c>
       <c r="J669">
         <f ca="1"/>
-        <v>77.941450000000003</v>
+        <v>79.057699999999997</v>
       </c>
     </row>
     <row r="670" spans="1:10" x14ac:dyDescent="0.25">
@@ -42205,7 +42256,7 @@
       </c>
       <c r="C670">
         <f ca="1"/>
-        <v>324.36799999999999</v>
+        <v>324.245</v>
       </c>
       <c r="D670">
         <f ca="1"/>
@@ -42221,7 +42272,7 @@
       </c>
       <c r="J670">
         <f ca="1"/>
-        <v>78.118650000000002</v>
+        <v>79.237440000000007</v>
       </c>
     </row>
     <row r="671" spans="1:10" x14ac:dyDescent="0.25">
@@ -42236,13 +42287,17 @@
         <f ca="1"/>
         <v>4.0599999999999997E-2</v>
       </c>
+      <c r="F671">
+        <f ca="1"/>
+        <v>241.20332999999999</v>
+      </c>
       <c r="I671">
         <f ca="1"/>
         <v>1.67E-2</v>
       </c>
       <c r="J671">
         <f ca="1"/>
-        <v>78.165539999999993</v>
+        <v>79.486620000000002</v>
       </c>
     </row>
     <row r="672" spans="1:10" x14ac:dyDescent="0.25">
@@ -42251,19 +42306,23 @@
       </c>
       <c r="C672">
         <f ca="1"/>
-        <v>325.03100000000001</v>
+        <v>325.06299999999999</v>
       </c>
       <c r="D672">
         <f ca="1"/>
         <v>4.0899999999999999E-2</v>
       </c>
+      <c r="F672">
+        <f ca="1"/>
+        <v>247.15666999999999</v>
+      </c>
       <c r="I672">
         <f ca="1"/>
-        <v>1.6199999999999999E-2</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="J672">
         <f ca="1"/>
-        <v>78.574759999999998</v>
+        <v>80.104669999999999</v>
       </c>
     </row>
     <row r="673" spans="1:10" x14ac:dyDescent="0.25">
@@ -42272,32 +42331,111 @@
       </c>
       <c r="C673">
         <f ca="1"/>
-        <v>326.02999999999997</v>
+        <v>326.03100000000001</v>
       </c>
       <c r="D673">
         <f ca="1"/>
         <v>4.1399999999999999E-2</v>
       </c>
+      <c r="F673">
+        <f ca="1"/>
+        <v>253.11</v>
+      </c>
       <c r="I673">
         <f ca="1"/>
-        <v>1.55E-2</v>
+        <v>1.5900000000000001E-2</v>
       </c>
       <c r="J673">
         <f ca="1"/>
-        <v>78.853700000000003</v>
+        <v>80.472300000000004</v>
       </c>
     </row>
     <row r="674" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A674" t="str">
         <v>2026-01-31</v>
       </c>
+      <c r="C674">
+        <f ca="1"/>
+        <v>326.58800000000002</v>
+      </c>
       <c r="D674">
         <f ca="1"/>
-        <v>4.1799999999999997E-2</v>
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="F674">
+        <f ca="1"/>
+        <v>261.30667</v>
       </c>
       <c r="I674">
         <f ca="1"/>
-        <v>1.49E-2</v>
+        <v>1.54E-2</v>
+      </c>
+      <c r="J674">
+        <f ca="1"/>
+        <v>80.266639999999995</v>
+      </c>
+    </row>
+    <row r="675" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A675" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="C675">
+        <f ca="1"/>
+        <v>327.45999999999998</v>
+      </c>
+      <c r="D675">
+        <f ca="1"/>
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="F675">
+        <f ca="1"/>
+        <v>269.50333000000001</v>
+      </c>
+      <c r="I675">
+        <f ca="1"/>
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="J675">
+        <f ca="1"/>
+        <v>79.980410000000006</v>
+      </c>
+    </row>
+    <row r="676" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A676" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="C676">
+        <f ca="1"/>
+        <v>330.29300000000001</v>
+      </c>
+      <c r="D676">
+        <f ca="1"/>
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="F676">
+        <f ca="1"/>
+        <v>277.7</v>
+      </c>
+      <c r="I676">
+        <f ca="1"/>
+        <v>1.67E-2</v>
+      </c>
+      <c r="J676">
+        <f ca="1"/>
+        <v>79.883359999999996</v>
+      </c>
+    </row>
+    <row r="677" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A677" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="D677">
+        <f ca="1"/>
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I677">
+        <f ca="1"/>
+        <v>1.6400000000000001E-2</v>
       </c>
     </row>
   </sheetData>

--- a/ecy4.xlsx
+++ b/ecy4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://perissosprivatewealth-my.sharepoint.com/personal/brandon_perissosprivatewealth_com/Documents/1 Perissos Private Wealth Management/5 Python/01_Active_Strategies/Wealth Utility API/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="418" documentId="13_ncr:1_{A317B0E7-1C5D-450E-A529-DF31A54AA737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E0B27F3-1BEB-4DCC-822C-B34D4988B4E8}"/>
+  <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{A317B0E7-1C5D-450E-A529-DF31A54AA737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A348269F-7370-4258-894B-78847219CA50}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="15840" windowWidth="28800" windowHeight="15840" activeTab="1" xr2:uid="{7D23DFD4-FCD3-40E1-B8A0-B864FE11F7D6}"/>
+    <workbookView xWindow="28695" yWindow="15840" windowWidth="29010" windowHeight="15945" activeTab="1" xr2:uid="{7D23DFD4-FCD3-40E1-B8A0-B864FE11F7D6}"/>
   </bookViews>
   <sheets>
     <sheet name="ecy" sheetId="2" r:id="rId1"/>
@@ -945,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173E5D82-F300-41D6-89B7-1A964CE4FD56}">
-  <dimension ref="A1:F557"/>
+  <dimension ref="A1:F561"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -977,15 +977,15 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="array" ref="A2:A557">_xll.YCDS("I:SP500ECY",,"1980-01-01")</f>
+        <f t="array" ref="A2:A561">_xll.YCDS("I:SP500ECY",,"1980-01-01")</f>
         <v>1980-01-31</v>
       </c>
       <c r="B2">
-        <f t="array" aca="1" ref="B2:B557" ca="1">_xll.YCS("I:SP500ECY",,"1980-01-01")</f>
+        <f t="array" aca="1" ref="B2:B561" ca="1">_xll.YCS("I:SP500ECY",,"1980-01-01")</f>
         <v>7.9799999999999996E-2</v>
       </c>
       <c r="C2">
-        <f t="array" aca="1" ref="C2:C557" ca="1">_xll.YCS("I:usltir",,"1980-01-01")</f>
+        <f t="array" aca="1" ref="C2:C561" ca="1">_xll.YCS("I:usltir",,"1980-01-01")</f>
         <v>0.108</v>
       </c>
       <c r="D2">
@@ -993,7 +993,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="E2" s="1">
-        <f t="array" aca="1" ref="E2:E556" ca="1">_xll.YCS("I:us1mccpi",,"1980-01-01")</f>
+        <f t="array" aca="1" ref="E2:E560" ca="1">_xll.YCS("I:us1mccpi",,"1980-01-01")</f>
         <v>1.4E-2</v>
       </c>
       <c r="F2" s="1">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="B554">
         <f ca="1"/>
-        <v>1.54E-2</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="C554">
         <f ca="1"/>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="B555">
         <f ca="1"/>
-        <v>1.7000000000000001E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="C555">
         <f ca="1"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="B556">
         <f ca="1"/>
-        <v>1.67E-2</v>
+        <v>1.77E-2</v>
       </c>
       <c r="C556">
         <f ca="1"/>
@@ -14805,11 +14805,79 @@
       </c>
       <c r="B557">
         <f ca="1"/>
-        <v>1.6400000000000001E-2</v>
+        <v>1.66E-2</v>
       </c>
       <c r="C557">
         <f ca="1"/>
-        <v>4.2999999999999997E-2</v>
+        <v>4.3200000000000002E-2</v>
+      </c>
+      <c r="E557" s="1">
+        <f ca="1"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A558" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="B558">
+        <f ca="1"/>
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="C558">
+        <f ca="1"/>
+        <v>4.48E-2</v>
+      </c>
+      <c r="E558" s="1">
+        <f ca="1"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A559" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="B559">
+        <f ca="1"/>
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="C559">
+        <f ca="1"/>
+        <v>4.4699999999999997E-2</v>
+      </c>
+      <c r="E559" s="1">
+        <f ca="1"/>
+        <v>-4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A560" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B560">
+        <f ca="1"/>
+        <v>1.18E-2</v>
+      </c>
+      <c r="C560">
+        <f ca="1"/>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="E560" s="1">
+        <f ca="1"/>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A561" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="B561">
+        <f ca="1"/>
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="C561">
+        <f ca="1"/>
+        <v>4.7500000000000001E-2</v>
       </c>
     </row>
   </sheetData>
@@ -14819,14 +14887,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA56A079-CA0B-477E-8FC4-5F43798C1EE5}">
-  <dimension ref="A1:J677"/>
+  <dimension ref="A1:J681"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14864,7 +14932,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="array" ref="A2:A677">_xll.YCDS("I:USLTIR",,"1970-01-31")</f>
+        <f t="array" ref="A2:A681">_xll.YCDS("I:USLTIR",,"1970-01-31")</f>
         <v>1970-01-31</v>
       </c>
       <c r="B2">
@@ -14872,11 +14940,11 @@
         <v>48.877504749340375</v>
       </c>
       <c r="C2">
-        <f t="array" aca="1" ref="C2:C676" ca="1">_xll.YCS("I:USCPI",,"1970-01-31")</f>
+        <f t="array" aca="1" ref="C2:C680" ca="1">_xll.YCS("I:USCPI",,"1970-01-31")</f>
         <v>37.9</v>
       </c>
       <c r="D2">
-        <f t="array" aca="1" ref="D2:D677" ca="1">_xll.YCS("I:USLTIR",,"1970-01-31")</f>
+        <f t="array" aca="1" ref="D2:D681" ca="1">_xll.YCS("I:USLTIR",,"1970-01-31")</f>
         <v>7.7899999999999997E-2</v>
       </c>
       <c r="E2">
@@ -14895,11 +14963,11 @@
         <v>1.0916666666666661E-3</v>
       </c>
       <c r="I2" s="2">
-        <f t="array" aca="1" ref="I2:I677" ca="1">_xll.YCS("I:SP500ECY",,"1970-01-31")</f>
+        <f t="array" aca="1" ref="I2:I681" ca="1">_xll.YCS("I:SP500ECY",,"1970-01-31")</f>
         <v>6.4000000000000003E-3</v>
       </c>
       <c r="J2" s="2">
-        <f t="array" aca="1" ref="J2:J676" ca="1">_xll.YCS("I:SP500RD", ,"1970-01-31")</f>
+        <f t="array" aca="1" ref="J2:J679" ca="1">_xll.YCS("I:SP500RD", ,"1970-01-31")</f>
         <v>21.813400000000001</v>
       </c>
     </row>
@@ -41107,7 +41175,7 @@
         <v>2023-05-31</v>
       </c>
       <c r="B642">
-        <f t="shared" ref="B642:B669" ca="1" si="40">F642*$C$669/C642</f>
+        <f t="shared" ref="B642:B680" ca="1" si="40">F642*$C$669/C642</f>
         <v>190.85561928493718</v>
       </c>
       <c r="C642">
@@ -41160,7 +41228,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="E643">
-        <f t="shared" ref="E643:E669" ca="1" si="41">D643/12</f>
+        <f t="shared" ref="E643:E681" ca="1" si="41">D643/12</f>
         <v>3.1249999999999997E-3</v>
       </c>
       <c r="F643">
@@ -41209,7 +41277,7 @@
         <v>182.09</v>
       </c>
       <c r="G644">
-        <f t="shared" ref="G644:G669" ca="1" si="43">C644/C643-1</f>
+        <f t="shared" ref="G644:G681" ca="1" si="43">C644/C643-1</f>
         <v>1.6968158395787025E-3</v>
       </c>
       <c r="H644">
@@ -41550,7 +41618,7 @@
       </c>
       <c r="J652">
         <f ca="1"/>
-        <v>74.362930000000006</v>
+        <v>75.993449999999996</v>
       </c>
     </row>
     <row r="653" spans="1:10" x14ac:dyDescent="0.25">
@@ -41591,7 +41659,7 @@
       </c>
       <c r="J653">
         <f ca="1"/>
-        <v>74.475790000000003</v>
+        <v>76.108800000000002</v>
       </c>
     </row>
     <row r="654" spans="1:10" x14ac:dyDescent="0.25">
@@ -41632,7 +41700,7 @@
       </c>
       <c r="J654">
         <f ca="1"/>
-        <v>74.752840000000006</v>
+        <v>76.391919999999999</v>
       </c>
     </row>
     <row r="655" spans="1:10" x14ac:dyDescent="0.25">
@@ -41673,7 +41741,7 @@
       </c>
       <c r="J655">
         <f ca="1"/>
-        <v>75.128079999999997</v>
+        <v>76.305400000000006</v>
       </c>
     </row>
     <row r="656" spans="1:10" x14ac:dyDescent="0.25">
@@ -41714,7 +41782,7 @@
       </c>
       <c r="J656">
         <f ca="1"/>
-        <v>75.535849999999996</v>
+        <v>76.719560000000001</v>
       </c>
     </row>
     <row r="657" spans="1:10" x14ac:dyDescent="0.25">
@@ -41755,7 +41823,7 @@
       </c>
       <c r="J657">
         <f ca="1"/>
-        <v>75.968969999999999</v>
+        <v>77.159469999999999</v>
       </c>
     </row>
     <row r="658" spans="1:10" x14ac:dyDescent="0.25">
@@ -41796,7 +41864,7 @@
       </c>
       <c r="J658">
         <f ca="1"/>
-        <v>76.341049999999996</v>
+        <v>77.537379999999999</v>
       </c>
     </row>
     <row r="659" spans="1:10" x14ac:dyDescent="0.25">
@@ -41837,7 +41905,7 @@
       </c>
       <c r="J659">
         <f ca="1"/>
-        <v>76.74924</v>
+        <v>77.95196</v>
       </c>
     </row>
     <row r="660" spans="1:10" x14ac:dyDescent="0.25">
@@ -41878,7 +41946,7 @@
       </c>
       <c r="J660">
         <f ca="1"/>
-        <v>77.287090000000006</v>
+        <v>78.498239999999996</v>
       </c>
     </row>
     <row r="661" spans="1:10" x14ac:dyDescent="0.25">
@@ -41919,7 +41987,7 @@
       </c>
       <c r="J661">
         <f ca="1"/>
-        <v>77.75573</v>
+        <v>78.974220000000003</v>
       </c>
     </row>
     <row r="662" spans="1:10" x14ac:dyDescent="0.25">
@@ -41960,7 +42028,7 @@
       </c>
       <c r="J662">
         <f ca="1"/>
-        <v>77.701859999999996</v>
+        <v>78.919510000000002</v>
       </c>
     </row>
     <row r="663" spans="1:10" x14ac:dyDescent="0.25">
@@ -42001,7 +42069,7 @@
       </c>
       <c r="J663">
         <f ca="1"/>
-        <v>77.808080000000004</v>
+        <v>79.0274</v>
       </c>
     </row>
     <row r="664" spans="1:10" x14ac:dyDescent="0.25">
@@ -42042,7 +42110,7 @@
       </c>
       <c r="J664">
         <f ca="1"/>
-        <v>78.082449999999994</v>
+        <v>79.306070000000005</v>
       </c>
     </row>
     <row r="665" spans="1:10" x14ac:dyDescent="0.25">
@@ -42083,7 +42151,7 @@
       </c>
       <c r="J665">
         <f ca="1"/>
-        <v>78.250529999999998</v>
+        <v>79.476780000000005</v>
       </c>
     </row>
     <row r="666" spans="1:10" x14ac:dyDescent="0.25">
@@ -42124,7 +42192,7 @@
       </c>
       <c r="J666">
         <f ca="1"/>
-        <v>78.497079999999997</v>
+        <v>79.727199999999996</v>
       </c>
     </row>
     <row r="667" spans="1:10" x14ac:dyDescent="0.25">
@@ -42165,7 +42233,7 @@
       </c>
       <c r="J667">
         <f ca="1"/>
-        <v>78.638620000000003</v>
+        <v>79.870949999999993</v>
       </c>
     </row>
     <row r="668" spans="1:10" x14ac:dyDescent="0.25">
@@ -42206,7 +42274,7 @@
       </c>
       <c r="J668">
         <f ca="1"/>
-        <v>78.902439999999999</v>
+        <v>80.138900000000007</v>
       </c>
     </row>
     <row r="669" spans="1:10" x14ac:dyDescent="0.25">
@@ -42238,7 +42306,7 @@
         <v>3.4826442022666271E-3</v>
       </c>
       <c r="H669">
-        <f t="shared" ca="1" si="42"/>
+        <f ca="1">E669-G669</f>
         <v>6.7355797733372694E-5</v>
       </c>
       <c r="I669">
@@ -42247,13 +42315,17 @@
       </c>
       <c r="J669">
         <f ca="1"/>
-        <v>79.057699999999997</v>
+        <v>80.296599999999998</v>
       </c>
     </row>
     <row r="670" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A670" t="str">
         <v>2025-09-30</v>
       </c>
+      <c r="B670">
+        <f t="shared" ca="1" si="40"/>
+        <v>234.55784283489336</v>
+      </c>
       <c r="C670">
         <f ca="1"/>
         <v>324.245</v>
@@ -42262,23 +42334,39 @@
         <f ca="1"/>
         <v>4.1200000000000001E-2</v>
       </c>
+      <c r="E670">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.4333333333333334E-3</v>
+      </c>
       <c r="F670">
         <f ca="1"/>
         <v>235.25</v>
       </c>
+      <c r="G670">
+        <f t="shared" ca="1" si="43"/>
+        <v>2.9509018191040681E-3</v>
+      </c>
+      <c r="H670">
+        <f t="shared" ref="H670:H680" ca="1" si="44">E670-G670</f>
+        <v>4.8243151422926525E-4</v>
+      </c>
       <c r="I670">
         <f ca="1"/>
         <v>1.6299999999999999E-2</v>
       </c>
       <c r="J670">
         <f ca="1"/>
-        <v>79.237440000000007</v>
+        <v>80.479150000000004</v>
       </c>
     </row>
     <row r="671" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A671" t="str">
         <v>2025-10-31</v>
       </c>
+      <c r="B671" t="e">
+        <f t="shared" ca="1" si="40"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="C671" t="str">
         <f ca="1"/>
         <v>ERR: NO DATA</v>
@@ -42287,9 +42375,21 @@
         <f ca="1"/>
         <v>4.0599999999999997E-2</v>
       </c>
+      <c r="E671">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.3833333333333332E-3</v>
+      </c>
       <c r="F671">
         <f ca="1"/>
-        <v>241.20332999999999</v>
+        <v>237.04467</v>
+      </c>
+      <c r="G671" t="e">
+        <f t="shared" ca="1" si="43"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H671" t="e">
+        <f t="shared" ca="1" si="44"/>
+        <v>#VALUE!</v>
       </c>
       <c r="I671">
         <f ca="1"/>
@@ -42297,13 +42397,17 @@
       </c>
       <c r="J671">
         <f ca="1"/>
-        <v>79.486620000000002</v>
+        <v>80.732240000000004</v>
       </c>
     </row>
     <row r="672" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A672" t="str">
         <v>2025-11-30</v>
       </c>
+      <c r="B672">
+        <f t="shared" ca="1" si="40"/>
+        <v>237.53735686629977</v>
+      </c>
       <c r="C672">
         <f ca="1"/>
         <v>325.06299999999999</v>
@@ -42312,9 +42416,21 @@
         <f ca="1"/>
         <v>4.0899999999999999E-2</v>
       </c>
+      <c r="E672">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.4083333333333331E-3</v>
+      </c>
       <c r="F672">
         <f ca="1"/>
-        <v>247.15666999999999</v>
+        <v>238.83932999999999</v>
+      </c>
+      <c r="G672" t="e">
+        <f t="shared" ca="1" si="43"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H672" t="e">
+        <f t="shared" ca="1" si="44"/>
+        <v>#VALUE!</v>
       </c>
       <c r="I672">
         <f ca="1"/>
@@ -42322,13 +42438,17 @@
       </c>
       <c r="J672">
         <f ca="1"/>
-        <v>80.104669999999999</v>
+        <v>81.359979999999993</v>
       </c>
     </row>
     <row r="673" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A673" t="str">
         <v>2025-12-31</v>
       </c>
+      <c r="B673">
+        <f t="shared" ca="1" si="40"/>
+        <v>238.61168568019602</v>
+      </c>
       <c r="C673">
         <f ca="1"/>
         <v>326.03100000000001</v>
@@ -42337,9 +42457,21 @@
         <f ca="1"/>
         <v>4.1399999999999999E-2</v>
       </c>
+      <c r="E673">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.4499999999999999E-3</v>
+      </c>
       <c r="F673">
         <f ca="1"/>
-        <v>253.11</v>
+        <v>240.63399999999999</v>
+      </c>
+      <c r="G673">
+        <f t="shared" ca="1" si="43"/>
+        <v>2.9778842870460398E-3</v>
+      </c>
+      <c r="H673">
+        <f t="shared" ca="1" si="44"/>
+        <v>4.7211571295396014E-4</v>
       </c>
       <c r="I673">
         <f ca="1"/>
@@ -42347,13 +42479,17 @@
       </c>
       <c r="J673">
         <f ca="1"/>
-        <v>80.472300000000004</v>
+        <v>81.733369999999994</v>
       </c>
     </row>
     <row r="674" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A674" t="str">
         <v>2026-01-31</v>
       </c>
+      <c r="B674">
+        <f t="shared" ca="1" si="40"/>
+        <v>245.16343386153193</v>
+      </c>
       <c r="C674">
         <f ca="1"/>
         <v>326.58800000000002</v>
@@ -42362,23 +42498,39 @@
         <f ca="1"/>
         <v>4.2099999999999999E-2</v>
       </c>
+      <c r="E674">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.5083333333333334E-3</v>
+      </c>
       <c r="F674">
         <f ca="1"/>
-        <v>261.30667</v>
+        <v>247.66367</v>
+      </c>
+      <c r="G674">
+        <f t="shared" ca="1" si="43"/>
+        <v>1.70842649932057E-3</v>
+      </c>
+      <c r="H674">
+        <f t="shared" ca="1" si="44"/>
+        <v>1.7999068340127634E-3</v>
       </c>
       <c r="I674">
         <f ca="1"/>
-        <v>1.54E-2</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="J674">
         <f ca="1"/>
-        <v>80.266639999999995</v>
+        <v>81.720860000000002</v>
       </c>
     </row>
     <row r="675" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A675" t="str">
         <v>2026-02-28</v>
       </c>
+      <c r="B675">
+        <f t="shared" ca="1" si="40"/>
+        <v>251.45074619504675</v>
+      </c>
       <c r="C675">
         <f ca="1"/>
         <v>327.45999999999998</v>
@@ -42387,23 +42539,39 @@
         <f ca="1"/>
         <v>4.1300000000000003E-2</v>
       </c>
+      <c r="E675">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.4416666666666671E-3</v>
+      </c>
       <c r="F675">
         <f ca="1"/>
-        <v>269.50333000000001</v>
+        <v>254.69333</v>
+      </c>
+      <c r="G675">
+        <f t="shared" ca="1" si="43"/>
+        <v>2.6700307420970404E-3</v>
+      </c>
+      <c r="H675">
+        <f t="shared" ca="1" si="44"/>
+        <v>7.716359245696267E-4</v>
       </c>
       <c r="I675">
         <f ca="1"/>
-        <v>1.7000000000000001E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="J675">
         <f ca="1"/>
-        <v>79.980410000000006</v>
+        <v>81.624690000000001</v>
       </c>
     </row>
     <row r="676" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A676" t="str">
         <v>2026-03-31</v>
       </c>
+      <c r="B676">
+        <f t="shared" ca="1" si="40"/>
+        <v>256.17464007108839</v>
+      </c>
       <c r="C676">
         <f ca="1"/>
         <v>330.29300000000001</v>
@@ -42412,30 +42580,174 @@
         <f ca="1"/>
         <v>4.2500000000000003E-2</v>
       </c>
+      <c r="E676">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.5416666666666669E-3</v>
+      </c>
       <c r="F676">
         <f ca="1"/>
-        <v>277.7</v>
+        <v>261.72300000000001</v>
+      </c>
+      <c r="G676">
+        <f t="shared" ca="1" si="43"/>
+        <v>8.6514383436144815E-3</v>
+      </c>
+      <c r="H676">
+        <f t="shared" ca="1" si="44"/>
+        <v>-5.1097716769478146E-3</v>
       </c>
       <c r="I676">
         <f ca="1"/>
-        <v>1.67E-2</v>
+        <v>1.77E-2</v>
       </c>
       <c r="J676">
         <f ca="1"/>
-        <v>79.883359999999996</v>
+        <v>81.061530000000005</v>
       </c>
     </row>
     <row r="677" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A677" t="str">
         <v>2026-04-30</v>
       </c>
+      <c r="C677">
+        <f ca="1"/>
+        <v>332.40699999999998</v>
+      </c>
       <c r="D677">
         <f ca="1"/>
-        <v>4.2999999999999997E-2</v>
+        <v>4.3200000000000002E-2</v>
+      </c>
+      <c r="E677">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.6000000000000003E-3</v>
+      </c>
+      <c r="G677">
+        <f t="shared" ca="1" si="43"/>
+        <v>6.4003778463364025E-3</v>
+      </c>
+      <c r="H677">
+        <f t="shared" ca="1" si="44"/>
+        <v>-2.8003778463364022E-3</v>
       </c>
       <c r="I677">
         <f ca="1"/>
-        <v>1.6400000000000001E-2</v>
+        <v>1.66E-2</v>
+      </c>
+      <c r="J677">
+        <f ca="1"/>
+        <v>80.599710000000002</v>
+      </c>
+    </row>
+    <row r="678" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A678" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C678">
+        <f ca="1"/>
+        <v>333.97899999999998</v>
+      </c>
+      <c r="D678">
+        <f ca="1"/>
+        <v>4.48E-2</v>
+      </c>
+      <c r="E678">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.7333333333333333E-3</v>
+      </c>
+      <c r="G678">
+        <f t="shared" ca="1" si="43"/>
+        <v>4.7291422864139676E-3</v>
+      </c>
+      <c r="H678">
+        <f t="shared" ca="1" si="44"/>
+        <v>-9.9580895308063432E-4</v>
+      </c>
+      <c r="I678">
+        <f ca="1"/>
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="J678">
+        <f ca="1"/>
+        <v>80.313969999999998</v>
+      </c>
+    </row>
+    <row r="679" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A679" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="C679">
+        <f ca="1"/>
+        <v>332.56799999999998</v>
+      </c>
+      <c r="D679">
+        <f ca="1"/>
+        <v>4.4699999999999997E-2</v>
+      </c>
+      <c r="E679">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.7249999999999996E-3</v>
+      </c>
+      <c r="G679">
+        <f t="shared" ca="1" si="43"/>
+        <v>-4.2248165303806484E-3</v>
+      </c>
+      <c r="H679">
+        <f t="shared" ca="1" si="44"/>
+        <v>7.9498165303806476E-3</v>
+      </c>
+      <c r="I679">
+        <f ca="1"/>
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="J679">
+        <f ca="1"/>
+        <v>80.816400000000002</v>
+      </c>
+    </row>
+    <row r="680" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A680" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="C680">
+        <f ca="1"/>
+        <v>332.81299999999999</v>
+      </c>
+      <c r="D680">
+        <f ca="1"/>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="E680">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.8333333333333331E-3</v>
+      </c>
+      <c r="G680">
+        <f t="shared" ca="1" si="43"/>
+        <v>7.3669144355448246E-4</v>
+      </c>
+      <c r="H680">
+        <f t="shared" ca="1" si="44"/>
+        <v>3.0966418897788507E-3</v>
+      </c>
+      <c r="I680">
+        <f ca="1"/>
+        <v>1.18E-2</v>
+      </c>
+    </row>
+    <row r="681" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A681" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="D681">
+        <f ca="1"/>
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="E681">
+        <f t="shared" ca="1" si="41"/>
+        <v>3.9583333333333337E-3</v>
+      </c>
+      <c r="I681">
+        <f ca="1"/>
+        <v>9.7000000000000003E-3</v>
       </c>
     </row>
   </sheetData>
